--- a/pilar_a/data/Archivos 2026/01_KPI Gestión REDCO_2026.xlsx
+++ b/pilar_a/data/Archivos 2026/01_KPI Gestión REDCO_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://redcoglobalcl.sharepoint.com/sites/GestinEstratgicaREDCO/Shared Documents/General/Gestión Estratégica 2026/202512_Reunión 12 (Diciembre 2025)/Archivos 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/udd/redco_proyect/pilar_a/data/Archivos 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5573D6A-765A-4BBD-9631-884C4A4DC62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8CAE78-8A39-804E-82C0-DA6BE821FA65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="7" xr2:uid="{4C009CC9-234F-4387-A9FC-237F9D80746C}"/>
+    <workbookView xWindow="3820" yWindow="2380" windowWidth="23260" windowHeight="13020" activeTab="7" xr2:uid="{4C009CC9-234F-4387-A9FC-237F9D80746C}"/>
   </bookViews>
   <sheets>
     <sheet name="KPIs_v1" sheetId="4" state="hidden" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Dashboard 2026" sheetId="14" r:id="rId11"/>
     <sheet name="Vasos comunicantes" sheetId="16" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -105,17 +105,17 @@
     </comment>
     <comment ref="BL14" authorId="1" shapeId="0" xr:uid="{9C79CA23-7444-4EC9-A862-016D818B0E90}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se quita AMSA RIINO y HDD</t>
       </text>
     </comment>
     <comment ref="AW17" authorId="2" shapeId="0" xr:uid="{BE1A866C-FEBC-43B1-BC9C-35293926D488}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se agrega invoice 03 emitido a Franco Nevada la ultima semana de julio por 99 kUSD</t>
       </text>
     </comment>
@@ -255,25 +255,25 @@
   <commentList>
     <comment ref="BL8" authorId="0" shapeId="0" xr:uid="{25C0FD45-3462-464B-AE3A-2F6E585A4329}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se quita AMSA RIINO y HDD</t>
       </text>
     </comment>
     <comment ref="BM10" authorId="1" shapeId="0" xr:uid="{8E8B538D-F26B-48EA-AA5B-065C86F76E09}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se suman los trabajos adicionales a Py Los Calatos V3 por 41k</t>
       </text>
     </comment>
     <comment ref="AW11" authorId="2" shapeId="0" xr:uid="{AC8B7546-E2B4-40F9-85AE-96800B93B9EF}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se agrega invoice 03 emitido a Franco Nevada la ultima semana de julio por 99 kUSD</t>
       </text>
     </comment>
@@ -512,25 +512,25 @@
     </comment>
     <comment ref="BF8" authorId="2" shapeId="0" xr:uid="{02A34764-E66A-4EE5-B2F5-CBDBB61FD64C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se quita AMSA RIINO y HDD</t>
       </text>
     </comment>
     <comment ref="BG10" authorId="3" shapeId="0" xr:uid="{233C6B5E-AD6E-4B43-9459-5D58742E082C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se suman los trabajos adicionales a Py Los Calatos V3 por 41k</t>
       </text>
     </comment>
     <comment ref="AQ11" authorId="4" shapeId="0" xr:uid="{D1278AE0-395A-4E97-8EE6-4B28E873EE5C}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Comentario encadenado]
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
     Se agrega invoice 03 emitido a Franco Nevada la ultima semana de julio por 99 kUSD</t>
       </text>
     </comment>
@@ -2208,16 +2208,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="#,##0_ ;\-#,##0\ "/>
-    <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="0.0\ \p\p"/>
-    <numFmt numFmtId="171" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="#,##0_ ;\-#,##0\ "/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0\ \p\p"/>
+    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="97">
+  <fonts count="97" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4400,7 +4400,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="716">
@@ -4427,7 +4427,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4454,7 +4454,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4470,7 +4470,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="5" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4487,7 +4487,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="5" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4500,7 +4500,7 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="6" fillId="5" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4567,7 +4567,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4595,7 +4595,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4613,22 +4613,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4845,7 +4845,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="12" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4860,7 +4860,7 @@
     <xf numFmtId="3" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="11" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4887,10 +4887,10 @@
     <xf numFmtId="3" fontId="8" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4986,7 +4986,7 @@
     <xf numFmtId="3" fontId="12" fillId="9" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5067,7 +5067,7 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5079,10 +5079,10 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="42" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5585,7 +5585,7 @@
     <xf numFmtId="3" fontId="51" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="51" fillId="24" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="51" fillId="24" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="14" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5597,7 +5597,7 @@
     <xf numFmtId="3" fontId="51" fillId="14" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="51" fillId="24" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="51" fillId="24" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5615,7 +5615,7 @@
     <xf numFmtId="3" fontId="50" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="50" fillId="24" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="50" fillId="24" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="76" fillId="14" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5633,7 +5633,7 @@
     <xf numFmtId="3" fontId="51" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="51" fillId="24" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="51" fillId="24" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="14" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5642,10 +5642,10 @@
     <xf numFmtId="0" fontId="72" fillId="14" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="51" fillId="14" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="51" fillId="14" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="51" fillId="24" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="51" fillId="24" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="49" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5654,25 +5654,25 @@
     <xf numFmtId="3" fontId="51" fillId="24" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="51" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="51" fillId="24" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="51" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="51" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="50" fillId="24" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="50" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="51" fillId="24" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="51" fillId="24" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="51" fillId="24" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="14" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5795,7 +5795,7 @@
     <xf numFmtId="3" fontId="56" fillId="10" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="10" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="56" fillId="10" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="57" fillId="10" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5807,11 +5807,11 @@
     <xf numFmtId="3" fontId="56" fillId="17" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="56" fillId="17" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="56" fillId="17" borderId="105" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="105" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="56" fillId="10" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="56" fillId="10" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="105" xfId="0" applyFill="1" applyBorder="1"/>
@@ -5819,7 +5819,7 @@
     <xf numFmtId="3" fontId="55" fillId="20" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="55" fillId="20" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="55" fillId="20" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="55" fillId="20" borderId="102" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5870,6 +5870,306 @@
     <xf numFmtId="1" fontId="80" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="29" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="44" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="47" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="32" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="58" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5957,300 +6257,6 @@
     <xf numFmtId="3" fontId="58" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="6" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="6" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="29" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="44" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="47" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="32" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="77" fillId="14" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6314,6 +6320,7 @@
     <xf numFmtId="0" fontId="60" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="62" fillId="10" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6344,9 +6351,13 @@
     <xf numFmtId="0" fontId="62" fillId="10" borderId="108" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="17" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="53" fillId="17" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="10" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="88" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="89" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -6359,36 +6370,25 @@
     <xf numFmtId="0" fontId="92" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="17" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="15" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="88" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="17" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="53" fillId="17" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="10" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="10" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="56" fillId="17" borderId="91" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="55" fillId="20" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="56" fillId="10" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="104" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="20" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Millares [0]" xfId="1" builtinId="6"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="22">
     <dxf>
@@ -6473,22 +6473,22 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF2D6A4F"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFC8553D"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFC8553D"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF2D6A4F"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF2D6A4F"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFC8553D"/>
       </font>
     </dxf>
     <dxf>
@@ -6525,7 +6525,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6936,7 +6936,7 @@
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7351,7 +7351,7 @@
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7770,7 +7770,7 @@
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8312,7 +8312,7 @@
 <file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8711,7 +8711,7 @@
 <file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9228,7 +9228,7 @@
 <file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9745,7 +9745,7 @@
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10265,7 +10265,7 @@
 <file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10817,7 +10817,7 @@
 <file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11642,7 +11642,7 @@
 <file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -11995,7 +11995,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -12421,7 +12421,7 @@
 <file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13053,7 +13053,7 @@
 <file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -13378,7 +13378,7 @@
 <file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14066,7 +14066,7 @@
 <file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14502,7 +14502,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14921,7 +14921,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15340,7 +15340,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15895,7 +15895,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -16395,7 +16395,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17015,7 +17015,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -17426,7 +17426,7 @@
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -31787,27 +31787,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBB576E-7EED-48AF-ACAA-415CC711666B}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="B1:X35"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.9" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="48"/>
-    <col min="2" max="2" width="2.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.140625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="7.85546875" style="48" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="7.85546875" style="48" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="48"/>
+    <col min="2" max="2" width="2.83203125" style="48" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.1640625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="7.83203125" style="48" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="7.83203125" style="48" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="6" style="48" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="7.85546875" style="48" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="8.85546875" style="48" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.85546875" style="48" customWidth="1"/>
-    <col min="19" max="19" width="7.5703125" style="48" customWidth="1"/>
-    <col min="20" max="16384" width="11.5703125" style="48"/>
+    <col min="11" max="11" width="7.83203125" style="48" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="8.83203125" style="48" customWidth="1"/>
+    <col min="17" max="17" width="10.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" style="48" customWidth="1"/>
+    <col min="19" max="19" width="7.5" style="48" customWidth="1"/>
+    <col min="20" max="16384" width="11.5" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.45" thickBot="1"/>
-    <row r="2" spans="2:21" ht="14.45" thickBot="1">
+    <row r="1" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="116" t="s">
         <v>0</v>
       </c>
@@ -31866,11 +31866,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="18" customHeight="1">
-      <c r="B3" s="565">
+    <row r="3" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="538">
         <v>1</v>
       </c>
-      <c r="C3" s="567" t="s">
+      <c r="C3" s="540" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="105" t="s">
@@ -31900,7 +31900,7 @@
         <f>+SUM(H3:J3)</f>
         <v>42</v>
       </c>
-      <c r="L3" s="569">
+      <c r="L3" s="542">
         <f>+K4/K3</f>
         <v>236.3095238095238</v>
       </c>
@@ -31923,16 +31923,16 @@
       <c r="R3" s="106">
         <v>3</v>
       </c>
-      <c r="S3" s="582">
+      <c r="S3" s="555">
         <f>+R4/R3</f>
         <v>323.66666666666669</v>
       </c>
       <c r="T3" s="61"/>
       <c r="U3" s="152"/>
     </row>
-    <row r="4" spans="2:21" ht="18" customHeight="1" thickBot="1">
-      <c r="B4" s="566"/>
-      <c r="C4" s="568"/>
+    <row r="4" spans="2:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="539"/>
+      <c r="C4" s="541"/>
       <c r="D4" s="108" t="s">
         <v>13</v>
       </c>
@@ -31961,7 +31961,7 @@
         <f t="shared" ref="K4:K23" si="0">+SUM(H4:J4)</f>
         <v>9925</v>
       </c>
-      <c r="L4" s="570"/>
+      <c r="L4" s="543"/>
       <c r="M4" s="109">
         <v>200</v>
       </c>
@@ -31981,14 +31981,14 @@
       <c r="R4" s="109">
         <v>971</v>
       </c>
-      <c r="S4" s="583"/>
+      <c r="S4" s="556"/>
       <c r="U4" s="152"/>
     </row>
-    <row r="5" spans="2:21" ht="18" customHeight="1">
-      <c r="B5" s="565">
+    <row r="5" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="538">
         <v>2</v>
       </c>
-      <c r="C5" s="567" t="s">
+      <c r="C5" s="540" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="105" t="s">
@@ -32016,7 +32016,7 @@
         <f>+SUM(H5:J5)</f>
         <v>18</v>
       </c>
-      <c r="L5" s="569">
+      <c r="L5" s="542">
         <f>+K6/K5</f>
         <v>181.66666666666666</v>
       </c>
@@ -32039,15 +32039,15 @@
       <c r="R5" s="114">
         <v>1</v>
       </c>
-      <c r="S5" s="582">
+      <c r="S5" s="555">
         <f>+R6/R5</f>
         <v>1045</v>
       </c>
       <c r="U5" s="154"/>
     </row>
-    <row r="6" spans="2:21" ht="18" customHeight="1" thickBot="1">
-      <c r="B6" s="566"/>
-      <c r="C6" s="568"/>
+    <row r="6" spans="2:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="539"/>
+      <c r="C6" s="541"/>
       <c r="D6" s="108" t="s">
         <v>13</v>
       </c>
@@ -32075,7 +32075,7 @@
         <f t="shared" si="0"/>
         <v>3270</v>
       </c>
-      <c r="L6" s="570"/>
+      <c r="L6" s="543"/>
       <c r="M6" s="115">
         <v>690</v>
       </c>
@@ -32095,10 +32095,10 @@
       <c r="R6" s="115">
         <v>1045</v>
       </c>
-      <c r="S6" s="583"/>
+      <c r="S6" s="556"/>
       <c r="U6" s="152"/>
     </row>
-    <row r="7" spans="2:21" ht="18" hidden="1" customHeight="1">
+    <row r="7" spans="2:21" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="111"/>
       <c r="C7" s="112" t="s">
         <v>15</v>
@@ -32125,7 +32125,7 @@
       <c r="R7" s="103"/>
       <c r="S7" s="54"/>
     </row>
-    <row r="8" spans="2:21" ht="18" hidden="1" customHeight="1">
+    <row r="8" spans="2:21" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B8" s="46"/>
       <c r="C8" s="62" t="s">
         <v>17</v>
@@ -32152,7 +32152,7 @@
       <c r="R8" s="60"/>
       <c r="S8" s="49"/>
     </row>
-    <row r="9" spans="2:21" ht="30.6" hidden="1" customHeight="1" thickBot="1">
+    <row r="9" spans="2:21" ht="30.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="63"/>
       <c r="C9" s="120" t="s">
         <v>19</v>
@@ -32179,11 +32179,11 @@
       <c r="R9" s="124"/>
       <c r="S9" s="55"/>
     </row>
-    <row r="10" spans="2:21" ht="18" customHeight="1">
-      <c r="B10" s="565">
+    <row r="10" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="538">
         <v>3</v>
       </c>
-      <c r="C10" s="567" t="s">
+      <c r="C10" s="540" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="105" t="s">
@@ -32205,7 +32205,7 @@
         <f>+SUM(H10:J10)</f>
         <v>15</v>
       </c>
-      <c r="L10" s="569">
+      <c r="L10" s="542">
         <f>+K11/K10</f>
         <v>193</v>
       </c>
@@ -32224,14 +32224,14 @@
       <c r="R10" s="106">
         <v>0</v>
       </c>
-      <c r="S10" s="582">
+      <c r="S10" s="555">
         <v>0</v>
       </c>
       <c r="U10" s="152"/>
     </row>
-    <row r="11" spans="2:21" ht="18" customHeight="1" thickBot="1">
-      <c r="B11" s="571"/>
-      <c r="C11" s="572"/>
+    <row r="11" spans="2:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="544"/>
+      <c r="C11" s="545"/>
       <c r="D11" s="42" t="s">
         <v>13</v>
       </c>
@@ -32251,7 +32251,7 @@
         <f t="shared" si="0"/>
         <v>2895</v>
       </c>
-      <c r="L11" s="573"/>
+      <c r="L11" s="546"/>
       <c r="M11" s="43">
         <v>0</v>
       </c>
@@ -32267,12 +32267,12 @@
       <c r="R11" s="43">
         <v>0</v>
       </c>
-      <c r="S11" s="586"/>
+      <c r="S11" s="559"/>
       <c r="U11" s="152"/>
     </row>
-    <row r="12" spans="2:21" ht="14.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="B12" s="566"/>
-      <c r="C12" s="568"/>
+    <row r="12" spans="2:21" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="539"/>
+      <c r="C12" s="541"/>
       <c r="D12" s="126" t="s">
         <v>21</v>
       </c>
@@ -32292,7 +32292,7 @@
         <f>+SUM(H12:J12)</f>
         <v>8</v>
       </c>
-      <c r="L12" s="570"/>
+      <c r="L12" s="543"/>
       <c r="M12" s="127"/>
       <c r="N12" s="127"/>
       <c r="O12" s="127"/>
@@ -32302,13 +32302,13 @@
         <v>0</v>
       </c>
       <c r="R12" s="127"/>
-      <c r="S12" s="583"/>
+      <c r="S12" s="556"/>
     </row>
-    <row r="13" spans="2:21" ht="18" customHeight="1">
-      <c r="B13" s="565">
+    <row r="13" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="538">
         <v>4</v>
       </c>
-      <c r="C13" s="567" t="s">
+      <c r="C13" s="540" t="s">
         <v>22</v>
       </c>
       <c r="D13" s="105" t="s">
@@ -32330,7 +32330,7 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="L13" s="569">
+      <c r="L13" s="542">
         <f>+K14/K13</f>
         <v>31.950819672131146</v>
       </c>
@@ -32353,15 +32353,15 @@
       <c r="R13" s="106">
         <v>16</v>
       </c>
-      <c r="S13" s="582">
+      <c r="S13" s="555">
         <f>+R14/R13</f>
         <v>35.1875</v>
       </c>
       <c r="U13" s="152"/>
     </row>
-    <row r="14" spans="2:21" ht="18" customHeight="1" thickBot="1">
-      <c r="B14" s="566"/>
-      <c r="C14" s="568"/>
+    <row r="14" spans="2:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="539"/>
+      <c r="C14" s="541"/>
       <c r="D14" s="108" t="s">
         <v>13</v>
       </c>
@@ -32381,7 +32381,7 @@
         <f t="shared" si="0"/>
         <v>1949</v>
       </c>
-      <c r="L14" s="570"/>
+      <c r="L14" s="543"/>
       <c r="M14" s="109">
         <v>762</v>
       </c>
@@ -32401,13 +32401,13 @@
       <c r="R14" s="109">
         <v>563</v>
       </c>
-      <c r="S14" s="583"/>
+      <c r="S14" s="556"/>
     </row>
-    <row r="15" spans="2:21" ht="18" customHeight="1">
-      <c r="B15" s="565">
+    <row r="15" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="538">
         <v>5</v>
       </c>
-      <c r="C15" s="567" t="s">
+      <c r="C15" s="540" t="s">
         <v>23</v>
       </c>
       <c r="D15" s="105" t="s">
@@ -32429,7 +32429,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="L15" s="569">
+      <c r="L15" s="542">
         <f>+K16/K15</f>
         <v>34.384615384615387</v>
       </c>
@@ -32452,13 +32452,13 @@
       <c r="R15" s="106">
         <v>0</v>
       </c>
-      <c r="S15" s="582">
+      <c r="S15" s="555">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:21" ht="18" customHeight="1" thickBot="1">
-      <c r="B16" s="566"/>
-      <c r="C16" s="568"/>
+    <row r="16" spans="2:21" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="539"/>
+      <c r="C16" s="541"/>
       <c r="D16" s="108" t="s">
         <v>13</v>
       </c>
@@ -32479,7 +32479,7 @@
         <f t="shared" si="0"/>
         <v>1788</v>
       </c>
-      <c r="L16" s="570"/>
+      <c r="L16" s="543"/>
       <c r="M16" s="109">
         <v>0</v>
       </c>
@@ -32499,14 +32499,14 @@
       <c r="R16" s="109">
         <v>0</v>
       </c>
-      <c r="S16" s="583"/>
+      <c r="S16" s="556"/>
       <c r="U16" s="61"/>
     </row>
-    <row r="17" spans="2:24" ht="18" customHeight="1">
-      <c r="B17" s="576">
+    <row r="17" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="549">
         <v>6</v>
       </c>
-      <c r="C17" s="585" t="s">
+      <c r="C17" s="558" t="s">
         <v>24</v>
       </c>
       <c r="D17" s="128" t="s">
@@ -32528,7 +32528,7 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="L17" s="569">
+      <c r="L17" s="542">
         <f>+K18/K17</f>
         <v>32.379310344827587</v>
       </c>
@@ -32551,13 +32551,13 @@
       <c r="R17" s="114">
         <v>0</v>
       </c>
-      <c r="S17" s="582">
+      <c r="S17" s="555">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:24" ht="18" customHeight="1" thickBot="1">
-      <c r="B18" s="577"/>
-      <c r="C18" s="575"/>
+    <row r="18" spans="2:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="550"/>
+      <c r="C18" s="548"/>
       <c r="D18" s="129" t="s">
         <v>13</v>
       </c>
@@ -32577,7 +32577,7 @@
         <f t="shared" si="0"/>
         <v>1878</v>
       </c>
-      <c r="L18" s="570"/>
+      <c r="L18" s="543"/>
       <c r="M18" s="115">
         <v>427</v>
       </c>
@@ -32597,14 +32597,14 @@
       <c r="R18" s="115">
         <v>0</v>
       </c>
-      <c r="S18" s="583"/>
+      <c r="S18" s="556"/>
       <c r="U18" s="61"/>
     </row>
-    <row r="19" spans="2:24" ht="18" customHeight="1">
-      <c r="B19" s="576">
+    <row r="19" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="549">
         <v>7</v>
       </c>
-      <c r="C19" s="574" t="s">
+      <c r="C19" s="547" t="s">
         <v>25</v>
       </c>
       <c r="D19" s="128" t="s">
@@ -32617,7 +32617,7 @@
       <c r="I19" s="114"/>
       <c r="J19" s="114"/>
       <c r="K19" s="106"/>
-      <c r="L19" s="569"/>
+      <c r="L19" s="542"/>
       <c r="M19" s="114">
         <v>4</v>
       </c>
@@ -32637,14 +32637,14 @@
       <c r="R19" s="114">
         <v>10</v>
       </c>
-      <c r="S19" s="582">
+      <c r="S19" s="555">
         <f>+R20/R19</f>
         <v>17.5</v>
       </c>
     </row>
-    <row r="20" spans="2:24" ht="18" customHeight="1" thickBot="1">
-      <c r="B20" s="577"/>
-      <c r="C20" s="575"/>
+    <row r="20" spans="2:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="550"/>
+      <c r="C20" s="548"/>
       <c r="D20" s="143" t="s">
         <v>13</v>
       </c>
@@ -32655,7 +32655,7 @@
       <c r="I20" s="144"/>
       <c r="J20" s="144"/>
       <c r="K20" s="145"/>
-      <c r="L20" s="570"/>
+      <c r="L20" s="543"/>
       <c r="M20" s="144">
         <v>192</v>
       </c>
@@ -32675,13 +32675,13 @@
       <c r="R20" s="144">
         <v>175</v>
       </c>
-      <c r="S20" s="583"/>
+      <c r="S20" s="556"/>
     </row>
-    <row r="21" spans="2:24" ht="18" customHeight="1">
-      <c r="B21" s="576">
+    <row r="21" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="549">
         <v>8</v>
       </c>
-      <c r="C21" s="574" t="s">
+      <c r="C21" s="547" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="105" t="s">
@@ -32701,7 +32701,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="L21" s="569">
+      <c r="L21" s="542">
         <f>+K22/K21</f>
         <v>23.5</v>
       </c>
@@ -32724,14 +32724,14 @@
       <c r="R21" s="106">
         <v>1</v>
       </c>
-      <c r="S21" s="582">
+      <c r="S21" s="555">
         <f>+R22/R21</f>
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="2:24" ht="18" customHeight="1" thickBot="1">
-      <c r="B22" s="577"/>
-      <c r="C22" s="584"/>
+    <row r="22" spans="2:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="550"/>
+      <c r="C22" s="557"/>
       <c r="D22" s="108" t="s">
         <v>13</v>
       </c>
@@ -32749,7 +32749,7 @@
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="L22" s="570"/>
+      <c r="L22" s="543"/>
       <c r="M22" s="109">
         <v>70</v>
       </c>
@@ -32769,9 +32769,9 @@
       <c r="R22" s="109">
         <v>35</v>
       </c>
-      <c r="S22" s="583"/>
+      <c r="S22" s="556"/>
     </row>
-    <row r="23" spans="2:24" s="148" customFormat="1" ht="14.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="23" spans="2:24" s="148" customFormat="1" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B23" s="130"/>
       <c r="C23" s="131" t="s">
         <v>27</v>
@@ -32810,9 +32810,9 @@
       <c r="R23" s="133"/>
       <c r="S23" s="134"/>
     </row>
-    <row r="24" spans="2:24" s="148" customFormat="1" ht="14.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="B24" s="580"/>
-      <c r="C24" s="578" t="s">
+    <row r="24" spans="2:24" s="148" customFormat="1" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="553"/>
+      <c r="C24" s="551" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="98" t="s">
@@ -32825,7 +32825,7 @@
       <c r="I24" s="56"/>
       <c r="J24" s="56"/>
       <c r="K24" s="56"/>
-      <c r="L24" s="587"/>
+      <c r="L24" s="560"/>
       <c r="M24" s="56"/>
       <c r="N24" s="56"/>
       <c r="O24" s="56"/>
@@ -32835,11 +32835,11 @@
         <v>0</v>
       </c>
       <c r="R24" s="56"/>
-      <c r="S24" s="587"/>
+      <c r="S24" s="560"/>
     </row>
-    <row r="25" spans="2:24" s="148" customFormat="1" ht="14.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="B25" s="581"/>
-      <c r="C25" s="579"/>
+    <row r="25" spans="2:24" s="148" customFormat="1" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="554"/>
+      <c r="C25" s="552"/>
       <c r="D25" s="121" t="s">
         <v>13</v>
       </c>
@@ -32850,7 +32850,7 @@
       <c r="I25" s="150"/>
       <c r="J25" s="150"/>
       <c r="K25" s="150"/>
-      <c r="L25" s="588"/>
+      <c r="L25" s="561"/>
       <c r="M25" s="150"/>
       <c r="N25" s="150"/>
       <c r="O25" s="150"/>
@@ -32860,13 +32860,13 @@
         <v>0</v>
       </c>
       <c r="R25" s="150"/>
-      <c r="S25" s="588"/>
+      <c r="S25" s="561"/>
     </row>
-    <row r="26" spans="2:24" ht="18" customHeight="1">
-      <c r="B26" s="576">
+    <row r="26" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="549">
         <v>9</v>
       </c>
-      <c r="C26" s="574" t="s">
+      <c r="C26" s="547" t="s">
         <v>29</v>
       </c>
       <c r="D26" s="105" t="s">
@@ -32888,7 +32888,7 @@
         <f>+SUM(H26:J26)</f>
         <v>55</v>
       </c>
-      <c r="L26" s="569">
+      <c r="L26" s="542">
         <f>+K27/K26</f>
         <v>38.109090909090909</v>
       </c>
@@ -32911,7 +32911,7 @@
       <c r="R26" s="106">
         <v>2</v>
       </c>
-      <c r="S26" s="582">
+      <c r="S26" s="555">
         <f>+R27/R26</f>
         <v>23</v>
       </c>
@@ -32926,9 +32926,9 @@
         <v>175</v>
       </c>
     </row>
-    <row r="27" spans="2:24" ht="18" customHeight="1" thickBot="1">
-      <c r="B27" s="577"/>
-      <c r="C27" s="575"/>
+    <row r="27" spans="2:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="550"/>
+      <c r="C27" s="548"/>
       <c r="D27" s="108" t="s">
         <v>13</v>
       </c>
@@ -32948,7 +32948,7 @@
         <f>+SUM(H27:J27)</f>
         <v>2096</v>
       </c>
-      <c r="L27" s="570"/>
+      <c r="L27" s="543"/>
       <c r="M27" s="109">
         <v>197</v>
       </c>
@@ -32968,7 +32968,7 @@
       <c r="R27" s="109">
         <v>46</v>
       </c>
-      <c r="S27" s="583"/>
+      <c r="S27" s="556"/>
       <c r="T27" s="48">
         <v>706</v>
       </c>
@@ -32979,11 +32979,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="28" spans="2:24" ht="18" customHeight="1">
-      <c r="B28" s="576">
+    <row r="28" spans="2:24" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="549">
         <v>10</v>
       </c>
-      <c r="C28" s="574" t="s">
+      <c r="C28" s="547" t="s">
         <v>32</v>
       </c>
       <c r="D28" s="128" t="s">
@@ -33001,7 +33001,7 @@
         <f t="shared" ref="K28:K29" si="2">+SUM(H28:J28)</f>
         <v>8</v>
       </c>
-      <c r="L28" s="569">
+      <c r="L28" s="542">
         <f>+K29/K28</f>
         <v>35.75</v>
       </c>
@@ -33024,7 +33024,7 @@
       <c r="R28" s="106">
         <v>5</v>
       </c>
-      <c r="S28" s="582">
+      <c r="S28" s="555">
         <f>+R29/R28</f>
         <v>50.8</v>
       </c>
@@ -33035,9 +33035,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="29" spans="2:24" ht="18" customHeight="1" thickBot="1">
-      <c r="B29" s="577"/>
-      <c r="C29" s="575"/>
+    <row r="29" spans="2:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="550"/>
+      <c r="C29" s="548"/>
       <c r="D29" s="129" t="s">
         <v>35</v>
       </c>
@@ -33053,7 +33053,7 @@
         <f t="shared" si="2"/>
         <v>286</v>
       </c>
-      <c r="L29" s="570"/>
+      <c r="L29" s="543"/>
       <c r="M29" s="109">
         <v>110</v>
       </c>
@@ -33074,7 +33074,7 @@
       <c r="R29" s="109">
         <v>254</v>
       </c>
-      <c r="S29" s="583"/>
+      <c r="S29" s="556"/>
       <c r="V29" s="48" t="s">
         <v>36</v>
       </c>
@@ -33082,7 +33082,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="2:24" ht="18" customHeight="1" thickBot="1">
+    <row r="30" spans="2:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="135">
         <v>11</v>
       </c>
@@ -33143,7 +33143,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="31" spans="2:24" ht="18" customHeight="1" thickBot="1">
+    <row r="31" spans="2:24" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B31" s="135">
         <v>12</v>
       </c>
@@ -33197,7 +33197,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="4:19">
+    <row r="34" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D34" s="53"/>
       <c r="E34" s="53"/>
       <c r="F34" s="53"/>
@@ -33206,7 +33206,7 @@
       <c r="R34" s="61"/>
       <c r="S34" s="61"/>
     </row>
-    <row r="35" spans="4:19">
+    <row r="35" spans="4:19" x14ac:dyDescent="0.2">
       <c r="D35" s="53"/>
       <c r="E35" s="53"/>
       <c r="F35" s="53"/>
@@ -33272,170 +33272,170 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC5B3164-BAAE-422C-861F-C15AFA865EB8}">
   <dimension ref="A1:R118"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="415" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" style="415" customWidth="1"/>
+    <col min="1" max="1" width="1.5" style="415" customWidth="1"/>
+    <col min="2" max="2" width="34.5" style="415" customWidth="1"/>
     <col min="3" max="3" width="10" style="415" customWidth="1"/>
-    <col min="4" max="9" width="13.140625" style="415" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="415" customWidth="1"/>
-    <col min="11" max="17" width="13.140625" style="415" customWidth="1"/>
-    <col min="18" max="16384" width="10.85546875" style="415"/>
+    <col min="4" max="9" width="13.1640625" style="415" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" style="415" customWidth="1"/>
+    <col min="11" max="17" width="13.1640625" style="415" customWidth="1"/>
+    <col min="18" max="16384" width="10.83203125" style="415"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="8.1" customHeight="1"/>
-    <row r="2" spans="1:18" ht="24" customHeight="1">
+    <row r="1" spans="1:18" ht="8" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="416" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="16.149999999999999" customHeight="1">
+    <row r="3" spans="1:18" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="417" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="14.1" customHeight="1">
+    <row r="4" spans="1:18" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="418" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="8.1" customHeight="1" thickBot="1"/>
-    <row r="6" spans="1:18" ht="18" customHeight="1" thickTop="1">
-      <c r="B6" s="663" t="s">
+    <row r="5" spans="1:18" ht="8" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="665" t="s">
         <v>335</v>
       </c>
-      <c r="C6" s="664"/>
-      <c r="D6" s="663" t="s">
+      <c r="C6" s="666"/>
+      <c r="D6" s="665" t="s">
         <v>286</v>
       </c>
-      <c r="E6" s="664"/>
-      <c r="F6" s="664"/>
-      <c r="G6" s="663" t="s">
+      <c r="E6" s="666"/>
+      <c r="F6" s="666"/>
+      <c r="G6" s="665" t="s">
         <v>336</v>
       </c>
-      <c r="H6" s="664"/>
-      <c r="I6" s="664"/>
-      <c r="J6" s="663" t="s">
+      <c r="H6" s="666"/>
+      <c r="I6" s="666"/>
+      <c r="J6" s="665" t="s">
         <v>337</v>
       </c>
-      <c r="K6" s="664"/>
-      <c r="L6" s="664"/>
-      <c r="M6" s="663" t="s">
+      <c r="K6" s="666"/>
+      <c r="L6" s="666"/>
+      <c r="M6" s="665" t="s">
         <v>338</v>
       </c>
-      <c r="N6" s="670"/>
-      <c r="O6" s="671"/>
+      <c r="N6" s="672"/>
+      <c r="O6" s="673"/>
     </row>
-    <row r="7" spans="1:18" ht="4.1500000000000004" customHeight="1">
-      <c r="B7" s="665"/>
-      <c r="C7" s="666"/>
-      <c r="D7" s="665"/>
-      <c r="E7" s="666"/>
-      <c r="F7" s="666"/>
-      <c r="G7" s="665"/>
-      <c r="H7" s="666"/>
-      <c r="I7" s="666"/>
-      <c r="J7" s="665"/>
-      <c r="K7" s="666"/>
-      <c r="L7" s="666"/>
-      <c r="M7" s="665"/>
-      <c r="N7" s="666"/>
-      <c r="O7" s="672"/>
+    <row r="7" spans="1:18" ht="4.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="667"/>
+      <c r="C7" s="668"/>
+      <c r="D7" s="667"/>
+      <c r="E7" s="668"/>
+      <c r="F7" s="668"/>
+      <c r="G7" s="667"/>
+      <c r="H7" s="668"/>
+      <c r="I7" s="668"/>
+      <c r="J7" s="667"/>
+      <c r="K7" s="668"/>
+      <c r="L7" s="668"/>
+      <c r="M7" s="667"/>
+      <c r="N7" s="668"/>
+      <c r="O7" s="674"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1">
-      <c r="B8" s="667" t="str">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="669" t="str">
         <f>TEXT(E37,"#.##0")&amp;" kUS$  ("&amp;E36&amp;" #)"</f>
         <v>4.051 kUS$  (34 #)</v>
       </c>
-      <c r="C8" s="666"/>
-      <c r="D8" s="667" t="str">
+      <c r="C8" s="668"/>
+      <c r="D8" s="669" t="str">
         <f>TEXT(E39,"#.##0")&amp;" kUS$  ("&amp;E38&amp;" #)"</f>
         <v>3.591 kUS$  (96 #)</v>
       </c>
-      <c r="E8" s="666"/>
-      <c r="F8" s="666"/>
-      <c r="G8" s="667" t="str">
+      <c r="E8" s="668"/>
+      <c r="F8" s="668"/>
+      <c r="G8" s="669" t="str">
         <f>TEXT(E41,"#.##0")&amp;" kUS$  ("&amp;E40&amp;" #)"</f>
         <v>3.598 kUS$  (86 #)</v>
       </c>
-      <c r="H8" s="666"/>
-      <c r="I8" s="666"/>
-      <c r="J8" s="667" t="str">
+      <c r="H8" s="668"/>
+      <c r="I8" s="668"/>
+      <c r="J8" s="669" t="str">
         <f>TEXT(E43,"#.##0")&amp;" kUS$  ("&amp;E42&amp;" #)"</f>
         <v>3.134 kUS$  (76 #)</v>
       </c>
-      <c r="K8" s="666"/>
-      <c r="L8" s="666"/>
-      <c r="M8" s="667" t="str">
+      <c r="K8" s="668"/>
+      <c r="L8" s="668"/>
+      <c r="M8" s="669" t="str">
         <f>TEXT(E45,"#.##0")&amp;" kUS$  ("&amp;E44&amp;" #)"</f>
         <v>3.204 kUS$  (79 #)</v>
       </c>
-      <c r="N8" s="666"/>
-      <c r="O8" s="672"/>
+      <c r="N8" s="668"/>
+      <c r="O8" s="674"/>
     </row>
-    <row r="9" spans="1:18" ht="16.149999999999999" customHeight="1">
-      <c r="B9" s="668" t="str">
+    <row r="9" spans="1:18" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="670" t="str">
         <f>"vs "&amp;TEXT(D37,"#.##0")&amp;" kUS$ en 2025"</f>
         <v>vs 5.020 kUS$ en 2025</v>
       </c>
-      <c r="C9" s="666"/>
-      <c r="D9" s="668" t="str">
+      <c r="C9" s="668"/>
+      <c r="D9" s="670" t="str">
         <f>"vs "&amp;TEXT(D39,"#.##0")&amp;" kUS$ en 2025"</f>
         <v>vs 3.847 kUS$ en 2025</v>
       </c>
-      <c r="E9" s="666"/>
-      <c r="F9" s="666"/>
-      <c r="G9" s="668" t="str">
+      <c r="E9" s="668"/>
+      <c r="F9" s="668"/>
+      <c r="G9" s="670" t="str">
         <f>"vs "&amp;TEXT(D41,"#.##0")&amp;" kUS$ en 2025"</f>
         <v>vs 3.689 kUS$ en 2025</v>
       </c>
-      <c r="H9" s="666"/>
-      <c r="I9" s="666"/>
-      <c r="J9" s="668" t="str">
+      <c r="H9" s="668"/>
+      <c r="I9" s="668"/>
+      <c r="J9" s="670" t="str">
         <f>"vs "&amp;TEXT(D43,"#.##0")&amp;" kUS$ en 2025"</f>
         <v>vs 3.552 kUS$ en 2025</v>
       </c>
-      <c r="K9" s="666"/>
-      <c r="L9" s="666"/>
-      <c r="M9" s="668" t="str">
+      <c r="K9" s="668"/>
+      <c r="L9" s="668"/>
+      <c r="M9" s="670" t="str">
         <f>"vs "&amp;TEXT(D45,"#.##0")&amp;" kUS$ en 2025"</f>
         <v>vs 3.665 kUS$ en 2025</v>
       </c>
-      <c r="N9" s="666"/>
-      <c r="O9" s="672"/>
+      <c r="N9" s="668"/>
+      <c r="O9" s="674"/>
     </row>
-    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="B10" s="669" t="str">
+    <row r="10" spans="1:18" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="671" t="str">
         <f>IF(G37&lt;0,"▼ ","▲ ")&amp;TEXT(ABS(G37),"0,0%")</f>
         <v>▼ 19,3%</v>
       </c>
-      <c r="C10" s="666"/>
-      <c r="D10" s="669" t="str">
+      <c r="C10" s="668"/>
+      <c r="D10" s="671" t="str">
         <f>IF(G39&lt;0,"▼ ","▲ ")&amp;TEXT(ABS(G39),"0,0%")</f>
         <v>▼ 6,7%</v>
       </c>
-      <c r="E10" s="666"/>
-      <c r="F10" s="666"/>
-      <c r="G10" s="669" t="str">
+      <c r="E10" s="668"/>
+      <c r="F10" s="668"/>
+      <c r="G10" s="671" t="str">
         <f>IF(G41&lt;0,"▼ ","▲ ")&amp;TEXT(ABS(G41),"0,0%")</f>
         <v>▼ 2,5%</v>
       </c>
-      <c r="H10" s="666"/>
-      <c r="I10" s="666"/>
-      <c r="J10" s="669" t="str">
+      <c r="H10" s="668"/>
+      <c r="I10" s="668"/>
+      <c r="J10" s="671" t="str">
         <f>IF(G43&lt;0,"▼ ","▲ ")&amp;TEXT(ABS(G43),"0,0%")</f>
         <v>▼ 11,8%</v>
       </c>
-      <c r="K10" s="666"/>
-      <c r="L10" s="666"/>
-      <c r="M10" s="669" t="str">
+      <c r="K10" s="668"/>
+      <c r="L10" s="668"/>
+      <c r="M10" s="671" t="str">
         <f>IF(G45&lt;0,"▼ ","▲ ")&amp;TEXT(ABS(G45),"0,0%")</f>
         <v>▼ 12,6%</v>
       </c>
-      <c r="N10" s="666"/>
-      <c r="O10" s="672"/>
+      <c r="N10" s="668"/>
+      <c r="O10" s="674"/>
     </row>
-    <row r="11" spans="1:18" ht="12" customHeight="1">
+    <row r="11" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="419"/>
       <c r="B11" s="420"/>
       <c r="C11" s="420"/>
@@ -33454,7 +33454,7 @@
       <c r="P11" s="419"/>
       <c r="Q11" s="419"/>
     </row>
-    <row r="12" spans="1:18" ht="10.5" customHeight="1">
+    <row r="12" spans="1:18" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="419"/>
       <c r="C12" s="419"/>
       <c r="D12" s="419"/>
@@ -33472,7 +33472,7 @@
       <c r="P12" s="419"/>
       <c r="Q12" s="419"/>
     </row>
-    <row r="13" spans="1:18" ht="16.899999999999999">
+    <row r="13" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="419"/>
       <c r="B13" s="421" t="s">
         <v>339</v>
@@ -33493,7 +33493,7 @@
       <c r="P13" s="419"/>
       <c r="Q13" s="419"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" s="419"/>
       <c r="B14" s="419"/>
       <c r="C14" s="419"/>
@@ -33512,7 +33512,7 @@
       <c r="P14" s="419"/>
       <c r="Q14" s="419"/>
     </row>
-    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1">
+    <row r="15" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="419"/>
       <c r="B15" s="422" t="s">
         <v>340</v>
@@ -33566,7 +33566,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="18" customHeight="1">
+    <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="419"/>
       <c r="B16" s="426" t="s">
         <v>220</v>
@@ -33635,7 +33635,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18" customHeight="1">
+    <row r="17" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="419"/>
       <c r="B17" s="430" t="s">
         <v>220</v>
@@ -33704,7 +33704,7 @@
         <v>-0.16897389292795773</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18" customHeight="1">
+    <row r="18" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="419"/>
       <c r="B18" s="434" t="s">
         <v>221</v>
@@ -33773,7 +33773,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="18" customHeight="1">
+    <row r="19" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="419"/>
       <c r="B19" s="430" t="s">
         <v>221</v>
@@ -33842,7 +33842,7 @@
         <v>-0.5765289256198346</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="18" customHeight="1">
+    <row r="20" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="419"/>
       <c r="B20" s="434" t="s">
         <v>286</v>
@@ -33911,7 +33911,7 @@
         <v>0.17647058823529413</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="18" customHeight="1">
+    <row r="21" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="419"/>
       <c r="B21" s="430" t="s">
         <v>286</v>
@@ -33980,7 +33980,7 @@
         <v>-0.15827338129496402</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="18" customHeight="1">
+    <row r="22" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="419"/>
       <c r="B22" s="434" t="s">
         <v>23</v>
@@ -34049,7 +34049,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="18" customHeight="1">
+    <row r="23" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="419"/>
       <c r="B23" s="430" t="s">
         <v>23</v>
@@ -34118,7 +34118,7 @@
         <v>-0.23150684931506849</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="18" customHeight="1">
+    <row r="24" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="419"/>
       <c r="B24" s="434" t="s">
         <v>24</v>
@@ -34187,7 +34187,7 @@
         <v>-0.2857142857142857</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="18" customHeight="1">
+    <row r="25" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="419"/>
       <c r="B25" s="430" t="s">
         <v>24</v>
@@ -34256,7 +34256,7 @@
         <v>-0.36790393013100436</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="18" customHeight="1">
+    <row r="26" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="419"/>
       <c r="B26" s="437" t="s">
         <v>352</v>
@@ -34325,7 +34325,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="18" customHeight="1">
+    <row r="27" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="419"/>
       <c r="B27" s="440" t="s">
         <v>352</v>
@@ -34394,7 +34394,7 @@
         <v>-0.321656050955414</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="18" customHeight="1">
+    <row r="28" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="419"/>
       <c r="B28" s="442" t="s">
         <v>233</v>
@@ -34463,7 +34463,7 @@
         <v>1.6853932584269662E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="18" customHeight="1" thickBot="1">
+    <row r="29" spans="1:18" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="419"/>
       <c r="B29" s="446" t="s">
         <v>37</v>
@@ -34532,7 +34532,7 @@
         <v>-8.7003863716192426E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" s="419"/>
       <c r="B30" s="419"/>
       <c r="C30" s="419"/>
@@ -34552,7 +34552,7 @@
       <c r="Q30"/>
       <c r="R30"/>
     </row>
-    <row r="31" spans="1:18" ht="16.899999999999999">
+    <row r="31" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="419"/>
       <c r="B31" s="421" t="s">
         <v>353</v>
@@ -34573,7 +34573,7 @@
       <c r="P31" s="419"/>
       <c r="Q31" s="419"/>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" s="419"/>
       <c r="B32" s="419"/>
       <c r="C32" s="419"/>
@@ -34592,7 +34592,7 @@
       <c r="P32" s="419"/>
       <c r="Q32" s="419"/>
     </row>
-    <row r="33" spans="1:17" ht="18" customHeight="1" thickBot="1">
+    <row r="33" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A33" s="419"/>
       <c r="B33" s="422" t="s">
         <v>340</v>
@@ -34627,7 +34627,7 @@
       <c r="P33" s="419"/>
       <c r="Q33" s="419"/>
     </row>
-    <row r="34" spans="1:17" ht="18" customHeight="1">
+    <row r="34" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="419"/>
       <c r="B34" s="426" t="s">
         <v>220</v>
@@ -34668,7 +34668,7 @@
       <c r="P34" s="419"/>
       <c r="Q34" s="419"/>
     </row>
-    <row r="35" spans="1:17" ht="18" customHeight="1">
+    <row r="35" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="419"/>
       <c r="B35" s="430" t="s">
         <v>220</v>
@@ -34709,7 +34709,7 @@
       <c r="P35" s="419"/>
       <c r="Q35" s="419"/>
     </row>
-    <row r="36" spans="1:17" ht="18" customHeight="1">
+    <row r="36" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="419"/>
       <c r="B36" s="434" t="s">
         <v>221</v>
@@ -34750,7 +34750,7 @@
       <c r="P36" s="419"/>
       <c r="Q36" s="419"/>
     </row>
-    <row r="37" spans="1:17" ht="18" customHeight="1">
+    <row r="37" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="419"/>
       <c r="B37" s="430" t="s">
         <v>221</v>
@@ -34791,7 +34791,7 @@
       <c r="P37" s="419"/>
       <c r="Q37" s="419"/>
     </row>
-    <row r="38" spans="1:17" ht="18" customHeight="1">
+    <row r="38" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="419"/>
       <c r="B38" s="434" t="s">
         <v>286</v>
@@ -34832,7 +34832,7 @@
       <c r="P38" s="419"/>
       <c r="Q38" s="419"/>
     </row>
-    <row r="39" spans="1:17" ht="18" customHeight="1">
+    <row r="39" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="419"/>
       <c r="B39" s="430" t="s">
         <v>286</v>
@@ -34873,7 +34873,7 @@
       <c r="P39" s="419"/>
       <c r="Q39" s="419"/>
     </row>
-    <row r="40" spans="1:17" ht="18" customHeight="1">
+    <row r="40" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="419"/>
       <c r="B40" s="434" t="s">
         <v>23</v>
@@ -34914,7 +34914,7 @@
       <c r="P40" s="419"/>
       <c r="Q40" s="419"/>
     </row>
-    <row r="41" spans="1:17" ht="18" customHeight="1">
+    <row r="41" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="419"/>
       <c r="B41" s="430" t="s">
         <v>23</v>
@@ -34955,7 +34955,7 @@
       <c r="P41" s="419"/>
       <c r="Q41" s="419"/>
     </row>
-    <row r="42" spans="1:17" ht="18" customHeight="1">
+    <row r="42" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="419"/>
       <c r="B42" s="434" t="s">
         <v>24</v>
@@ -34996,7 +34996,7 @@
       <c r="P42" s="419"/>
       <c r="Q42" s="419"/>
     </row>
-    <row r="43" spans="1:17" ht="18" customHeight="1">
+    <row r="43" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="419"/>
       <c r="B43" s="430" t="s">
         <v>24</v>
@@ -35037,7 +35037,7 @@
       <c r="P43" s="419"/>
       <c r="Q43" s="419"/>
     </row>
-    <row r="44" spans="1:17" ht="18" customHeight="1">
+    <row r="44" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="419"/>
       <c r="B44" s="437" t="s">
         <v>352</v>
@@ -35078,7 +35078,7 @@
       <c r="P44" s="419"/>
       <c r="Q44" s="419"/>
     </row>
-    <row r="45" spans="1:17" ht="18" customHeight="1">
+    <row r="45" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="419"/>
       <c r="B45" s="440" t="s">
         <v>352</v>
@@ -35119,7 +35119,7 @@
       <c r="P45" s="419"/>
       <c r="Q45" s="419"/>
     </row>
-    <row r="46" spans="1:17" ht="18" customHeight="1">
+    <row r="46" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="419"/>
       <c r="B46" s="442" t="s">
         <v>233</v>
@@ -35160,7 +35160,7 @@
       <c r="P46" s="419"/>
       <c r="Q46" s="419"/>
     </row>
-    <row r="47" spans="1:17" ht="18" customHeight="1" thickBot="1">
+    <row r="47" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="419"/>
       <c r="B47" s="446" t="s">
         <v>37</v>
@@ -35195,7 +35195,7 @@
       <c r="P47" s="419"/>
       <c r="Q47" s="419"/>
     </row>
-    <row r="48" spans="1:17">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" s="419"/>
       <c r="B48" s="419"/>
       <c r="C48" s="419"/>
@@ -35214,7 +35214,7 @@
       <c r="P48" s="419"/>
       <c r="Q48" s="419"/>
     </row>
-    <row r="49" spans="1:17" ht="16.899999999999999">
+    <row r="49" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="419"/>
       <c r="B49" s="421" t="s">
         <v>357</v>
@@ -35235,7 +35235,7 @@
       <c r="P49" s="419"/>
       <c r="Q49" s="419"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50" s="419"/>
       <c r="B50" s="419"/>
       <c r="C50" s="419"/>
@@ -35254,7 +35254,7 @@
       <c r="P50" s="419"/>
       <c r="Q50" s="419"/>
     </row>
-    <row r="51" spans="1:17" ht="18" customHeight="1" thickBot="1">
+    <row r="51" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="419"/>
       <c r="B51" s="422" t="s">
         <v>358</v>
@@ -35285,7 +35285,7 @@
       </c>
       <c r="K51" s="419"/>
     </row>
-    <row r="52" spans="1:17" ht="18" customHeight="1">
+    <row r="52" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="419"/>
       <c r="B52" s="426" t="s">
         <v>220</v>
@@ -35323,7 +35323,7 @@
       </c>
       <c r="K52" s="419"/>
     </row>
-    <row r="53" spans="1:17" ht="18" customHeight="1">
+    <row r="53" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="419"/>
       <c r="B53" s="463"/>
       <c r="C53" s="464">
@@ -35359,7 +35359,7 @@
       </c>
       <c r="K53" s="419"/>
     </row>
-    <row r="54" spans="1:17" ht="18" customHeight="1">
+    <row r="54" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="419"/>
       <c r="B54" s="434" t="s">
         <v>366</v>
@@ -35397,7 +35397,7 @@
       </c>
       <c r="K54" s="419"/>
     </row>
-    <row r="55" spans="1:17" ht="18" customHeight="1">
+    <row r="55" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="419"/>
       <c r="B55" s="463"/>
       <c r="C55" s="464">
@@ -35433,7 +35433,7 @@
       </c>
       <c r="K55" s="419"/>
     </row>
-    <row r="56" spans="1:17" ht="18" customHeight="1">
+    <row r="56" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="419"/>
       <c r="B56" s="434" t="s">
         <v>23</v>
@@ -35471,7 +35471,7 @@
       </c>
       <c r="K56" s="419"/>
     </row>
-    <row r="57" spans="1:17" ht="18" customHeight="1">
+    <row r="57" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="419"/>
       <c r="B57" s="463"/>
       <c r="C57" s="464">
@@ -35507,7 +35507,7 @@
       </c>
       <c r="K57" s="419"/>
     </row>
-    <row r="58" spans="1:17" ht="18" customHeight="1">
+    <row r="58" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="419"/>
       <c r="B58" s="434" t="s">
         <v>24</v>
@@ -35545,7 +35545,7 @@
       </c>
       <c r="K58" s="419"/>
     </row>
-    <row r="59" spans="1:17" ht="18" customHeight="1">
+    <row r="59" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="419"/>
       <c r="B59" s="463"/>
       <c r="C59" s="464">
@@ -35581,7 +35581,7 @@
       </c>
       <c r="K59" s="419"/>
     </row>
-    <row r="60" spans="1:17" ht="18" customHeight="1">
+    <row r="60" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="419"/>
       <c r="B60" s="437" t="s">
         <v>284</v>
@@ -35619,7 +35619,7 @@
       </c>
       <c r="K60" s="419"/>
     </row>
-    <row r="61" spans="1:17" ht="18" customHeight="1">
+    <row r="61" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="419"/>
       <c r="B61" s="463"/>
       <c r="C61" s="464">
@@ -35655,7 +35655,7 @@
       </c>
       <c r="K61" s="419"/>
     </row>
-    <row r="62" spans="1:17" ht="18" customHeight="1">
+    <row r="62" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="419"/>
       <c r="B62" s="442" t="s">
         <v>233</v>
@@ -35693,7 +35693,7 @@
       </c>
       <c r="K62" s="419"/>
     </row>
-    <row r="63" spans="1:17" ht="18" customHeight="1" thickBot="1">
+    <row r="63" spans="1:17" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A63" s="419"/>
       <c r="B63" s="459"/>
       <c r="C63" s="467">
@@ -35729,7 +35729,7 @@
       </c>
       <c r="K63" s="419"/>
     </row>
-    <row r="64" spans="1:17">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64" s="419"/>
       <c r="B64" s="419"/>
       <c r="C64" s="419"/>
@@ -35748,7 +35748,7 @@
       <c r="P64" s="419"/>
       <c r="Q64" s="419"/>
     </row>
-    <row r="65" spans="1:17" ht="16.899999999999999">
+    <row r="65" spans="1:17" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="419"/>
       <c r="B65" s="421" t="s">
         <v>367</v>
@@ -35769,7 +35769,7 @@
       <c r="P65" s="419"/>
       <c r="Q65" s="419"/>
     </row>
-    <row r="66" spans="1:17">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66" s="419"/>
       <c r="B66" s="419"/>
       <c r="C66" s="419"/>
@@ -35788,7 +35788,7 @@
       <c r="P66" s="419"/>
       <c r="Q66" s="419"/>
     </row>
-    <row r="67" spans="1:17">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67" s="419"/>
       <c r="B67" s="419"/>
       <c r="C67" s="419"/>
@@ -35807,7 +35807,7 @@
       <c r="P67" s="419"/>
       <c r="Q67" s="419"/>
     </row>
-    <row r="68" spans="1:17">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68" s="419"/>
       <c r="B68" s="419"/>
       <c r="C68" s="419"/>
@@ -35826,7 +35826,7 @@
       <c r="P68" s="419"/>
       <c r="Q68" s="419"/>
     </row>
-    <row r="69" spans="1:17">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69" s="419"/>
       <c r="B69" s="419"/>
       <c r="C69" s="419"/>
@@ -35845,7 +35845,7 @@
       <c r="P69" s="419"/>
       <c r="Q69" s="419"/>
     </row>
-    <row r="70" spans="1:17">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70" s="419"/>
       <c r="B70" s="419"/>
       <c r="C70" s="419"/>
@@ -35864,7 +35864,7 @@
       <c r="P70" s="419"/>
       <c r="Q70" s="419"/>
     </row>
-    <row r="106" spans="2:16">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B106" s="460" t="s">
         <v>368</v>
       </c>
@@ -35874,7 +35874,7 @@
       <c r="I106" s="461"/>
       <c r="J106" s="462"/>
     </row>
-    <row r="107" spans="2:16">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B107" s="460" t="s">
         <v>45</v>
       </c>
@@ -35913,7 +35913,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="108" spans="2:16">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B108" s="461" t="s">
         <v>305</v>
       </c>
@@ -35960,7 +35960,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="109" spans="2:16">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B109" s="461" t="s">
         <v>307</v>
       </c>
@@ -36007,7 +36007,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="110" spans="2:16">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B110" s="461" t="s">
         <v>308</v>
       </c>
@@ -36054,7 +36054,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="111" spans="2:16">
+    <row r="111" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B111" s="461" t="s">
         <v>310</v>
       </c>
@@ -36101,7 +36101,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="112" spans="2:16">
+    <row r="112" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B112" s="461" t="s">
         <v>311</v>
       </c>
@@ -36148,32 +36148,32 @@
         <v>543</v>
       </c>
     </row>
-    <row r="113" spans="5:7">
+    <row r="113" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E113" s="461"/>
       <c r="F113" s="461"/>
       <c r="G113" s="461"/>
     </row>
-    <row r="114" spans="5:7">
+    <row r="114" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E114" s="461"/>
       <c r="F114" s="461"/>
       <c r="G114" s="461"/>
     </row>
-    <row r="115" spans="5:7">
+    <row r="115" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E115" s="461"/>
       <c r="F115" s="461"/>
       <c r="G115" s="461"/>
     </row>
-    <row r="116" spans="5:7">
+    <row r="116" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E116" s="461"/>
       <c r="F116" s="461"/>
       <c r="G116" s="461"/>
     </row>
-    <row r="117" spans="5:7">
+    <row r="117" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E117" s="461"/>
       <c r="F117" s="461"/>
       <c r="G117" s="461"/>
     </row>
-    <row r="118" spans="5:7">
+    <row r="118" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118"/>
@@ -36215,11 +36215,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10">
-    <cfRule type="containsText" dxfId="19" priority="56" operator="containsText" text="▼">
+    <cfRule type="containsText" dxfId="19" priority="57" operator="containsText" text="▲">
+      <formula>NOT(ISERROR(SEARCH("▲",D10)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="18" priority="56" operator="containsText" text="▼">
       <formula>NOT(ISERROR(SEARCH("▼",D10)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="57" operator="containsText" text="▲">
-      <formula>NOT(ISERROR(SEARCH("▲",D10)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:F29">
@@ -36232,10 +36232,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F28">
-    <cfRule type="cellIs" dxfId="17" priority="53" operator="lessThan">
+    <cfRule type="cellIs" dxfId="17" priority="52" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="52" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="53" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36281,18 +36281,18 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I28">
-    <cfRule type="cellIs" dxfId="11" priority="26" operator="greaterThan">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="27" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
     <cfRule type="iconSet" priority="25">
       <iconSet iconSet="3Arrows">
         <cfvo type="percent" val="0"/>
         <cfvo type="num" val="0" gte="0"/>
         <cfvo type="num" val="0.05" gte="0"/>
       </iconSet>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="26" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="27" operator="lessThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J10">
@@ -36512,28 +36512,28 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C439820-62AE-4366-ADBB-A1EBFD7A7E12}">
   <dimension ref="A1:Z59"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="20" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="2.83203125" customWidth="1"/>
+    <col min="2" max="20" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="45" customHeight="1">
+    <row r="1" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="407"/>
-      <c r="B1" s="683" t="s">
+      <c r="B1" s="685" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="703"/>
-      <c r="D1" s="703"/>
-      <c r="E1" s="703"/>
-      <c r="F1" s="703"/>
-      <c r="G1" s="703"/>
-      <c r="H1" s="703"/>
-      <c r="I1" s="703"/>
-      <c r="J1" s="703"/>
-      <c r="K1" s="703"/>
-      <c r="L1" s="703"/>
-      <c r="M1" s="703"/>
+      <c r="C1" s="686"/>
+      <c r="D1" s="686"/>
+      <c r="E1" s="686"/>
+      <c r="F1" s="686"/>
+      <c r="G1" s="686"/>
+      <c r="H1" s="686"/>
+      <c r="I1" s="686"/>
+      <c r="J1" s="686"/>
+      <c r="K1" s="686"/>
+      <c r="L1" s="686"/>
+      <c r="M1" s="686"/>
       <c r="N1" s="407"/>
       <c r="O1" s="407"/>
       <c r="P1" s="407"/>
@@ -36548,7 +36548,7 @@
       <c r="Y1" s="407"/>
       <c r="Z1" s="407"/>
     </row>
-    <row r="2" spans="1:26" ht="22.15" customHeight="1" thickBot="1">
+    <row r="2" spans="1:26" ht="22.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="407"/>
       <c r="B2" s="520" t="s">
         <v>378</v>
@@ -36578,7 +36578,7 @@
       <c r="Y2" s="407"/>
       <c r="Z2" s="407"/>
     </row>
-    <row r="3" spans="1:26" ht="8.1" customHeight="1">
+    <row r="3" spans="1:26" ht="8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="407"/>
       <c r="B3" s="408"/>
       <c r="C3" s="408"/>
@@ -36606,7 +36606,7 @@
       <c r="Y3" s="407"/>
       <c r="Z3" s="407"/>
     </row>
-    <row r="4" spans="1:26" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="4" spans="1:26" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="407"/>
       <c r="B4" s="516" t="s">
         <v>379</v>
@@ -36636,40 +36636,40 @@
       <c r="Y4" s="407"/>
       <c r="Z4" s="407"/>
     </row>
-    <row r="5" spans="1:26" ht="22.15" customHeight="1">
+    <row r="5" spans="1:26" ht="22.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="407"/>
-      <c r="B5" s="684" t="s">
+      <c r="B5" s="687" t="s">
         <v>380</v>
       </c>
-      <c r="C5" s="685"/>
-      <c r="D5" s="686" t="s">
+      <c r="C5" s="688"/>
+      <c r="D5" s="689" t="s">
         <v>286</v>
       </c>
-      <c r="E5" s="687"/>
-      <c r="F5" s="688" t="s">
+      <c r="E5" s="690"/>
+      <c r="F5" s="691" t="s">
         <v>336</v>
       </c>
-      <c r="G5" s="689"/>
-      <c r="H5" s="692" t="s">
+      <c r="G5" s="692"/>
+      <c r="H5" s="695" t="s">
         <v>337</v>
       </c>
-      <c r="I5" s="693"/>
-      <c r="J5" s="686" t="s">
+      <c r="I5" s="696"/>
+      <c r="J5" s="689" t="s">
         <v>338</v>
       </c>
-      <c r="K5" s="687"/>
-      <c r="L5" s="690" t="s">
+      <c r="K5" s="690"/>
+      <c r="L5" s="693" t="s">
         <v>381</v>
       </c>
-      <c r="M5" s="691"/>
-      <c r="N5" s="677" t="s">
+      <c r="M5" s="694"/>
+      <c r="N5" s="679" t="s">
         <v>382</v>
       </c>
-      <c r="O5" s="678"/>
-      <c r="P5" s="679" t="s">
+      <c r="O5" s="680"/>
+      <c r="P5" s="681" t="s">
         <v>383</v>
       </c>
-      <c r="Q5" s="680"/>
+      <c r="Q5" s="682"/>
       <c r="R5" s="407"/>
       <c r="S5" s="407"/>
       <c r="T5" s="407"/>
@@ -36680,45 +36680,45 @@
       <c r="Y5" s="407"/>
       <c r="Z5" s="407"/>
     </row>
-    <row r="6" spans="1:26" ht="42" customHeight="1">
+    <row r="6" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A6" s="407"/>
-      <c r="B6" s="681">
+      <c r="B6" s="683">
         <f>'KPI´s de negocio 2026'!BU5</f>
         <v>34</v>
       </c>
-      <c r="C6" s="682"/>
-      <c r="D6" s="681">
+      <c r="C6" s="684"/>
+      <c r="D6" s="683">
         <f>'KPI´s de negocio 2026'!BU7</f>
         <v>109</v>
       </c>
-      <c r="E6" s="682"/>
-      <c r="F6" s="681">
+      <c r="E6" s="684"/>
+      <c r="F6" s="683">
         <f>'KPI´s de negocio 2026'!BU9</f>
         <v>86</v>
       </c>
-      <c r="G6" s="682"/>
-      <c r="H6" s="681">
+      <c r="G6" s="684"/>
+      <c r="H6" s="683">
         <f>'KPI´s de negocio 2026'!BU11</f>
         <v>77</v>
       </c>
-      <c r="I6" s="682"/>
-      <c r="J6" s="681">
+      <c r="I6" s="684"/>
+      <c r="J6" s="683">
         <f>'KPI´s de negocio 2026'!BU13</f>
         <v>82</v>
       </c>
-      <c r="K6" s="682"/>
-      <c r="L6" s="681" t="s">
+      <c r="K6" s="684"/>
+      <c r="L6" s="683" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="682"/>
-      <c r="N6" s="681" t="s">
+      <c r="M6" s="684"/>
+      <c r="N6" s="683" t="s">
         <v>39</v>
       </c>
-      <c r="O6" s="682"/>
-      <c r="P6" s="681" t="s">
+      <c r="O6" s="684"/>
+      <c r="P6" s="683" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="682"/>
+      <c r="Q6" s="684"/>
       <c r="R6" s="407"/>
       <c r="S6" s="407"/>
       <c r="T6" s="407"/>
@@ -36729,39 +36729,39 @@
       <c r="Y6" s="407"/>
       <c r="Z6" s="407"/>
     </row>
-    <row r="7" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="7" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="407"/>
-      <c r="B7" s="675" t="str">
+      <c r="B7" s="677" t="str">
         <f>"vs 2025: "&amp;TEXT('KPI´s de negocio 2026'!F5,"#.##0")</f>
         <v>vs 2025: 78</v>
       </c>
-      <c r="C7" s="676"/>
-      <c r="D7" s="675" t="str">
+      <c r="C7" s="678"/>
+      <c r="D7" s="677" t="str">
         <f>"vs 2025: "&amp;TEXT('KPI´s de negocio 2026'!F7,"#.##0")</f>
         <v>vs 2025: 222</v>
       </c>
-      <c r="E7" s="676"/>
-      <c r="F7" s="675" t="str">
+      <c r="E7" s="678"/>
+      <c r="F7" s="677" t="str">
         <f>"vs 2025: "&amp;TEXT('KPI´s de negocio 2026'!F9,"#.##0")</f>
         <v>vs 2025: 204</v>
       </c>
-      <c r="G7" s="676"/>
-      <c r="H7" s="675" t="str">
+      <c r="G7" s="678"/>
+      <c r="H7" s="677" t="str">
         <f>"vs 2025: "&amp;TEXT('KPI´s de negocio 2026'!F11,"#.##0")</f>
         <v>vs 2025: 219</v>
       </c>
-      <c r="I7" s="676"/>
-      <c r="J7" s="675" t="str">
+      <c r="I7" s="678"/>
+      <c r="J7" s="677" t="str">
         <f>"vs 2025: "&amp;TEXT('KPI´s de negocio 2026'!F13,"#.##0")</f>
         <v>vs 2025: 216</v>
       </c>
-      <c r="K7" s="676"/>
-      <c r="L7" s="675"/>
-      <c r="M7" s="676"/>
-      <c r="N7" s="675"/>
-      <c r="O7" s="676"/>
-      <c r="P7" s="675"/>
-      <c r="Q7" s="676"/>
+      <c r="K7" s="678"/>
+      <c r="L7" s="677"/>
+      <c r="M7" s="678"/>
+      <c r="N7" s="677"/>
+      <c r="O7" s="678"/>
+      <c r="P7" s="677"/>
+      <c r="Q7" s="678"/>
       <c r="R7" s="407"/>
       <c r="S7" s="407"/>
       <c r="T7" s="407"/>
@@ -36772,7 +36772,7 @@
       <c r="Y7" s="407"/>
       <c r="Z7" s="407"/>
     </row>
-    <row r="8" spans="1:26" ht="16.149999999999999" customHeight="1" thickBot="1">
+    <row r="8" spans="1:26" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="407"/>
       <c r="B8" s="518" t="s">
         <v>384</v>
@@ -36802,40 +36802,40 @@
       <c r="Y8" s="407"/>
       <c r="Z8" s="407"/>
     </row>
-    <row r="9" spans="1:26" ht="22.15" customHeight="1">
+    <row r="9" spans="1:26" ht="22.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="407"/>
-      <c r="B9" s="684" t="s">
+      <c r="B9" s="687" t="s">
         <v>380</v>
       </c>
-      <c r="C9" s="685"/>
-      <c r="D9" s="686" t="s">
+      <c r="C9" s="688"/>
+      <c r="D9" s="689" t="s">
         <v>286</v>
       </c>
-      <c r="E9" s="687"/>
-      <c r="F9" s="688" t="s">
+      <c r="E9" s="690"/>
+      <c r="F9" s="691" t="s">
         <v>336</v>
       </c>
-      <c r="G9" s="689"/>
-      <c r="H9" s="692" t="s">
+      <c r="G9" s="692"/>
+      <c r="H9" s="695" t="s">
         <v>337</v>
       </c>
-      <c r="I9" s="693"/>
-      <c r="J9" s="686" t="s">
+      <c r="I9" s="696"/>
+      <c r="J9" s="689" t="s">
         <v>338</v>
       </c>
-      <c r="K9" s="687"/>
-      <c r="L9" s="690" t="s">
+      <c r="K9" s="690"/>
+      <c r="L9" s="693" t="s">
         <v>381</v>
       </c>
-      <c r="M9" s="691"/>
-      <c r="N9" s="677" t="s">
+      <c r="M9" s="694"/>
+      <c r="N9" s="679" t="s">
         <v>382</v>
       </c>
-      <c r="O9" s="678"/>
-      <c r="P9" s="679" t="s">
+      <c r="O9" s="680"/>
+      <c r="P9" s="681" t="s">
         <v>383</v>
       </c>
-      <c r="Q9" s="680"/>
+      <c r="Q9" s="682"/>
       <c r="R9" s="407"/>
       <c r="S9" s="407"/>
       <c r="T9" s="407"/>
@@ -36846,45 +36846,45 @@
       <c r="Y9" s="407"/>
       <c r="Z9" s="407"/>
     </row>
-    <row r="10" spans="1:26" ht="42" customHeight="1">
+    <row r="10" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="407"/>
-      <c r="B10" s="673">
+      <c r="B10" s="675">
         <f>'KPI´s de negocio 2026'!BU6</f>
         <v>4050.92</v>
       </c>
-      <c r="C10" s="674"/>
-      <c r="D10" s="673">
+      <c r="C10" s="676"/>
+      <c r="D10" s="675">
         <f>'KPI´s de negocio 2026'!BU8</f>
         <v>4206.6089012747216</v>
       </c>
-      <c r="E10" s="674"/>
-      <c r="F10" s="673">
+      <c r="E10" s="676"/>
+      <c r="F10" s="675">
         <f>'KPI´s de negocio 2026'!BU10</f>
         <v>3598.2507099047621</v>
       </c>
-      <c r="G10" s="674"/>
-      <c r="H10" s="673">
+      <c r="G10" s="676"/>
+      <c r="H10" s="675">
         <f>'KPI´s de negocio 2026'!BU12</f>
         <v>3210.4487193704408</v>
       </c>
-      <c r="I10" s="674"/>
-      <c r="J10" s="673">
+      <c r="I10" s="676"/>
+      <c r="J10" s="675">
         <f>'KPI´s de negocio 2026'!BU14</f>
         <v>3253</v>
       </c>
-      <c r="K10" s="674"/>
-      <c r="L10" s="673" t="s">
+      <c r="K10" s="676"/>
+      <c r="L10" s="675" t="s">
         <v>39</v>
       </c>
-      <c r="M10" s="674"/>
-      <c r="N10" s="673" t="s">
+      <c r="M10" s="676"/>
+      <c r="N10" s="675" t="s">
         <v>39</v>
       </c>
-      <c r="O10" s="674"/>
-      <c r="P10" s="673" t="s">
+      <c r="O10" s="676"/>
+      <c r="P10" s="675" t="s">
         <v>39</v>
       </c>
-      <c r="Q10" s="674"/>
+      <c r="Q10" s="676"/>
       <c r="R10" s="407"/>
       <c r="S10" s="407"/>
       <c r="T10" s="407"/>
@@ -36895,39 +36895,39 @@
       <c r="Y10" s="407"/>
       <c r="Z10" s="407"/>
     </row>
-    <row r="11" spans="1:26" ht="20.100000000000001" customHeight="1">
+    <row r="11" spans="1:26" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="407"/>
-      <c r="B11" s="675" t="str">
+      <c r="B11" s="677" t="str">
         <f>"vs 2025: kUS$ "&amp;TEXT(ROUND('KPI´s de negocio 2026'!F6,0),"#.##0")</f>
         <v>vs 2025: kUS$ 10.276</v>
       </c>
-      <c r="C11" s="676"/>
-      <c r="D11" s="675" t="str">
+      <c r="C11" s="678"/>
+      <c r="D11" s="677" t="str">
         <f>"vs 2025: kUS$ "&amp;TEXT(ROUND('KPI´s de negocio 2026'!F8,0),"#.##0")</f>
         <v>vs 2025: kUS$ 9.037</v>
       </c>
-      <c r="E11" s="676"/>
-      <c r="F11" s="675" t="str">
+      <c r="E11" s="678"/>
+      <c r="F11" s="677" t="str">
         <f>"vs 2025: kUS$ "&amp;TEXT(ROUND('KPI´s de negocio 2026'!F10,0),"#.##0")</f>
         <v>vs 2025: kUS$ 9.353</v>
       </c>
-      <c r="G11" s="676"/>
-      <c r="H11" s="675" t="str">
+      <c r="G11" s="678"/>
+      <c r="H11" s="677" t="str">
         <f>"vs 2025: kUS$ "&amp;TEXT(ROUND('KPI´s de negocio 2026'!F12,0),"#.##0")</f>
         <v>vs 2025: kUS$ 9.795</v>
       </c>
-      <c r="I11" s="676"/>
-      <c r="J11" s="675" t="str">
+      <c r="I11" s="678"/>
+      <c r="J11" s="677" t="str">
         <f>"vs 2025: kUS$ "&amp;TEXT(ROUND('KPI´s de negocio 2026'!F14,0),"#.##0")</f>
         <v>vs 2025: kUS$ 9.025</v>
       </c>
-      <c r="K11" s="676"/>
-      <c r="L11" s="675"/>
-      <c r="M11" s="676"/>
-      <c r="N11" s="675"/>
-      <c r="O11" s="676"/>
-      <c r="P11" s="675"/>
-      <c r="Q11" s="676"/>
+      <c r="K11" s="678"/>
+      <c r="L11" s="677"/>
+      <c r="M11" s="678"/>
+      <c r="N11" s="677"/>
+      <c r="O11" s="678"/>
+      <c r="P11" s="677"/>
+      <c r="Q11" s="678"/>
       <c r="R11" s="407"/>
       <c r="S11" s="407"/>
       <c r="T11" s="407"/>
@@ -36938,7 +36938,7 @@
       <c r="Y11" s="407"/>
       <c r="Z11" s="407"/>
     </row>
-    <row r="12" spans="1:26" ht="10.15" customHeight="1">
+    <row r="12" spans="1:26" ht="10.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="407"/>
       <c r="B12" s="407"/>
       <c r="C12" s="407"/>
@@ -36966,7 +36966,7 @@
       <c r="Y12" s="407"/>
       <c r="Z12" s="407"/>
     </row>
-    <row r="13" spans="1:26" ht="25.15" customHeight="1">
+    <row r="13" spans="1:26" ht="25.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="407"/>
       <c r="B13" s="409" t="s">
         <v>385</v>
@@ -36996,7 +36996,7 @@
       <c r="Y13" s="407"/>
       <c r="Z13" s="407"/>
     </row>
-    <row r="14" spans="1:26" ht="16.899999999999999">
+    <row r="14" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A14" s="407"/>
       <c r="B14" s="407"/>
       <c r="C14" s="407"/>
@@ -37024,7 +37024,7 @@
       <c r="Y14" s="407"/>
       <c r="Z14" s="407"/>
     </row>
-    <row r="15" spans="1:26" ht="16.899999999999999">
+    <row r="15" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A15" s="407"/>
       <c r="B15" s="407"/>
       <c r="C15" s="407"/>
@@ -37052,7 +37052,7 @@
       <c r="Y15" s="407"/>
       <c r="Z15" s="407"/>
     </row>
-    <row r="16" spans="1:26" ht="16.899999999999999">
+    <row r="16" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A16" s="407"/>
       <c r="B16" s="407"/>
       <c r="C16" s="407"/>
@@ -37080,7 +37080,7 @@
       <c r="Y16" s="407"/>
       <c r="Z16" s="407"/>
     </row>
-    <row r="17" spans="1:26" ht="16.899999999999999">
+    <row r="17" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A17" s="407"/>
       <c r="B17" s="407"/>
       <c r="C17" s="407"/>
@@ -37108,7 +37108,7 @@
       <c r="Y17" s="407"/>
       <c r="Z17" s="407"/>
     </row>
-    <row r="18" spans="1:26" ht="16.899999999999999">
+    <row r="18" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A18" s="407"/>
       <c r="B18" s="407"/>
       <c r="C18" s="407"/>
@@ -37136,7 +37136,7 @@
       <c r="Y18" s="407"/>
       <c r="Z18" s="407"/>
     </row>
-    <row r="19" spans="1:26" ht="16.899999999999999">
+    <row r="19" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A19" s="407"/>
       <c r="B19" s="407"/>
       <c r="C19" s="407"/>
@@ -37164,7 +37164,7 @@
       <c r="Y19" s="407"/>
       <c r="Z19" s="407"/>
     </row>
-    <row r="20" spans="1:26" ht="16.899999999999999">
+    <row r="20" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A20" s="407"/>
       <c r="B20" s="407"/>
       <c r="C20" s="407"/>
@@ -37192,7 +37192,7 @@
       <c r="Y20" s="407"/>
       <c r="Z20" s="407"/>
     </row>
-    <row r="21" spans="1:26" ht="16.899999999999999">
+    <row r="21" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A21" s="407"/>
       <c r="B21" s="407"/>
       <c r="C21" s="407"/>
@@ -37220,7 +37220,7 @@
       <c r="Y21" s="407"/>
       <c r="Z21" s="407"/>
     </row>
-    <row r="22" spans="1:26" ht="16.899999999999999">
+    <row r="22" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A22" s="407"/>
       <c r="B22" s="407"/>
       <c r="C22" s="407"/>
@@ -37248,7 +37248,7 @@
       <c r="Y22" s="407"/>
       <c r="Z22" s="407"/>
     </row>
-    <row r="23" spans="1:26" ht="16.899999999999999">
+    <row r="23" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A23" s="407"/>
       <c r="B23" s="407"/>
       <c r="C23" s="407"/>
@@ -37276,7 +37276,7 @@
       <c r="Y23" s="407"/>
       <c r="Z23" s="407"/>
     </row>
-    <row r="24" spans="1:26" ht="16.899999999999999">
+    <row r="24" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A24" s="407"/>
       <c r="B24" s="407"/>
       <c r="C24" s="407"/>
@@ -37304,7 +37304,7 @@
       <c r="Y24" s="407"/>
       <c r="Z24" s="407"/>
     </row>
-    <row r="25" spans="1:26" ht="16.899999999999999">
+    <row r="25" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A25" s="407"/>
       <c r="B25" s="407"/>
       <c r="C25" s="407"/>
@@ -37332,7 +37332,7 @@
       <c r="Y25" s="407"/>
       <c r="Z25" s="407"/>
     </row>
-    <row r="26" spans="1:26" ht="16.899999999999999">
+    <row r="26" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A26" s="407"/>
       <c r="B26" s="407"/>
       <c r="C26" s="407"/>
@@ -37360,7 +37360,7 @@
       <c r="Y26" s="407"/>
       <c r="Z26" s="407"/>
     </row>
-    <row r="27" spans="1:26" ht="16.899999999999999">
+    <row r="27" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="407"/>
       <c r="B27" s="407"/>
       <c r="C27" s="407"/>
@@ -37388,7 +37388,7 @@
       <c r="Y27" s="407"/>
       <c r="Z27" s="407"/>
     </row>
-    <row r="28" spans="1:26" ht="16.899999999999999">
+    <row r="28" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A28" s="407"/>
       <c r="B28" s="407"/>
       <c r="C28" s="407"/>
@@ -37416,7 +37416,7 @@
       <c r="Y28" s="407"/>
       <c r="Z28" s="407"/>
     </row>
-    <row r="29" spans="1:26" ht="16.899999999999999">
+    <row r="29" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A29" s="407"/>
       <c r="B29" s="407"/>
       <c r="C29" s="407"/>
@@ -37444,7 +37444,7 @@
       <c r="Y29" s="407"/>
       <c r="Z29" s="407"/>
     </row>
-    <row r="30" spans="1:26" ht="16.899999999999999">
+    <row r="30" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A30" s="407"/>
       <c r="B30" s="407"/>
       <c r="C30" s="407"/>
@@ -37472,7 +37472,7 @@
       <c r="Y30" s="407"/>
       <c r="Z30" s="407"/>
     </row>
-    <row r="31" spans="1:26" ht="16.899999999999999">
+    <row r="31" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A31" s="407"/>
       <c r="B31" s="407"/>
       <c r="C31" s="407"/>
@@ -37500,7 +37500,7 @@
       <c r="Y31" s="407"/>
       <c r="Z31" s="407"/>
     </row>
-    <row r="32" spans="1:26" ht="16.899999999999999">
+    <row r="32" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A32" s="407"/>
       <c r="B32" s="407"/>
       <c r="C32" s="407"/>
@@ -37528,7 +37528,7 @@
       <c r="Y32" s="407"/>
       <c r="Z32" s="407"/>
     </row>
-    <row r="33" spans="1:26" ht="16.899999999999999">
+    <row r="33" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A33" s="407"/>
       <c r="B33" s="407"/>
       <c r="C33" s="407"/>
@@ -37556,7 +37556,7 @@
       <c r="Y33" s="407"/>
       <c r="Z33" s="407"/>
     </row>
-    <row r="34" spans="1:26" ht="16.899999999999999">
+    <row r="34" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="407"/>
       <c r="B34" s="407"/>
       <c r="C34" s="407"/>
@@ -37584,7 +37584,7 @@
       <c r="Y34" s="407"/>
       <c r="Z34" s="407"/>
     </row>
-    <row r="35" spans="1:26" ht="16.899999999999999">
+    <row r="35" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A35" s="407"/>
       <c r="B35" s="407"/>
       <c r="C35" s="407"/>
@@ -37612,7 +37612,7 @@
       <c r="Y35" s="407"/>
       <c r="Z35" s="407"/>
     </row>
-    <row r="36" spans="1:26" ht="16.899999999999999">
+    <row r="36" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A36" s="407"/>
       <c r="B36" s="407"/>
       <c r="C36" s="407"/>
@@ -37640,7 +37640,7 @@
       <c r="Y36" s="407"/>
       <c r="Z36" s="407"/>
     </row>
-    <row r="37" spans="1:26" ht="16.899999999999999">
+    <row r="37" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A37" s="407"/>
       <c r="B37" s="407"/>
       <c r="C37" s="407"/>
@@ -37668,7 +37668,7 @@
       <c r="Y37" s="407"/>
       <c r="Z37" s="407"/>
     </row>
-    <row r="38" spans="1:26" ht="16.899999999999999">
+    <row r="38" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A38" s="407"/>
       <c r="B38" s="407"/>
       <c r="C38" s="407"/>
@@ -37696,7 +37696,7 @@
       <c r="Y38" s="407"/>
       <c r="Z38" s="407"/>
     </row>
-    <row r="39" spans="1:26" ht="16.899999999999999">
+    <row r="39" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A39" s="407"/>
       <c r="B39" s="407"/>
       <c r="C39" s="407"/>
@@ -37724,7 +37724,7 @@
       <c r="Y39" s="407"/>
       <c r="Z39" s="407"/>
     </row>
-    <row r="40" spans="1:26" ht="16.899999999999999">
+    <row r="40" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A40" s="407"/>
       <c r="B40" s="407"/>
       <c r="C40" s="407"/>
@@ -37752,7 +37752,7 @@
       <c r="Y40" s="407"/>
       <c r="Z40" s="407"/>
     </row>
-    <row r="41" spans="1:26" ht="16.899999999999999">
+    <row r="41" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A41" s="407"/>
       <c r="B41" s="407"/>
       <c r="C41" s="407"/>
@@ -37780,7 +37780,7 @@
       <c r="Y41" s="407"/>
       <c r="Z41" s="407"/>
     </row>
-    <row r="42" spans="1:26" ht="16.899999999999999">
+    <row r="42" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A42" s="407"/>
       <c r="B42" s="407"/>
       <c r="C42" s="407"/>
@@ -37808,7 +37808,7 @@
       <c r="Y42" s="407"/>
       <c r="Z42" s="407"/>
     </row>
-    <row r="43" spans="1:26" ht="16.899999999999999">
+    <row r="43" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A43" s="407"/>
       <c r="B43" s="407"/>
       <c r="C43" s="407"/>
@@ -37836,7 +37836,7 @@
       <c r="Y43" s="407"/>
       <c r="Z43" s="407"/>
     </row>
-    <row r="44" spans="1:26" ht="16.899999999999999">
+    <row r="44" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A44" s="407"/>
       <c r="B44" s="407"/>
       <c r="C44" s="407"/>
@@ -37864,7 +37864,7 @@
       <c r="Y44" s="407"/>
       <c r="Z44" s="407"/>
     </row>
-    <row r="45" spans="1:26" ht="16.899999999999999">
+    <row r="45" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A45" s="407"/>
       <c r="B45" s="407"/>
       <c r="C45" s="407"/>
@@ -37892,7 +37892,7 @@
       <c r="Y45" s="407"/>
       <c r="Z45" s="407"/>
     </row>
-    <row r="46" spans="1:26" ht="16.899999999999999">
+    <row r="46" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A46" s="407"/>
       <c r="B46" s="407"/>
       <c r="C46" s="407"/>
@@ -37920,7 +37920,7 @@
       <c r="Y46" s="407"/>
       <c r="Z46" s="407"/>
     </row>
-    <row r="47" spans="1:26" ht="16.899999999999999">
+    <row r="47" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A47" s="407"/>
       <c r="B47" s="407"/>
       <c r="C47" s="407"/>
@@ -37948,7 +37948,7 @@
       <c r="Y47" s="407"/>
       <c r="Z47" s="407"/>
     </row>
-    <row r="48" spans="1:26" ht="16.899999999999999">
+    <row r="48" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A48" s="407"/>
       <c r="B48" s="407"/>
       <c r="C48" s="407"/>
@@ -37976,7 +37976,7 @@
       <c r="Y48" s="407"/>
       <c r="Z48" s="407"/>
     </row>
-    <row r="49" spans="1:26" ht="16.899999999999999">
+    <row r="49" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A49" s="407"/>
       <c r="B49" s="407"/>
       <c r="C49" s="407"/>
@@ -38004,7 +38004,7 @@
       <c r="Y49" s="407"/>
       <c r="Z49" s="407"/>
     </row>
-    <row r="50" spans="1:26" ht="16.899999999999999">
+    <row r="50" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A50" s="407"/>
       <c r="B50" s="407"/>
       <c r="C50" s="407"/>
@@ -38032,7 +38032,7 @@
       <c r="Y50" s="407"/>
       <c r="Z50" s="407"/>
     </row>
-    <row r="51" spans="1:26" ht="16.899999999999999">
+    <row r="51" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A51" s="407"/>
       <c r="B51" s="407"/>
       <c r="C51" s="407"/>
@@ -38060,7 +38060,7 @@
       <c r="Y51" s="407"/>
       <c r="Z51" s="407"/>
     </row>
-    <row r="52" spans="1:26" ht="16.899999999999999">
+    <row r="52" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A52" s="407"/>
       <c r="B52" s="407"/>
       <c r="C52" s="407"/>
@@ -38088,7 +38088,7 @@
       <c r="Y52" s="407"/>
       <c r="Z52" s="407"/>
     </row>
-    <row r="53" spans="1:26" ht="16.899999999999999">
+    <row r="53" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A53" s="407"/>
       <c r="B53" s="414" t="s">
         <v>386</v>
@@ -38118,7 +38118,7 @@
       <c r="Y53" s="407"/>
       <c r="Z53" s="407"/>
     </row>
-    <row r="54" spans="1:26" ht="16.899999999999999">
+    <row r="54" spans="1:26" ht="16" x14ac:dyDescent="0.25">
       <c r="A54" s="407"/>
       <c r="B54" s="411" t="s">
         <v>45</v>
@@ -38172,7 +38172,7 @@
       <c r="Y54" s="407"/>
       <c r="Z54" s="407"/>
     </row>
-    <row r="55" spans="1:26">
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B55" s="413" t="s">
         <v>305</v>
       </c>
@@ -38225,7 +38225,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="56" spans="1:26">
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B56" s="413" t="s">
         <v>307</v>
       </c>
@@ -38278,7 +38278,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="57" spans="1:26">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B57" s="413" t="s">
         <v>308</v>
       </c>
@@ -38331,7 +38331,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="58" spans="1:26">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B58" s="413" t="s">
         <v>310</v>
       </c>
@@ -38379,7 +38379,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="59" spans="1:26">
+    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B59" s="413"/>
       <c r="C59" s="413"/>
       <c r="D59" s="413"/>
@@ -38457,24 +38457,24 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62585085-90E1-4B29-8977-34A8E1093D7F}">
   <dimension ref="A1:Y68"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="415" customWidth="1"/>
-    <col min="2" max="14" width="12.5703125" style="415" customWidth="1"/>
-    <col min="15" max="15" width="1.140625" style="415" customWidth="1"/>
-    <col min="16" max="16" width="1.42578125" style="415" customWidth="1"/>
-    <col min="17" max="23" width="11.5703125" style="415"/>
-    <col min="24" max="24" width="23.28515625" style="415" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.42578125" style="415" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="11.5703125" style="415"/>
+    <col min="1" max="1" width="1.1640625" style="415" customWidth="1"/>
+    <col min="2" max="14" width="12.5" style="415" customWidth="1"/>
+    <col min="15" max="15" width="1.1640625" style="415" customWidth="1"/>
+    <col min="16" max="16" width="1.5" style="415" customWidth="1"/>
+    <col min="17" max="23" width="11.5" style="415"/>
+    <col min="24" max="24" width="23.33203125" style="415" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.5" style="415" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="11.5" style="415"/>
   </cols>
   <sheetData>
-    <row r="1" spans="20:25" ht="18">
+    <row r="1" spans="20:25" ht="19" x14ac:dyDescent="0.2">
       <c r="T1" s="485" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="3" spans="20:25">
+    <row r="3" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T3" s="486" t="s">
         <v>397</v>
       </c>
@@ -38491,7 +38491,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="20:25">
+    <row r="4" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T4" s="487" t="s">
         <v>401</v>
       </c>
@@ -38508,7 +38508,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="5" spans="20:25">
+    <row r="5" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T5" s="487" t="s">
         <v>404</v>
       </c>
@@ -38525,7 +38525,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="6" spans="20:25">
+    <row r="6" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T6" s="487" t="s">
         <v>407</v>
       </c>
@@ -38542,7 +38542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="20:25">
+    <row r="7" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T7" s="487" t="s">
         <v>409</v>
       </c>
@@ -38559,7 +38559,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="8" spans="20:25">
+    <row r="8" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T8" s="487" t="s">
         <v>411</v>
       </c>
@@ -38576,7 +38576,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="9" spans="20:25">
+    <row r="9" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T9" s="487" t="s">
         <v>413</v>
       </c>
@@ -38593,7 +38593,7 @@
         <v>2770</v>
       </c>
     </row>
-    <row r="10" spans="20:25">
+    <row r="10" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T10" s="487" t="s">
         <v>416</v>
       </c>
@@ -38606,7 +38606,7 @@
       <c r="X10"/>
       <c r="Y10"/>
     </row>
-    <row r="11" spans="20:25">
+    <row r="11" spans="20:25" x14ac:dyDescent="0.2">
       <c r="T11" s="489" t="s">
         <v>418</v>
       </c>
@@ -38619,41 +38619,41 @@
       <c r="X11"/>
       <c r="Y11"/>
     </row>
-    <row r="12" spans="20:25">
+    <row r="12" spans="20:25" x14ac:dyDescent="0.2">
       <c r="X12"/>
       <c r="Y12"/>
     </row>
-    <row r="14" spans="20:25">
+    <row r="14" spans="20:25" x14ac:dyDescent="0.2">
       <c r="X14" s="491" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="15" spans="20:25">
+    <row r="15" spans="20:25" x14ac:dyDescent="0.2">
       <c r="X15" s="492" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="16" spans="20:25">
+    <row r="16" spans="20:25" x14ac:dyDescent="0.2">
       <c r="X16" s="492" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="17" spans="24:24">
+    <row r="17" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X17" s="492" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="18" spans="24:24">
+    <row r="18" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X18" s="492" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="19" spans="24:24">
+    <row r="19" spans="24:24" x14ac:dyDescent="0.2">
       <c r="X19" s="492" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="4.1500000000000004" customHeight="1">
+    <row r="40" spans="1:16" ht="4.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="483"/>
       <c r="B40" s="483"/>
       <c r="C40" s="483"/>
@@ -38671,29 +38671,29 @@
       <c r="O40" s="483"/>
       <c r="P40"/>
     </row>
-    <row r="41" spans="1:16" ht="28.15" customHeight="1">
+    <row r="41" spans="1:16" ht="28.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="483"/>
-      <c r="B41" s="704" t="s">
+      <c r="B41" s="701" t="s">
         <v>425</v>
       </c>
-      <c r="C41" s="704"/>
-      <c r="D41" s="704"/>
-      <c r="E41" s="704"/>
-      <c r="F41" s="704"/>
-      <c r="G41" s="704"/>
-      <c r="H41" s="704"/>
-      <c r="I41" s="704"/>
-      <c r="J41" s="704"/>
-      <c r="K41" s="704"/>
-      <c r="L41" s="695" t="s">
+      <c r="C41" s="701"/>
+      <c r="D41" s="701"/>
+      <c r="E41" s="701"/>
+      <c r="F41" s="701"/>
+      <c r="G41" s="701"/>
+      <c r="H41" s="701"/>
+      <c r="I41" s="701"/>
+      <c r="J41" s="701"/>
+      <c r="K41" s="701"/>
+      <c r="L41" s="702" t="s">
         <v>426</v>
       </c>
-      <c r="M41" s="695"/>
-      <c r="N41" s="695"/>
+      <c r="M41" s="702"/>
+      <c r="N41" s="702"/>
       <c r="O41" s="483"/>
       <c r="P41"/>
     </row>
-    <row r="42" spans="1:16" ht="3" customHeight="1">
+    <row r="42" spans="1:16" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="493"/>
       <c r="B42" s="493"/>
       <c r="C42" s="493"/>
@@ -38711,7 +38711,7 @@
       <c r="O42" s="493"/>
       <c r="P42"/>
     </row>
-    <row r="43" spans="1:16" ht="6" customHeight="1">
+    <row r="43" spans="1:16" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43"/>
@@ -38729,85 +38729,85 @@
       <c r="O43"/>
       <c r="P43"/>
     </row>
-    <row r="44" spans="1:16" ht="12" customHeight="1">
+    <row r="44" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44"/>
-      <c r="B44" s="696" t="s">
+      <c r="B44" s="703" t="s">
         <v>427</v>
       </c>
-      <c r="C44" s="696"/>
-      <c r="D44" s="696"/>
-      <c r="E44" s="696" t="s">
+      <c r="C44" s="703"/>
+      <c r="D44" s="703"/>
+      <c r="E44" s="703" t="s">
         <v>428</v>
       </c>
-      <c r="F44" s="696"/>
-      <c r="G44" s="696"/>
-      <c r="H44" s="696" t="s">
+      <c r="F44" s="703"/>
+      <c r="G44" s="703"/>
+      <c r="H44" s="703" t="s">
         <v>429</v>
       </c>
-      <c r="I44" s="696"/>
-      <c r="J44" s="696"/>
-      <c r="K44" s="696" t="s">
+      <c r="I44" s="703"/>
+      <c r="J44" s="703"/>
+      <c r="K44" s="703" t="s">
         <v>430</v>
       </c>
-      <c r="L44" s="696"/>
-      <c r="M44" s="696"/>
-      <c r="N44" s="696"/>
+      <c r="L44" s="703"/>
+      <c r="M44" s="703"/>
+      <c r="N44" s="703"/>
       <c r="O44"/>
       <c r="P44"/>
     </row>
-    <row r="45" spans="1:16" ht="26.1" customHeight="1">
+    <row r="45" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45"/>
-      <c r="B45" s="697">
+      <c r="B45" s="704">
         <v>2680</v>
       </c>
-      <c r="C45" s="697"/>
-      <c r="D45" s="697"/>
-      <c r="E45" s="697">
+      <c r="C45" s="704"/>
+      <c r="D45" s="704"/>
+      <c r="E45" s="704">
         <v>1624</v>
       </c>
-      <c r="F45" s="697"/>
-      <c r="G45" s="697"/>
-      <c r="H45" s="697">
+      <c r="F45" s="704"/>
+      <c r="G45" s="704"/>
+      <c r="H45" s="704">
         <v>2770</v>
       </c>
-      <c r="I45" s="697"/>
-      <c r="J45" s="697"/>
-      <c r="K45" s="697">
+      <c r="I45" s="704"/>
+      <c r="J45" s="704"/>
+      <c r="K45" s="704">
         <v>3615</v>
       </c>
-      <c r="L45" s="697"/>
-      <c r="M45" s="697"/>
-      <c r="N45" s="697"/>
+      <c r="L45" s="704"/>
+      <c r="M45" s="704"/>
+      <c r="N45" s="704"/>
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="1:16" ht="12" customHeight="1">
+    <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46"/>
-      <c r="B46" s="698" t="s">
+      <c r="B46" s="705" t="s">
         <v>431</v>
       </c>
-      <c r="C46" s="698"/>
-      <c r="D46" s="698"/>
-      <c r="E46" s="698" t="s">
+      <c r="C46" s="705"/>
+      <c r="D46" s="705"/>
+      <c r="E46" s="705" t="s">
         <v>432</v>
       </c>
-      <c r="F46" s="698"/>
-      <c r="G46" s="698"/>
-      <c r="H46" s="698" t="s">
+      <c r="F46" s="705"/>
+      <c r="G46" s="705"/>
+      <c r="H46" s="705" t="s">
         <v>433</v>
       </c>
-      <c r="I46" s="698"/>
-      <c r="J46" s="698"/>
-      <c r="K46" s="698" t="s">
+      <c r="I46" s="705"/>
+      <c r="J46" s="705"/>
+      <c r="K46" s="705" t="s">
         <v>434</v>
       </c>
-      <c r="L46" s="698"/>
-      <c r="M46" s="698"/>
-      <c r="N46" s="698"/>
+      <c r="L46" s="705"/>
+      <c r="M46" s="705"/>
+      <c r="N46" s="705"/>
       <c r="O46"/>
       <c r="P46"/>
     </row>
-    <row r="47" spans="1:16" ht="6" customHeight="1">
+    <row r="47" spans="1:16" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47"/>
@@ -38825,15 +38825,15 @@
       <c r="O47"/>
       <c r="P47"/>
     </row>
-    <row r="48" spans="1:16" ht="20.100000000000001" customHeight="1">
+    <row r="48" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48"/>
       <c r="B48" s="494" t="s">
         <v>397</v>
       </c>
-      <c r="C48" s="694" t="s">
+      <c r="C48" s="698" t="s">
         <v>435</v>
       </c>
-      <c r="D48" s="694"/>
+      <c r="D48" s="698"/>
       <c r="E48" s="495" t="s">
         <v>13</v>
       </c>
@@ -38841,11 +38841,11 @@
         <v>436</v>
       </c>
       <c r="G48" s="483"/>
-      <c r="H48" s="700" t="s">
+      <c r="H48" s="711" t="s">
         <v>400</v>
       </c>
-      <c r="I48" s="694"/>
-      <c r="J48" s="694"/>
+      <c r="I48" s="698"/>
+      <c r="J48" s="698"/>
       <c r="K48" s="496" t="s">
         <v>13</v>
       </c>
@@ -38855,25 +38855,25 @@
       <c r="O48"/>
       <c r="P48"/>
     </row>
-    <row r="49" spans="1:16" ht="18" customHeight="1">
+    <row r="49" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49"/>
       <c r="B49" s="497">
         <v>0</v>
       </c>
-      <c r="C49" s="705" t="s">
+      <c r="C49" s="699" t="s">
         <v>437</v>
       </c>
-      <c r="D49" s="705"/>
+      <c r="D49" s="699"/>
       <c r="E49" s="498">
         <v>2680</v>
       </c>
       <c r="F49" s="499"/>
       <c r="G49" s="484"/>
-      <c r="H49" s="706" t="s">
+      <c r="H49" s="707" t="s">
         <v>415</v>
       </c>
-      <c r="I49" s="705"/>
-      <c r="J49" s="705"/>
+      <c r="I49" s="699"/>
+      <c r="J49" s="699"/>
       <c r="K49" s="500">
         <v>2770</v>
       </c>
@@ -38883,15 +38883,15 @@
       <c r="O49"/>
       <c r="P49"/>
     </row>
-    <row r="50" spans="1:16" ht="18" customHeight="1">
+    <row r="50" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50"/>
       <c r="B50" s="501">
         <v>1</v>
       </c>
-      <c r="C50" s="707" t="s">
+      <c r="C50" s="700" t="s">
         <v>438</v>
       </c>
-      <c r="D50" s="707"/>
+      <c r="D50" s="700"/>
       <c r="E50" s="502">
         <v>634</v>
       </c>
@@ -38900,11 +38900,11 @@
         <v>0.23656716417910448</v>
       </c>
       <c r="G50" s="484"/>
-      <c r="H50" s="708" t="s">
+      <c r="H50" s="712" t="s">
         <v>439</v>
       </c>
-      <c r="I50" s="707"/>
-      <c r="J50" s="707"/>
+      <c r="I50" s="700"/>
+      <c r="J50" s="700"/>
       <c r="K50" s="504">
         <v>845</v>
       </c>
@@ -38914,15 +38914,15 @@
       <c r="O50"/>
       <c r="P50"/>
     </row>
-    <row r="51" spans="1:16" ht="18" customHeight="1">
+    <row r="51" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51"/>
       <c r="B51" s="505">
         <v>2</v>
       </c>
-      <c r="C51" s="709" t="s">
+      <c r="C51" s="697" t="s">
         <v>406</v>
       </c>
-      <c r="D51" s="709"/>
+      <c r="D51" s="697"/>
       <c r="E51" s="506">
         <v>777</v>
       </c>
@@ -38931,9 +38931,9 @@
         <v>0.28992537313432837</v>
       </c>
       <c r="G51" s="484"/>
-      <c r="H51" s="710"/>
-      <c r="I51" s="711"/>
-      <c r="J51" s="711"/>
+      <c r="H51" s="713"/>
+      <c r="I51" s="714"/>
+      <c r="J51" s="714"/>
       <c r="K51" s="508"/>
       <c r="L51"/>
       <c r="M51"/>
@@ -38941,15 +38941,15 @@
       <c r="O51"/>
       <c r="P51"/>
     </row>
-    <row r="52" spans="1:16" ht="18" customHeight="1">
+    <row r="52" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52"/>
       <c r="B52" s="501">
         <v>3</v>
       </c>
-      <c r="C52" s="707" t="s">
+      <c r="C52" s="700" t="s">
         <v>408</v>
       </c>
-      <c r="D52" s="707"/>
+      <c r="D52" s="700"/>
       <c r="E52" s="509">
         <v>0</v>
       </c>
@@ -38958,9 +38958,9 @@
         <v>0</v>
       </c>
       <c r="G52" s="484"/>
-      <c r="H52" s="710"/>
-      <c r="I52" s="711"/>
-      <c r="J52" s="711"/>
+      <c r="H52" s="713"/>
+      <c r="I52" s="714"/>
+      <c r="J52" s="714"/>
       <c r="K52" s="510"/>
       <c r="L52"/>
       <c r="M52"/>
@@ -38968,15 +38968,15 @@
       <c r="O52"/>
       <c r="P52"/>
     </row>
-    <row r="53" spans="1:16" ht="18" customHeight="1">
+    <row r="53" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53"/>
       <c r="B53" s="505">
         <v>4</v>
       </c>
-      <c r="C53" s="709" t="s">
+      <c r="C53" s="697" t="s">
         <v>410</v>
       </c>
-      <c r="D53" s="709"/>
+      <c r="D53" s="697"/>
       <c r="E53" s="506">
         <v>847</v>
       </c>
@@ -38985,9 +38985,9 @@
         <v>0.31604477611940296</v>
       </c>
       <c r="G53" s="484"/>
-      <c r="H53" s="710"/>
-      <c r="I53" s="711"/>
-      <c r="J53" s="711"/>
+      <c r="H53" s="713"/>
+      <c r="I53" s="714"/>
+      <c r="J53" s="714"/>
       <c r="K53" s="508"/>
       <c r="L53"/>
       <c r="M53"/>
@@ -38995,13 +38995,13 @@
       <c r="O53"/>
       <c r="P53"/>
     </row>
-    <row r="54" spans="1:16" ht="18" customHeight="1">
+    <row r="54" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54"/>
       <c r="B54" s="511"/>
-      <c r="C54" s="712" t="s">
+      <c r="C54" s="710" t="s">
         <v>440</v>
       </c>
-      <c r="D54" s="712"/>
+      <c r="D54" s="710"/>
       <c r="E54" s="512">
         <f>SUM(E50:E53)</f>
         <v>2258</v>
@@ -39011,11 +39011,11 @@
         <v>0.84253731343283578</v>
       </c>
       <c r="G54" s="484"/>
-      <c r="H54" s="713" t="s">
+      <c r="H54" s="715" t="s">
         <v>284</v>
       </c>
-      <c r="I54" s="712"/>
-      <c r="J54" s="712"/>
+      <c r="I54" s="710"/>
+      <c r="J54" s="710"/>
       <c r="K54" s="514">
         <f>K49+K50</f>
         <v>3615</v>
@@ -39026,7 +39026,7 @@
       <c r="O54"/>
       <c r="P54"/>
     </row>
-    <row r="55" spans="1:16" ht="18" customHeight="1">
+    <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55"/>
@@ -39044,7 +39044,7 @@
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" ht="18" customHeight="1">
+    <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56"/>
@@ -39062,7 +39062,7 @@
       <c r="O56"/>
       <c r="P56"/>
     </row>
-    <row r="57" spans="1:16" ht="20.100000000000001" customHeight="1">
+    <row r="57" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57"/>
@@ -39080,7 +39080,7 @@
       <c r="O57"/>
       <c r="P57"/>
     </row>
-    <row r="58" spans="1:16" ht="6" customHeight="1">
+    <row r="58" spans="1:16" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58"/>
@@ -39098,47 +39098,47 @@
       <c r="O58"/>
       <c r="P58"/>
     </row>
-    <row r="59" spans="1:16" ht="14.1" customHeight="1">
+    <row r="59" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59"/>
-      <c r="B59" s="714" t="s">
+      <c r="B59" s="708" t="s">
         <v>441</v>
       </c>
-      <c r="C59" s="714"/>
-      <c r="D59" s="714"/>
-      <c r="E59" s="714"/>
-      <c r="F59" s="714"/>
-      <c r="G59" s="714"/>
-      <c r="H59" s="714"/>
-      <c r="I59" s="714"/>
-      <c r="J59" s="714"/>
-      <c r="K59" s="714"/>
-      <c r="L59" s="714"/>
-      <c r="M59" s="714"/>
-      <c r="N59" s="714"/>
+      <c r="C59" s="708"/>
+      <c r="D59" s="708"/>
+      <c r="E59" s="708"/>
+      <c r="F59" s="708"/>
+      <c r="G59" s="708"/>
+      <c r="H59" s="708"/>
+      <c r="I59" s="708"/>
+      <c r="J59" s="708"/>
+      <c r="K59" s="708"/>
+      <c r="L59" s="708"/>
+      <c r="M59" s="708"/>
+      <c r="N59" s="708"/>
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="14.1" customHeight="1">
+    <row r="60" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60"/>
-      <c r="B60" s="714" t="s">
+      <c r="B60" s="708" t="s">
         <v>442</v>
       </c>
-      <c r="C60" s="714"/>
-      <c r="D60" s="714"/>
-      <c r="E60" s="714"/>
-      <c r="F60" s="714"/>
-      <c r="G60" s="714"/>
-      <c r="H60" s="714"/>
-      <c r="I60" s="714"/>
-      <c r="J60" s="714"/>
-      <c r="K60" s="714"/>
-      <c r="L60" s="714"/>
-      <c r="M60" s="714"/>
-      <c r="N60" s="714"/>
+      <c r="C60" s="708"/>
+      <c r="D60" s="708"/>
+      <c r="E60" s="708"/>
+      <c r="F60" s="708"/>
+      <c r="G60" s="708"/>
+      <c r="H60" s="708"/>
+      <c r="I60" s="708"/>
+      <c r="J60" s="708"/>
+      <c r="K60" s="708"/>
+      <c r="L60" s="708"/>
+      <c r="M60" s="708"/>
+      <c r="N60" s="708"/>
       <c r="O60"/>
       <c r="P60"/>
     </row>
-    <row r="61" spans="1:16" ht="14.1" customHeight="1">
+    <row r="61" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61"/>
@@ -39156,7 +39156,7 @@
       <c r="O61"/>
       <c r="P61"/>
     </row>
-    <row r="62" spans="1:16" ht="3" customHeight="1">
+    <row r="62" spans="1:16" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="515"/>
       <c r="B62" s="515"/>
       <c r="C62" s="515"/>
@@ -39174,29 +39174,29 @@
       <c r="O62" s="515"/>
       <c r="P62"/>
     </row>
-    <row r="63" spans="1:16" ht="14.1" customHeight="1">
+    <row r="63" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63"/>
-      <c r="B63" s="715" t="s">
+      <c r="B63" s="706" t="s">
         <v>443</v>
       </c>
-      <c r="C63" s="715"/>
-      <c r="D63" s="715"/>
-      <c r="E63" s="715"/>
-      <c r="F63" s="715"/>
+      <c r="C63" s="706"/>
+      <c r="D63" s="706"/>
+      <c r="E63" s="706"/>
+      <c r="F63" s="706"/>
       <c r="G63"/>
       <c r="H63"/>
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
       <c r="L63"/>
-      <c r="M63" s="699" t="s">
+      <c r="M63" s="709" t="s">
         <v>444</v>
       </c>
-      <c r="N63" s="699"/>
+      <c r="N63" s="709"/>
       <c r="O63"/>
       <c r="P63"/>
     </row>
-    <row r="64" spans="1:16" ht="14.1" customHeight="1">
+    <row r="64" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64"/>
       <c r="B64"/>
       <c r="C64"/>
@@ -39214,7 +39214,7 @@
       <c r="O64"/>
       <c r="P64"/>
     </row>
-    <row r="65" spans="1:16" ht="14.1" customHeight="1">
+    <row r="65" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65"/>
       <c r="B65"/>
       <c r="C65"/>
@@ -39232,7 +39232,7 @@
       <c r="O65"/>
       <c r="P65"/>
     </row>
-    <row r="66" spans="1:16" ht="4.1500000000000004" customHeight="1">
+    <row r="66" spans="1:16" ht="4.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66"/>
       <c r="B66"/>
       <c r="C66"/>
@@ -39250,7 +39250,7 @@
       <c r="O66"/>
       <c r="P66"/>
     </row>
-    <row r="67" spans="1:16" ht="16.149999999999999" customHeight="1">
+    <row r="67" spans="1:16" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67"/>
       <c r="B67"/>
       <c r="C67"/>
@@ -39268,7 +39268,7 @@
       <c r="O67"/>
       <c r="P67"/>
     </row>
-    <row r="68" spans="1:16" ht="6" customHeight="1">
+    <row r="68" spans="1:16" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68"/>
       <c r="B68"/>
       <c r="C68"/>
@@ -39331,25 +39331,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{149CF139-FCE1-436D-AC40-3B36FE214488}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="B2:K71"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="49.140625" customWidth="1"/>
+    <col min="5" max="5" width="49.1640625" customWidth="1"/>
     <col min="6" max="6" width="94" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.85546875" customWidth="1"/>
+    <col min="13" max="13" width="4.83203125" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="50.140625" customWidth="1"/>
-    <col min="16" max="16" width="16.140625" customWidth="1"/>
+    <col min="15" max="15" width="50.1640625" customWidth="1"/>
+    <col min="16" max="16" width="16.1640625" customWidth="1"/>
     <col min="17" max="17" width="41" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="15" thickBot="1"/>
-    <row r="3" spans="2:9" ht="15" thickBot="1">
+    <row r="2" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>41</v>
       </c>
@@ -39372,7 +39372,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B4" s="5">
         <v>1</v>
       </c>
@@ -39393,7 +39393,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B5" s="7">
         <v>2</v>
       </c>
@@ -39410,7 +39410,7 @@
       <c r="G5" s="92"/>
       <c r="H5" s="88"/>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="7">
         <v>3</v>
       </c>
@@ -39427,7 +39427,7 @@
       <c r="G6" s="92"/>
       <c r="H6" s="88"/>
     </row>
-    <row r="7" spans="2:9">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B7" s="7">
         <v>4</v>
       </c>
@@ -39444,7 +39444,7 @@
       <c r="G7" s="92"/>
       <c r="H7" s="88"/>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B8" s="7">
         <v>5</v>
       </c>
@@ -39461,7 +39461,7 @@
       <c r="G8" s="92"/>
       <c r="H8" s="88"/>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="7">
         <v>6</v>
       </c>
@@ -39478,7 +39478,7 @@
       <c r="G9" s="92"/>
       <c r="H9" s="88"/>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="7">
         <v>7</v>
       </c>
@@ -39495,7 +39495,7 @@
       <c r="G10" s="92"/>
       <c r="H10" s="88"/>
     </row>
-    <row r="11" spans="2:9" ht="15" thickBot="1">
+    <row r="11" spans="2:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="7">
         <v>8</v>
       </c>
@@ -39512,7 +39512,7 @@
       <c r="G11" s="92"/>
       <c r="H11" s="88"/>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B12" s="7">
         <v>9</v>
       </c>
@@ -39533,7 +39533,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B13" s="7">
         <v>10</v>
       </c>
@@ -39550,7 +39550,7 @@
       <c r="G13" s="92"/>
       <c r="H13" s="88"/>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B14" s="7">
         <v>11</v>
       </c>
@@ -39567,7 +39567,7 @@
       <c r="G14" s="92"/>
       <c r="H14" s="88"/>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B15" s="7">
         <v>12</v>
       </c>
@@ -39584,7 +39584,7 @@
       <c r="G15" s="92"/>
       <c r="H15" s="88"/>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B16" s="7">
         <v>13</v>
       </c>
@@ -39601,7 +39601,7 @@
       <c r="G16" s="92"/>
       <c r="H16" s="88"/>
     </row>
-    <row r="17" spans="2:11" ht="15" thickBot="1">
+    <row r="17" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="7">
         <v>14</v>
       </c>
@@ -39618,7 +39618,7 @@
       <c r="G17" s="93"/>
       <c r="H17" s="90"/>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="7">
         <v>15</v>
       </c>
@@ -39639,7 +39639,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="7">
         <v>16</v>
       </c>
@@ -39656,7 +39656,7 @@
       <c r="G19" s="92"/>
       <c r="H19" s="88"/>
     </row>
-    <row r="20" spans="2:11" ht="15" thickBot="1">
+    <row r="20" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="7">
         <v>17</v>
       </c>
@@ -39673,7 +39673,7 @@
       <c r="G20" s="92"/>
       <c r="H20" s="88"/>
     </row>
-    <row r="21" spans="2:11">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="7">
         <v>18</v>
       </c>
@@ -39706,7 +39706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:11">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="7">
         <v>19</v>
       </c>
@@ -39732,7 +39732,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="2:11">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="58">
         <v>20</v>
       </c>
@@ -39755,7 +39755,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="15" thickBot="1">
+    <row r="24" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="58">
         <v>21</v>
       </c>
@@ -39778,7 +39778,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="2:11">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="7">
         <v>22</v>
       </c>
@@ -39805,7 +39805,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="26" spans="2:11">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="7">
         <v>23</v>
       </c>
@@ -39828,7 +39828,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="2:11">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="7">
         <v>24</v>
       </c>
@@ -39851,7 +39851,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="2:11">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="7">
         <v>25</v>
       </c>
@@ -39874,7 +39874,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="2:11">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="7">
         <v>26</v>
       </c>
@@ -39897,7 +39897,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="2:11">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="7">
         <v>27</v>
       </c>
@@ -39920,7 +39920,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="15" thickBot="1">
+    <row r="31" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B31" s="7">
         <v>28</v>
       </c>
@@ -39947,7 +39947,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="7">
         <v>29</v>
       </c>
@@ -39970,7 +39970,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="7">
         <v>30</v>
       </c>
@@ -39993,7 +39993,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="7">
         <v>31</v>
       </c>
@@ -40016,7 +40016,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="7">
         <v>32</v>
       </c>
@@ -40039,7 +40039,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="7">
         <v>33</v>
       </c>
@@ -40060,7 +40060,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="7">
         <v>34</v>
       </c>
@@ -40081,7 +40081,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="2:8" ht="15" thickBot="1">
+    <row r="38" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B38" s="15">
         <v>35</v>
       </c>
@@ -40102,7 +40102,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="2:8" ht="15" thickBot="1">
+    <row r="39" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C39" s="68" t="s">
         <v>94</v>
       </c>
@@ -40117,10 +40117,10 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" thickBot="1">
+    <row r="40" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="H40" s="19"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C41" s="21" t="s">
         <v>66</v>
       </c>
@@ -40137,7 +40137,7 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C42" s="26" t="s">
         <v>66</v>
       </c>
@@ -40154,7 +40154,7 @@
         <v>45000</v>
       </c>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C43" s="26" t="s">
         <v>66</v>
       </c>
@@ -40169,7 +40169,7 @@
         <v>1600000</v>
       </c>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C44" s="26" t="s">
         <v>66</v>
       </c>
@@ -40186,7 +40186,7 @@
         <v>240000</v>
       </c>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C45" s="26" t="s">
         <v>66</v>
       </c>
@@ -40203,7 +40203,7 @@
         <v>220000</v>
       </c>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C46" s="26" t="s">
         <v>66</v>
       </c>
@@ -40220,7 +40220,7 @@
         <v>180000</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="15" thickBot="1">
+    <row r="47" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C47" s="28" t="s">
         <v>66</v>
       </c>
@@ -40235,7 +40235,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C48" s="33" t="s">
         <v>64</v>
       </c>
@@ -40250,7 +40250,7 @@
         <v>425000</v>
       </c>
     </row>
-    <row r="49" spans="3:7">
+    <row r="49" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C49" s="26" t="s">
         <v>64</v>
       </c>
@@ -40267,7 +40267,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="50" spans="3:7">
+    <row r="50" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C50" s="26" t="s">
         <v>64</v>
       </c>
@@ -40282,7 +40282,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="51" spans="3:7">
+    <row r="51" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C51" s="26" t="s">
         <v>64</v>
       </c>
@@ -40299,7 +40299,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="52" spans="3:7">
+    <row r="52" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C52" s="26" t="s">
         <v>64</v>
       </c>
@@ -40316,7 +40316,7 @@
         <v>340000</v>
       </c>
     </row>
-    <row r="53" spans="3:7">
+    <row r="53" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C53" s="26" t="s">
         <v>64</v>
       </c>
@@ -40331,7 +40331,7 @@
         <v>334000</v>
       </c>
     </row>
-    <row r="54" spans="3:7">
+    <row r="54" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C54" s="26" t="s">
         <v>64</v>
       </c>
@@ -40346,7 +40346,7 @@
         <v>160000</v>
       </c>
     </row>
-    <row r="55" spans="3:7">
+    <row r="55" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C55" s="26" t="s">
         <v>64</v>
       </c>
@@ -40363,7 +40363,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="56" spans="3:7" ht="15" thickBot="1">
+    <row r="56" spans="3:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C56" s="28" t="s">
         <v>64</v>
       </c>
@@ -40380,7 +40380,7 @@
         <v>566000</v>
       </c>
     </row>
-    <row r="57" spans="3:7">
+    <row r="57" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C57" s="21" t="s">
         <v>62</v>
       </c>
@@ -40397,7 +40397,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="58" spans="3:7">
+    <row r="58" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C58" s="26" t="s">
         <v>62</v>
       </c>
@@ -40414,7 +40414,7 @@
         <v>1100000</v>
       </c>
     </row>
-    <row r="59" spans="3:7">
+    <row r="59" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C59" s="26" t="s">
         <v>62</v>
       </c>
@@ -40431,7 +40431,7 @@
         <v>66000</v>
       </c>
     </row>
-    <row r="60" spans="3:7" ht="15" thickBot="1">
+    <row r="60" spans="3:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C60" s="28" t="s">
         <v>62</v>
       </c>
@@ -40448,7 +40448,7 @@
         <v>250000</v>
       </c>
     </row>
-    <row r="61" spans="3:7">
+    <row r="61" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C61" s="26" t="s">
         <v>60</v>
       </c>
@@ -40465,7 +40465,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="62" spans="3:7">
+    <row r="62" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C62" s="26" t="s">
         <v>60</v>
       </c>
@@ -40482,7 +40482,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="63" spans="3:7" ht="15" thickBot="1">
+    <row r="63" spans="3:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C63" s="26" t="s">
         <v>60</v>
       </c>
@@ -40499,7 +40499,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="3:7">
+    <row r="64" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C64" s="21" t="s">
         <v>49</v>
       </c>
@@ -40516,7 +40516,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="65" spans="3:7">
+    <row r="65" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C65" s="26" t="s">
         <v>49</v>
       </c>
@@ -40533,7 +40533,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="66" spans="3:7">
+    <row r="66" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C66" s="26" t="s">
         <v>49</v>
       </c>
@@ -40550,7 +40550,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="67" spans="3:7">
+    <row r="67" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C67" s="26" t="s">
         <v>49</v>
       </c>
@@ -40567,7 +40567,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="68" spans="3:7">
+    <row r="68" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C68" s="26" t="s">
         <v>49</v>
       </c>
@@ -40584,7 +40584,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="69" spans="3:7">
+    <row r="69" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C69" s="26" t="s">
         <v>49</v>
       </c>
@@ -40601,7 +40601,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="70" spans="3:7">
+    <row r="70" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C70" s="26" t="s">
         <v>49</v>
       </c>
@@ -40618,7 +40618,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="71" spans="3:7" ht="15" thickBot="1">
+    <row r="71" spans="3:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C71" s="28" t="s">
         <v>49</v>
       </c>
@@ -40644,19 +40644,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1398C9E4-6DF0-4C3C-A84E-6325BD1743DE}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="B2:O21"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="48"/>
-    <col min="2" max="2" width="2.85546875" style="48" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.140625" style="48" customWidth="1"/>
-    <col min="8" max="13" width="11.5703125" style="48"/>
-    <col min="14" max="14" width="14.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.5703125" style="48"/>
+    <col min="1" max="1" width="11.5" style="48"/>
+    <col min="2" max="2" width="2.83203125" style="48" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.1640625" style="48" customWidth="1"/>
+    <col min="8" max="13" width="11.5" style="48"/>
+    <col min="14" max="14" width="14.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.5" style="48"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15">
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
@@ -40697,11 +40697,11 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B3" s="589">
+    <row r="3" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="562">
         <v>1</v>
       </c>
-      <c r="C3" s="572" t="s">
+      <c r="C3" s="545" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="42" t="s">
@@ -40726,14 +40726,14 @@
         <f>+SUM(H3:J3)</f>
         <v>42</v>
       </c>
-      <c r="L3" s="590">
+      <c r="L3" s="563">
         <f>+K4/K3</f>
         <v>236.3095238095238</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B4" s="589"/>
-      <c r="C4" s="572"/>
+    <row r="4" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="562"/>
+      <c r="C4" s="545"/>
       <c r="D4" s="42" t="s">
         <v>13</v>
       </c>
@@ -40756,13 +40756,13 @@
         <f t="shared" ref="K4:K15" si="0">+SUM(H4:J4)</f>
         <v>9925</v>
       </c>
-      <c r="L4" s="591"/>
+      <c r="L4" s="564"/>
     </row>
-    <row r="5" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B5" s="589">
+    <row r="5" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="562">
         <v>2</v>
       </c>
-      <c r="C5" s="572" t="s">
+      <c r="C5" s="545" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="42" t="s">
@@ -40784,14 +40784,14 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="L5" s="590">
+      <c r="L5" s="563">
         <f>+K6/K5</f>
         <v>181.66666666666666</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B6" s="589"/>
-      <c r="C6" s="572"/>
+    <row r="6" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="562"/>
+      <c r="C6" s="545"/>
       <c r="D6" s="42" t="s">
         <v>13</v>
       </c>
@@ -40811,13 +40811,13 @@
         <f t="shared" si="0"/>
         <v>3270</v>
       </c>
-      <c r="L6" s="591"/>
+      <c r="L6" s="564"/>
     </row>
-    <row r="7" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B7" s="589">
+    <row r="7" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="562">
         <v>3</v>
       </c>
-      <c r="C7" s="572" t="s">
+      <c r="C7" s="545" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="42" t="s">
@@ -40839,14 +40839,14 @@
         <f>+SUM(H7:J7)</f>
         <v>15</v>
       </c>
-      <c r="L7" s="590">
+      <c r="L7" s="563">
         <f>+K8/K7</f>
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B8" s="589"/>
-      <c r="C8" s="572"/>
+    <row r="8" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="562"/>
+      <c r="C8" s="545"/>
       <c r="D8" s="42" t="s">
         <v>13</v>
       </c>
@@ -40866,11 +40866,11 @@
         <f t="shared" si="0"/>
         <v>2895</v>
       </c>
-      <c r="L8" s="573"/>
+      <c r="L8" s="546"/>
     </row>
-    <row r="9" spans="2:15" ht="16.350000000000001" hidden="1" customHeight="1">
-      <c r="B9" s="589"/>
-      <c r="C9" s="572"/>
+    <row r="9" spans="2:15" ht="16.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="562"/>
+      <c r="C9" s="545"/>
       <c r="D9" s="51" t="s">
         <v>21</v>
       </c>
@@ -40890,13 +40890,13 @@
         <f>+SUM(H9:J9)</f>
         <v>8</v>
       </c>
-      <c r="L9" s="591"/>
+      <c r="L9" s="564"/>
     </row>
-    <row r="10" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B10" s="589">
+    <row r="10" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="562">
         <v>4</v>
       </c>
-      <c r="C10" s="572" t="s">
+      <c r="C10" s="545" t="s">
         <v>22</v>
       </c>
       <c r="D10" s="42" t="s">
@@ -40918,14 +40918,14 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="L10" s="590">
+      <c r="L10" s="563">
         <f>+K11/K10</f>
         <v>31.950819672131146</v>
       </c>
     </row>
-    <row r="11" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B11" s="589"/>
-      <c r="C11" s="572"/>
+    <row r="11" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="562"/>
+      <c r="C11" s="545"/>
       <c r="D11" s="42" t="s">
         <v>13</v>
       </c>
@@ -40945,13 +40945,13 @@
         <f t="shared" si="0"/>
         <v>1949</v>
       </c>
-      <c r="L11" s="591"/>
+      <c r="L11" s="564"/>
     </row>
-    <row r="12" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B12" s="589">
+    <row r="12" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="562">
         <v>5</v>
       </c>
-      <c r="C12" s="572" t="s">
+      <c r="C12" s="545" t="s">
         <v>174</v>
       </c>
       <c r="D12" s="42" t="s">
@@ -40973,7 +40973,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="L12" s="590">
+      <c r="L12" s="563">
         <f>+K13/K12</f>
         <v>34.384615384615387</v>
       </c>
@@ -40986,9 +40986,9 @@
         <v>9902.7692307692305</v>
       </c>
     </row>
-    <row r="13" spans="2:15" ht="16.350000000000001" customHeight="1">
-      <c r="B13" s="589"/>
-      <c r="C13" s="572"/>
+    <row r="13" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="562"/>
+      <c r="C13" s="545"/>
       <c r="D13" s="42" t="s">
         <v>13</v>
       </c>
@@ -41009,7 +41009,7 @@
         <f t="shared" si="0"/>
         <v>1788</v>
       </c>
-      <c r="L13" s="591"/>
+      <c r="L13" s="564"/>
       <c r="N13" s="53" t="s">
         <v>175</v>
       </c>
@@ -41017,7 +41017,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="16.350000000000001" customHeight="1">
+    <row r="14" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="46">
         <v>6</v>
       </c>
@@ -41048,7 +41048,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="16.350000000000001" customHeight="1">
+    <row r="15" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="46">
         <v>7</v>
       </c>
@@ -41079,7 +41079,7 @@
         <v>698.66666666666663</v>
       </c>
     </row>
-    <row r="16" spans="2:15" ht="16.350000000000001" customHeight="1">
+    <row r="16" spans="2:15" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="46">
         <v>8</v>
       </c>
@@ -41112,7 +41112,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="16.350000000000001" customHeight="1">
+    <row r="17" spans="2:12" ht="16.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="46">
         <v>9</v>
       </c>
@@ -41142,13 +41142,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
       <c r="G20" s="53"/>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D21" s="53"/>
       <c r="E21" s="53"/>
       <c r="F21" s="53"/>
@@ -41180,54 +41180,54 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C77A829-0E62-4C8A-BC78-7619E4137AEF}">
   <sheetPr codeName="Hoja4"/>
   <dimension ref="B1:CC38"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.9" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="14" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="48"/>
-    <col min="2" max="2" width="6.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5" style="48"/>
+    <col min="2" max="2" width="6.83203125" style="48" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" style="48" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="48" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="6.42578125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="7.140625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="6.140625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="6.42578125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="26.5" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="48" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="6.5" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="7.1640625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="6.1640625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="6.5" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="6" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="5.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="12.5703125" style="48" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="17" width="8.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="22" width="9.140625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="5.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="12.5" style="48" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="17" width="8.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="22" width="9.1640625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="25" max="27" width="9" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="33" width="11.140625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="34" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="35" max="38" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="40" max="43" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="44" max="44" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="45" max="49" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="50" max="50" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="51" max="54" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="55" max="55" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="56" max="59" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="60" max="60" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="61" max="64" width="10.85546875" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="65" max="65" width="10.85546875" style="48" customWidth="1" collapsed="1"/>
-    <col min="66" max="66" width="8.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="10.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="33" width="11.1640625" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="34" max="34" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="35" max="38" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="39" max="39" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="40" max="43" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="45" max="49" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="50" max="50" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="51" max="54" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="55" max="55" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="56" max="59" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="60" max="60" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="61" max="64" width="10.83203125" style="48" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="65" max="65" width="10.83203125" style="48" customWidth="1" collapsed="1"/>
+    <col min="66" max="66" width="8.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="10.1640625" style="48" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="11" style="48" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="11.5703125" style="48"/>
-    <col min="70" max="70" width="13.85546875" style="48" bestFit="1" customWidth="1"/>
-    <col min="71" max="16384" width="11.5703125" style="48"/>
+    <col min="69" max="69" width="11.5" style="48"/>
+    <col min="70" max="70" width="13.83203125" style="48" bestFit="1" customWidth="1"/>
+    <col min="71" max="16384" width="11.5" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:74" ht="14.45" thickBot="1"/>
-    <row r="2" spans="2:74" ht="14.45" thickBot="1">
+    <row r="1" spans="2:74" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:74" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="155" t="s">
         <v>178</v>
       </c>
@@ -41433,14 +41433,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:74" ht="18" customHeight="1">
-      <c r="B3" s="606" t="s">
+    <row r="3" spans="2:74" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="579" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="576">
+      <c r="C3" s="549">
         <v>1</v>
       </c>
-      <c r="D3" s="602" t="s">
+      <c r="D3" s="575" t="s">
         <v>220</v>
       </c>
       <c r="E3" s="105" t="s">
@@ -41470,7 +41470,7 @@
         <f>+SUM(I3:K3)</f>
         <v>42</v>
       </c>
-      <c r="M3" s="569">
+      <c r="M3" s="542">
         <f>+L4/L3</f>
         <v>236.3095238095238</v>
       </c>
@@ -41601,46 +41601,46 @@
       <c r="BA3" s="106">
         <v>5</v>
       </c>
-      <c r="BB3" s="701">
+      <c r="BB3" s="536">
         <v>1</v>
       </c>
       <c r="BC3" s="107">
         <f>+AY3+AZ3+BA3+BB3</f>
         <v>12</v>
       </c>
-      <c r="BD3" s="701">
+      <c r="BD3" s="536">
         <v>2</v>
       </c>
-      <c r="BE3" s="701">
+      <c r="BE3" s="536">
         <v>5</v>
       </c>
-      <c r="BF3" s="701">
+      <c r="BF3" s="536">
         <v>2</v>
       </c>
-      <c r="BG3" s="701">
+      <c r="BG3" s="536">
         <v>1</v>
       </c>
       <c r="BH3" s="107">
         <f>+BD3+BE3+BF3+BG3</f>
         <v>10</v>
       </c>
-      <c r="BI3" s="701">
-        <v>0</v>
-      </c>
-      <c r="BJ3" s="701">
+      <c r="BI3" s="536">
+        <v>0</v>
+      </c>
+      <c r="BJ3" s="536">
         <v>4</v>
       </c>
-      <c r="BK3" s="701">
+      <c r="BK3" s="536">
         <v>2</v>
       </c>
-      <c r="BL3" s="701">
+      <c r="BL3" s="536">
         <v>2</v>
       </c>
       <c r="BM3" s="107">
         <f>+BI3+BJ3+BK3+BL3</f>
         <v>8</v>
       </c>
-      <c r="BN3" s="582">
+      <c r="BN3" s="555">
         <f>+IFERROR(BM4/BM3,0)</f>
         <v>416.25</v>
       </c>
@@ -41648,7 +41648,7 @@
         <f>+R3+W3+AB3+AH3+AM3+AR3+AX3+BC3+BH3+BM3</f>
         <v>126</v>
       </c>
-      <c r="BP3" s="582">
+      <c r="BP3" s="555">
         <f>+BO4/BO3</f>
         <v>280.65873015873018</v>
       </c>
@@ -41657,10 +41657,10 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="2:74" ht="18" customHeight="1" thickBot="1">
-      <c r="B4" s="607"/>
-      <c r="C4" s="577"/>
-      <c r="D4" s="603"/>
+    <row r="4" spans="2:74" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="580"/>
+      <c r="C4" s="550"/>
+      <c r="D4" s="576"/>
       <c r="E4" s="108" t="s">
         <v>13</v>
       </c>
@@ -41689,7 +41689,7 @@
         <f t="shared" ref="L4:L24" si="1">+SUM(I4:K4)</f>
         <v>9925</v>
       </c>
-      <c r="M4" s="570"/>
+      <c r="M4" s="543"/>
       <c r="N4" s="109">
         <v>200</v>
       </c>
@@ -41821,41 +41821,41 @@
       <c r="BA4" s="109">
         <v>975</v>
       </c>
-      <c r="BB4" s="702">
+      <c r="BB4" s="537">
         <v>52</v>
       </c>
       <c r="BC4" s="110">
         <f t="shared" ref="BC4:BC18" si="2">+AY4+AZ4+BA4+BB4</f>
         <v>1789</v>
       </c>
-      <c r="BD4" s="702">
+      <c r="BD4" s="537">
         <f>380+84</f>
         <v>464</v>
       </c>
-      <c r="BE4" s="702">
+      <c r="BE4" s="537">
         <v>637</v>
       </c>
-      <c r="BF4" s="702">
+      <c r="BF4" s="537">
         <f>590-226</f>
         <v>364</v>
       </c>
-      <c r="BG4" s="702">
+      <c r="BG4" s="537">
         <v>100</v>
       </c>
       <c r="BH4" s="110">
         <f>+BD4+BE4+BF4+BG4</f>
         <v>1565</v>
       </c>
-      <c r="BI4" s="702">
-        <v>0</v>
-      </c>
-      <c r="BJ4" s="702">
+      <c r="BI4" s="537">
+        <v>0</v>
+      </c>
+      <c r="BJ4" s="537">
         <v>665</v>
       </c>
-      <c r="BK4" s="702">
+      <c r="BK4" s="537">
         <v>2365</v>
       </c>
-      <c r="BL4" s="702">
+      <c r="BL4" s="537">
         <f>125+175</f>
         <v>300</v>
       </c>
@@ -41863,12 +41863,12 @@
         <f>+BI4+BJ4+BK4+BL4</f>
         <v>3330</v>
       </c>
-      <c r="BN4" s="583"/>
+      <c r="BN4" s="556"/>
       <c r="BO4" s="193">
         <f>+R4+W4+AB4+AH4+AM4+AR4+AX4+BC4+BH4+BM4</f>
         <v>35363</v>
       </c>
-      <c r="BP4" s="583"/>
+      <c r="BP4" s="556"/>
       <c r="BQ4" s="61">
         <f>+AVERAGE(R4,W4,AB4,AH4,AM4,AR4,AX4,BC4,BH4,BM4)</f>
         <v>3536.3</v>
@@ -41881,14 +41881,14 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="5" spans="2:74" ht="18" customHeight="1">
-      <c r="B5" s="608" t="s">
+    <row r="5" spans="2:74" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="581" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="604">
+      <c r="C5" s="577">
         <v>2</v>
       </c>
-      <c r="D5" s="605" t="s">
+      <c r="D5" s="578" t="s">
         <v>221</v>
       </c>
       <c r="E5" s="101" t="s">
@@ -41916,7 +41916,7 @@
         <f>+SUM(I5:K5)</f>
         <v>18</v>
       </c>
-      <c r="M5" s="573">
+      <c r="M5" s="546">
         <f>+L6/L5</f>
         <v>181.66666666666666</v>
       </c>
@@ -42045,46 +42045,46 @@
       <c r="BA5" s="102">
         <v>3</v>
       </c>
-      <c r="BB5" s="701">
+      <c r="BB5" s="536">
         <v>2</v>
       </c>
       <c r="BC5" s="104">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="BD5" s="701">
-        <v>0</v>
-      </c>
-      <c r="BE5" s="701">
+      <c r="BD5" s="536">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="536">
         <v>3</v>
       </c>
-      <c r="BF5" s="701">
-        <v>0</v>
-      </c>
-      <c r="BG5" s="701">
+      <c r="BF5" s="536">
+        <v>0</v>
+      </c>
+      <c r="BG5" s="536">
         <v>1</v>
       </c>
       <c r="BH5" s="104">
         <f>+BD5+BE5+BF5+BG5</f>
         <v>4</v>
       </c>
-      <c r="BI5" s="701">
-        <v>0</v>
-      </c>
-      <c r="BJ5" s="701">
+      <c r="BI5" s="536">
+        <v>0</v>
+      </c>
+      <c r="BJ5" s="536">
         <v>1</v>
       </c>
-      <c r="BK5" s="701">
-        <v>0</v>
-      </c>
-      <c r="BL5" s="701">
+      <c r="BK5" s="536">
+        <v>0</v>
+      </c>
+      <c r="BL5" s="536">
         <v>2</v>
       </c>
       <c r="BM5" s="104">
         <f t="shared" ref="BM5:BM18" si="4">+BI5+BJ5+BK5+BL5</f>
         <v>3</v>
       </c>
-      <c r="BN5" s="586">
+      <c r="BN5" s="559">
         <f>+IFERROR(BM6/BM5,0)</f>
         <v>115</v>
       </c>
@@ -42092,7 +42092,7 @@
         <f>+R5+W5+AB5+AH5+AM5+AR5+AX5+BC5+BH5+BM5</f>
         <v>65</v>
       </c>
-      <c r="BP5" s="586">
+      <c r="BP5" s="559">
         <f>+BO6/BO5</f>
         <v>126.95384615384616</v>
       </c>
@@ -42100,10 +42100,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:74" ht="18" customHeight="1" thickBot="1">
-      <c r="B6" s="609"/>
-      <c r="C6" s="566"/>
-      <c r="D6" s="568"/>
+    <row r="6" spans="2:74" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="582"/>
+      <c r="C6" s="539"/>
+      <c r="D6" s="541"/>
       <c r="E6" s="108" t="s">
         <v>13</v>
       </c>
@@ -42131,7 +42131,7 @@
         <f t="shared" si="1"/>
         <v>3270</v>
       </c>
-      <c r="M6" s="570"/>
+      <c r="M6" s="543"/>
       <c r="N6" s="115">
         <v>690</v>
       </c>
@@ -42262,51 +42262,51 @@
       <c r="BA6" s="123">
         <v>485</v>
       </c>
-      <c r="BB6" s="702">
+      <c r="BB6" s="537">
         <v>120</v>
       </c>
       <c r="BC6" s="100">
         <f t="shared" si="2"/>
         <v>896</v>
       </c>
-      <c r="BD6" s="702">
-        <v>0</v>
-      </c>
-      <c r="BE6" s="702">
+      <c r="BD6" s="537">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="537">
         <v>446</v>
       </c>
-      <c r="BF6" s="702">
-        <v>0</v>
-      </c>
-      <c r="BG6" s="702">
+      <c r="BF6" s="537">
+        <v>0</v>
+      </c>
+      <c r="BG6" s="537">
         <v>190</v>
       </c>
       <c r="BH6" s="100">
         <f>+BD6+BE6+BF6+BG6</f>
         <v>636</v>
       </c>
-      <c r="BI6" s="702">
-        <v>0</v>
-      </c>
-      <c r="BJ6" s="702">
+      <c r="BI6" s="537">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="537">
         <v>140</v>
       </c>
-      <c r="BK6" s="702">
-        <v>0</v>
-      </c>
-      <c r="BL6" s="702">
+      <c r="BK6" s="537">
+        <v>0</v>
+      </c>
+      <c r="BL6" s="537">
         <v>205</v>
       </c>
       <c r="BM6" s="100">
         <f t="shared" si="4"/>
         <v>345</v>
       </c>
-      <c r="BN6" s="583"/>
+      <c r="BN6" s="556"/>
       <c r="BO6" s="193">
         <f>+R6+W6+AB6+AH6+AM6+AR6+AX6+BC6+BH6+BM6</f>
         <v>8252</v>
       </c>
-      <c r="BP6" s="583"/>
+      <c r="BP6" s="556"/>
       <c r="BQ6" s="61">
         <f>+AVERAGE(R6,W6,AB6,AH6,AM6,AR6,AX6,BC6,BH6,BM6)</f>
         <v>825.2</v>
@@ -42319,7 +42319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:74" ht="18" hidden="1" customHeight="1">
+    <row r="7" spans="2:74" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="187"/>
       <c r="C7" s="177"/>
       <c r="D7" s="112" t="s">
@@ -42413,7 +42413,7 @@
       <c r="BO7" s="194"/>
       <c r="BP7" s="198"/>
     </row>
-    <row r="8" spans="2:74" ht="18" hidden="1" customHeight="1" thickBot="1">
+    <row r="8" spans="2:74" ht="18" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="188"/>
       <c r="C8" s="173"/>
       <c r="D8" s="62" t="s">
@@ -42507,7 +42507,7 @@
       <c r="BO8" s="195"/>
       <c r="BP8" s="199"/>
     </row>
-    <row r="9" spans="2:74" ht="30.6" hidden="1" customHeight="1" thickBot="1">
+    <row r="9" spans="2:74" ht="30.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="189"/>
       <c r="C9" s="200"/>
       <c r="D9" s="120" t="s">
@@ -42601,12 +42601,12 @@
       <c r="BO9" s="196"/>
       <c r="BP9" s="174"/>
     </row>
-    <row r="10" spans="2:74" ht="18" hidden="1" customHeight="1">
-      <c r="B10" s="608" t="s">
+    <row r="10" spans="2:74" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="581" t="s">
         <v>222</v>
       </c>
-      <c r="C10" s="565"/>
-      <c r="D10" s="567" t="s">
+      <c r="C10" s="538"/>
+      <c r="D10" s="540" t="s">
         <v>20</v>
       </c>
       <c r="E10" s="105" t="s">
@@ -42628,7 +42628,7 @@
         <f>+SUM(I10:K10)</f>
         <v>15</v>
       </c>
-      <c r="M10" s="569">
+      <c r="M10" s="542">
         <f>+L11/L10</f>
         <v>193</v>
       </c>
@@ -42746,7 +42746,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BN10" s="582">
+      <c r="BN10" s="555">
         <f>+IFERROR(AM11/AM10,0)</f>
         <v>490</v>
       </c>
@@ -42754,17 +42754,17 @@
         <f>+R10+W10+AB10+AH10+AM10</f>
         <v>12</v>
       </c>
-      <c r="BP10" s="582">
+      <c r="BP10" s="555">
         <f>+BO11/BO10</f>
         <v>210.58333333333334</v>
       </c>
       <c r="BR10" s="152"/>
       <c r="BS10" s="61"/>
     </row>
-    <row r="11" spans="2:74" ht="18" hidden="1" customHeight="1" thickBot="1">
-      <c r="B11" s="610"/>
-      <c r="C11" s="571"/>
-      <c r="D11" s="572"/>
+    <row r="11" spans="2:74" ht="18" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="583"/>
+      <c r="C11" s="544"/>
+      <c r="D11" s="545"/>
       <c r="E11" s="42" t="s">
         <v>13</v>
       </c>
@@ -42784,7 +42784,7 @@
         <f t="shared" si="1"/>
         <v>2895</v>
       </c>
-      <c r="M11" s="573"/>
+      <c r="M11" s="546"/>
       <c r="N11" s="43">
         <v>0</v>
       </c>
@@ -42899,18 +42899,18 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BN11" s="586"/>
+      <c r="BN11" s="559"/>
       <c r="BO11" s="195">
         <f>+R11+W11+AB11+AH11+AM11</f>
         <v>2527</v>
       </c>
-      <c r="BP11" s="586"/>
+      <c r="BP11" s="559"/>
       <c r="BR11" s="152"/>
     </row>
-    <row r="12" spans="2:74" ht="14.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="B12" s="609"/>
-      <c r="C12" s="566"/>
-      <c r="D12" s="568"/>
+    <row r="12" spans="2:74" ht="14.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="582"/>
+      <c r="C12" s="539"/>
+      <c r="D12" s="541"/>
       <c r="E12" s="126" t="s">
         <v>21</v>
       </c>
@@ -42930,7 +42930,7 @@
         <f>+SUM(I12:K12)</f>
         <v>8</v>
       </c>
-      <c r="M12" s="570"/>
+      <c r="M12" s="543"/>
       <c r="N12" s="127"/>
       <c r="O12" s="127"/>
       <c r="P12" s="127"/>
@@ -43004,18 +43004,18 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="BN12" s="583"/>
+      <c r="BN12" s="556"/>
       <c r="BO12" s="193"/>
-      <c r="BP12" s="583"/>
+      <c r="BP12" s="556"/>
     </row>
-    <row r="13" spans="2:74" ht="18" customHeight="1">
-      <c r="B13" s="608" t="s">
+    <row r="13" spans="2:74" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="581" t="s">
         <v>222</v>
       </c>
-      <c r="C13" s="565">
+      <c r="C13" s="538">
         <v>3</v>
       </c>
-      <c r="D13" s="567" t="s">
+      <c r="D13" s="540" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="105" t="s">
@@ -43037,7 +43037,7 @@
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="M13" s="569">
+      <c r="M13" s="542">
         <f>+L14/L13</f>
         <v>31.950819672131146</v>
       </c>
@@ -43207,7 +43207,7 @@
         <f t="shared" si="4"/>
         <v>21</v>
       </c>
-      <c r="BN13" s="582">
+      <c r="BN13" s="555">
         <f>+IFERROR(BM14/BM13,0)</f>
         <v>33.571428571428569</v>
       </c>
@@ -43215,7 +43215,7 @@
         <f t="shared" ref="BO13:BO18" si="14">+R13+W13+AB13+AH13+AM13+AR13+AX13+BC13+BH13+BM13</f>
         <v>193</v>
       </c>
-      <c r="BP13" s="582">
+      <c r="BP13" s="555">
         <f>+BO14/BO13</f>
         <v>41.274611398963728</v>
       </c>
@@ -43228,10 +43228,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="2:74" ht="18" customHeight="1" thickBot="1">
-      <c r="B14" s="609"/>
-      <c r="C14" s="566"/>
-      <c r="D14" s="568"/>
+    <row r="14" spans="2:74" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="582"/>
+      <c r="C14" s="539"/>
+      <c r="D14" s="541"/>
       <c r="E14" s="108" t="s">
         <v>13</v>
       </c>
@@ -43251,7 +43251,7 @@
         <f t="shared" si="1"/>
         <v>1949</v>
       </c>
-      <c r="M14" s="570"/>
+      <c r="M14" s="543"/>
       <c r="N14" s="109">
         <v>762</v>
       </c>
@@ -43419,12 +43419,12 @@
         <f t="shared" si="4"/>
         <v>705</v>
       </c>
-      <c r="BN14" s="583"/>
+      <c r="BN14" s="556"/>
       <c r="BO14" s="193">
         <f t="shared" si="14"/>
         <v>7966</v>
       </c>
-      <c r="BP14" s="583"/>
+      <c r="BP14" s="556"/>
       <c r="BQ14" s="61">
         <f>+AVERAGE(R14,W14,AB14,AH14,AM14,AR14,AX14,BC14,BH14,BM14)</f>
         <v>796.6</v>
@@ -43437,14 +43437,14 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="2:74" ht="18" customHeight="1">
-      <c r="B15" s="608" t="s">
+    <row r="15" spans="2:74" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="581" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="565">
+      <c r="C15" s="538">
         <v>4</v>
       </c>
-      <c r="D15" s="601" t="s">
+      <c r="D15" s="574" t="s">
         <v>223</v>
       </c>
       <c r="E15" s="105" t="s">
@@ -43466,7 +43466,7 @@
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
-      <c r="M15" s="569">
+      <c r="M15" s="542">
         <f>+L16/L15</f>
         <v>34.384615384615387</v>
       </c>
@@ -43641,7 +43641,7 @@
         <f t="shared" si="4"/>
         <v>16</v>
       </c>
-      <c r="BN15" s="582">
+      <c r="BN15" s="555">
         <f>+IFERROR(BM16/BM15,0)</f>
         <v>39.799999999999997</v>
       </c>
@@ -43649,7 +43649,7 @@
         <f t="shared" si="14"/>
         <v>168</v>
       </c>
-      <c r="BP15" s="582">
+      <c r="BP15" s="555">
         <f>+BO16/BO15</f>
         <v>46.028571428571432</v>
       </c>
@@ -43662,10 +43662,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:74" ht="18" customHeight="1" thickBot="1">
-      <c r="B16" s="609"/>
-      <c r="C16" s="566"/>
-      <c r="D16" s="568"/>
+    <row r="16" spans="2:74" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="582"/>
+      <c r="C16" s="539"/>
+      <c r="D16" s="541"/>
       <c r="E16" s="108" t="s">
         <v>13</v>
       </c>
@@ -43686,7 +43686,7 @@
         <f t="shared" si="1"/>
         <v>1788</v>
       </c>
-      <c r="M16" s="570"/>
+      <c r="M16" s="543"/>
       <c r="N16" s="109">
         <v>0</v>
       </c>
@@ -43862,12 +43862,12 @@
         <f t="shared" si="4"/>
         <v>636.79999999999995</v>
       </c>
-      <c r="BN16" s="583"/>
+      <c r="BN16" s="556"/>
       <c r="BO16" s="193">
         <f t="shared" si="14"/>
         <v>7732.8</v>
       </c>
-      <c r="BP16" s="583"/>
+      <c r="BP16" s="556"/>
       <c r="BQ16" s="61">
         <f>+AVERAGE(R16,W16,AB16,AH16,AM16,AR16,AX16,BC16,BH16,BM16)</f>
         <v>773.28</v>
@@ -43883,14 +43883,14 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="2:81" ht="18" customHeight="1">
-      <c r="B17" s="611" t="s">
+    <row r="17" spans="2:81" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="584" t="s">
         <v>224</v>
       </c>
-      <c r="C17" s="576">
+      <c r="C17" s="549">
         <v>5</v>
       </c>
-      <c r="D17" s="574" t="s">
+      <c r="D17" s="547" t="s">
         <v>225</v>
       </c>
       <c r="E17" s="128" t="s">
@@ -43912,7 +43912,7 @@
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
-      <c r="M17" s="569">
+      <c r="M17" s="542">
         <f>+L18/L17</f>
         <v>32.379310344827587</v>
       </c>
@@ -44084,7 +44084,7 @@
         <f t="shared" si="4"/>
         <v>15</v>
       </c>
-      <c r="BN17" s="582">
+      <c r="BN17" s="555">
         <f>+IFERROR(BM18/BM17,0)</f>
         <v>50.733333333333334</v>
       </c>
@@ -44092,7 +44092,7 @@
         <f t="shared" si="14"/>
         <v>173</v>
       </c>
-      <c r="BP17" s="582">
+      <c r="BP17" s="555">
         <f>+BO18/BO17</f>
         <v>46.404624277456648</v>
       </c>
@@ -44126,10 +44126,10 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="18" spans="2:81" ht="18" customHeight="1" thickBot="1">
-      <c r="B18" s="612"/>
-      <c r="C18" s="577"/>
-      <c r="D18" s="575"/>
+    <row r="18" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="585"/>
+      <c r="C18" s="550"/>
+      <c r="D18" s="548"/>
       <c r="E18" s="129" t="s">
         <v>13</v>
       </c>
@@ -44149,7 +44149,7 @@
         <f t="shared" si="1"/>
         <v>1878</v>
       </c>
-      <c r="M18" s="570"/>
+      <c r="M18" s="543"/>
       <c r="N18" s="115">
         <v>427</v>
       </c>
@@ -44319,12 +44319,12 @@
         <f t="shared" si="4"/>
         <v>761</v>
       </c>
-      <c r="BN18" s="583"/>
+      <c r="BN18" s="556"/>
       <c r="BO18" s="193">
         <f t="shared" si="14"/>
         <v>8028</v>
       </c>
-      <c r="BP18" s="583"/>
+      <c r="BP18" s="556"/>
       <c r="BQ18" s="61">
         <f>+AVERAGE(R18,W18,AB18,AH18,AM18,AR18,AX18,BC18,BH18,BM18)</f>
         <v>802.8</v>
@@ -44364,14 +44364,14 @@
         <v>5700.6721600000001</v>
       </c>
     </row>
-    <row r="19" spans="2:81" ht="18" customHeight="1">
-      <c r="B19" s="611" t="s">
+    <row r="19" spans="2:81" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="584" t="s">
         <v>222</v>
       </c>
-      <c r="C19" s="576">
+      <c r="C19" s="549">
         <v>6</v>
       </c>
-      <c r="D19" s="574"/>
+      <c r="D19" s="547"/>
       <c r="E19" s="143" t="s">
         <v>0</v>
       </c>
@@ -44435,17 +44435,17 @@
       <c r="BK19" s="215"/>
       <c r="BL19" s="215"/>
       <c r="BM19" s="213"/>
-      <c r="BN19" s="598"/>
+      <c r="BN19" s="571"/>
       <c r="BO19" s="217"/>
-      <c r="BP19" s="598"/>
+      <c r="BP19" s="571"/>
       <c r="BQ19" s="61"/>
       <c r="BR19" s="61"/>
       <c r="BS19" s="61"/>
     </row>
-    <row r="20" spans="2:81" ht="18" customHeight="1" thickBot="1">
-      <c r="B20" s="612"/>
-      <c r="C20" s="577"/>
-      <c r="D20" s="575"/>
+    <row r="20" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="585"/>
+      <c r="C20" s="550"/>
+      <c r="D20" s="548"/>
       <c r="E20" s="143" t="s">
         <v>13</v>
       </c>
@@ -44509,21 +44509,21 @@
       <c r="BK20" s="221"/>
       <c r="BL20" s="221"/>
       <c r="BM20" s="219"/>
-      <c r="BN20" s="599"/>
+      <c r="BN20" s="572"/>
       <c r="BO20" s="223"/>
-      <c r="BP20" s="599"/>
+      <c r="BP20" s="572"/>
       <c r="BQ20" s="61"/>
       <c r="BR20" s="61"/>
       <c r="BS20" s="61"/>
     </row>
-    <row r="21" spans="2:81" ht="18" customHeight="1">
-      <c r="B21" s="613" t="s">
+    <row r="21" spans="2:81" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="586" t="s">
         <v>222</v>
       </c>
-      <c r="C21" s="592" t="s">
+      <c r="C21" s="565" t="s">
         <v>227</v>
       </c>
-      <c r="D21" s="594" t="s">
+      <c r="D21" s="567" t="s">
         <v>228</v>
       </c>
       <c r="E21" s="212" t="s">
@@ -44536,7 +44536,7 @@
       <c r="J21" s="213"/>
       <c r="K21" s="213"/>
       <c r="L21" s="214"/>
-      <c r="M21" s="596">
+      <c r="M21" s="569">
         <v>0</v>
       </c>
       <c r="N21" s="215">
@@ -44705,7 +44705,7 @@
         <f>+BL21</f>
         <v>6</v>
       </c>
-      <c r="BN21" s="598">
+      <c r="BN21" s="571">
         <f>+IFERROR(BM22/BM21,0)</f>
         <v>21.333333333333332</v>
       </c>
@@ -44713,16 +44713,16 @@
         <f>+BM21</f>
         <v>6</v>
       </c>
-      <c r="BP21" s="598">
+      <c r="BP21" s="571">
         <f>+BO22/BO21</f>
         <v>21.333333333333332</v>
       </c>
       <c r="BQ21" s="61"/>
     </row>
-    <row r="22" spans="2:81" ht="18" customHeight="1" thickBot="1">
-      <c r="B22" s="614"/>
-      <c r="C22" s="593"/>
-      <c r="D22" s="595"/>
+    <row r="22" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="587"/>
+      <c r="C22" s="566"/>
+      <c r="D22" s="568"/>
       <c r="E22" s="218" t="s">
         <v>13</v>
       </c>
@@ -44733,7 +44733,7 @@
       <c r="J22" s="219"/>
       <c r="K22" s="219"/>
       <c r="L22" s="220"/>
-      <c r="M22" s="597"/>
+      <c r="M22" s="570"/>
       <c r="N22" s="221">
         <v>192</v>
       </c>
@@ -44900,12 +44900,12 @@
         <f>+BL22</f>
         <v>128</v>
       </c>
-      <c r="BN22" s="599"/>
+      <c r="BN22" s="572"/>
       <c r="BO22" s="223">
         <f>+BM22</f>
         <v>128</v>
       </c>
-      <c r="BP22" s="599"/>
+      <c r="BP22" s="572"/>
       <c r="BQ22" s="61"/>
       <c r="BU22" s="48" t="s">
         <v>229</v>
@@ -44935,14 +44935,14 @@
         <v>751.5725900000001</v>
       </c>
     </row>
-    <row r="23" spans="2:81" ht="18" customHeight="1">
-      <c r="B23" s="613" t="s">
+    <row r="23" spans="2:81" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="586" t="s">
         <v>222</v>
       </c>
-      <c r="C23" s="592" t="s">
+      <c r="C23" s="565" t="s">
         <v>230</v>
       </c>
-      <c r="D23" s="594" t="s">
+      <c r="D23" s="567" t="s">
         <v>231</v>
       </c>
       <c r="E23" s="224" t="s">
@@ -44962,7 +44962,7 @@
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="M23" s="596">
+      <c r="M23" s="569">
         <f>+L24/L23</f>
         <v>23.5</v>
       </c>
@@ -45134,7 +45134,7 @@
         <f>+BL23</f>
         <v>4</v>
       </c>
-      <c r="BN23" s="598">
+      <c r="BN23" s="571">
         <f>+IFERROR(BM24/BM23,0)</f>
         <v>15.5</v>
       </c>
@@ -45142,16 +45142,16 @@
         <f>+BM23</f>
         <v>4</v>
       </c>
-      <c r="BP23" s="598">
+      <c r="BP23" s="571">
         <f>+BO24/BO23</f>
         <v>15.5</v>
       </c>
       <c r="BQ23" s="61"/>
     </row>
-    <row r="24" spans="2:81" ht="18" customHeight="1" thickBot="1">
-      <c r="B24" s="615"/>
-      <c r="C24" s="593"/>
-      <c r="D24" s="600"/>
+    <row r="24" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="588"/>
+      <c r="C24" s="566"/>
+      <c r="D24" s="573"/>
       <c r="E24" s="225" t="s">
         <v>13</v>
       </c>
@@ -45169,7 +45169,7 @@
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="M24" s="597"/>
+      <c r="M24" s="570"/>
       <c r="N24" s="227">
         <v>70</v>
       </c>
@@ -45342,12 +45342,12 @@
         <f>+BL24</f>
         <v>62</v>
       </c>
-      <c r="BN24" s="599"/>
+      <c r="BN24" s="572"/>
       <c r="BO24" s="229">
         <f>+BM24</f>
         <v>62</v>
       </c>
-      <c r="BP24" s="599"/>
+      <c r="BP24" s="572"/>
       <c r="BQ24" s="61"/>
       <c r="BS24" s="175"/>
       <c r="BU24" s="48" t="s">
@@ -45375,7 +45375,7 @@
         <v>894.28983830188668</v>
       </c>
     </row>
-    <row r="25" spans="2:81" s="148" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
+    <row r="25" spans="2:81" s="148" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B25" s="209" t="s">
         <v>224</v>
       </c>
@@ -45495,14 +45495,14 @@
       <c r="BS25" s="176"/>
       <c r="BT25" s="176"/>
     </row>
-    <row r="26" spans="2:81" ht="18" customHeight="1">
-      <c r="B26" s="611" t="s">
+    <row r="26" spans="2:81" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="584" t="s">
         <v>224</v>
       </c>
-      <c r="C26" s="576">
+      <c r="C26" s="549">
         <v>8</v>
       </c>
-      <c r="D26" s="574" t="s">
+      <c r="D26" s="547" t="s">
         <v>29</v>
       </c>
       <c r="E26" s="105" t="s">
@@ -45524,7 +45524,7 @@
         <f>+SUM(I26:K26)</f>
         <v>55</v>
       </c>
-      <c r="M26" s="569">
+      <c r="M26" s="542">
         <f>+L27/L26</f>
         <v>38.109090909090909</v>
       </c>
@@ -45697,7 +45697,7 @@
         <f t="shared" ref="BM26:BM27" si="17">+BI26+BJ26+BK26+BL26</f>
         <v>16</v>
       </c>
-      <c r="BN26" s="582">
+      <c r="BN26" s="555">
         <f>+IFERROR(BM27/BM26,0)</f>
         <v>45.5625</v>
       </c>
@@ -45705,7 +45705,7 @@
         <f>+R26+W26+AB26+AH26+AM26+AR26+AX26+BC26+BH26+BM26</f>
         <v>175</v>
       </c>
-      <c r="BP26" s="582">
+      <c r="BP26" s="555">
         <f>+BO27/BO26</f>
         <v>43.32</v>
       </c>
@@ -45718,10 +45718,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:81" ht="18" customHeight="1" thickBot="1">
-      <c r="B27" s="612"/>
-      <c r="C27" s="577"/>
-      <c r="D27" s="575"/>
+    <row r="27" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="585"/>
+      <c r="C27" s="550"/>
+      <c r="D27" s="548"/>
       <c r="E27" s="108" t="s">
         <v>13</v>
       </c>
@@ -45741,7 +45741,7 @@
         <f>+SUM(I27:K27)</f>
         <v>2096</v>
       </c>
-      <c r="M27" s="570"/>
+      <c r="M27" s="543"/>
       <c r="N27" s="109">
         <v>197</v>
       </c>
@@ -45911,12 +45911,12 @@
         <f t="shared" si="17"/>
         <v>729</v>
       </c>
-      <c r="BN27" s="583"/>
+      <c r="BN27" s="556"/>
       <c r="BO27" s="193">
         <f>+R27+W27+AB27+AH27+AM27+AR27+AX27+BC27+BH27+BM27</f>
         <v>7581</v>
       </c>
-      <c r="BP27" s="583"/>
+      <c r="BP27" s="556"/>
       <c r="BQ27" s="61">
         <f>+AVERAGE(R27,W27,AB27,AH27,AM27,AR27,AX27,BC27,BH27,BM27)</f>
         <v>758.1</v>
@@ -45929,14 +45929,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:81" ht="18" customHeight="1">
-      <c r="B28" s="611" t="s">
+    <row r="28" spans="2:81" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="584" t="s">
         <v>224</v>
       </c>
-      <c r="C28" s="576">
+      <c r="C28" s="549">
         <v>9</v>
       </c>
-      <c r="D28" s="574" t="s">
+      <c r="D28" s="547" t="s">
         <v>32</v>
       </c>
       <c r="E28" s="128" t="s">
@@ -45954,7 +45954,7 @@
         <f t="shared" ref="L28:L29" si="18">+SUM(I28:K28)</f>
         <v>8</v>
       </c>
-      <c r="M28" s="569">
+      <c r="M28" s="542">
         <f>+L29/L28</f>
         <v>35.75</v>
       </c>
@@ -46124,7 +46124,7 @@
         <f>+BL28</f>
         <v>5</v>
       </c>
-      <c r="BN28" s="582">
+      <c r="BN28" s="555">
         <f>+IFERROR(BM29/BM28,0)</f>
         <v>65.400000000000006</v>
       </c>
@@ -46132,17 +46132,17 @@
         <f>+BM28</f>
         <v>5</v>
       </c>
-      <c r="BP28" s="582">
+      <c r="BP28" s="555">
         <f>+IFERROR(BO29/BO28,0)</f>
         <v>65.400000000000006</v>
       </c>
       <c r="BQ28" s="61"/>
       <c r="BR28" s="61"/>
     </row>
-    <row r="29" spans="2:81" ht="18" customHeight="1" thickBot="1">
-      <c r="B29" s="612"/>
-      <c r="C29" s="577"/>
-      <c r="D29" s="575"/>
+    <row r="29" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="585"/>
+      <c r="C29" s="550"/>
+      <c r="D29" s="548"/>
       <c r="E29" s="129" t="s">
         <v>35</v>
       </c>
@@ -46158,7 +46158,7 @@
         <f t="shared" si="18"/>
         <v>286</v>
       </c>
-      <c r="M29" s="570"/>
+      <c r="M29" s="543"/>
       <c r="N29" s="109">
         <v>110</v>
       </c>
@@ -46326,16 +46326,16 @@
         <f>+BL29</f>
         <v>327</v>
       </c>
-      <c r="BN29" s="583"/>
+      <c r="BN29" s="556"/>
       <c r="BO29" s="193">
         <f>+BM29</f>
         <v>327</v>
       </c>
-      <c r="BP29" s="583"/>
+      <c r="BP29" s="556"/>
       <c r="BQ29" s="61"/>
       <c r="BR29" s="208"/>
     </row>
-    <row r="30" spans="2:81" ht="18" customHeight="1" thickBot="1">
+    <row r="30" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B30" s="190" t="s">
         <v>222</v>
       </c>
@@ -46554,7 +46554,7 @@
       </c>
       <c r="BR30" s="184"/>
     </row>
-    <row r="31" spans="2:81" ht="18" customHeight="1" thickBot="1">
+    <row r="31" spans="2:81" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B31" s="190" t="s">
         <v>222</v>
       </c>
@@ -46756,7 +46756,7 @@
         <v>0.71799999999999997</v>
       </c>
     </row>
-    <row r="33" spans="5:68">
+    <row r="33" spans="5:68" x14ac:dyDescent="0.2">
       <c r="AC33" s="48">
         <v>2</v>
       </c>
@@ -46770,7 +46770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="5:68">
+    <row r="34" spans="5:68" x14ac:dyDescent="0.2">
       <c r="E34" s="53"/>
       <c r="F34" s="53"/>
       <c r="G34" s="53"/>
@@ -46838,7 +46838,7 @@
       </c>
       <c r="BP34" s="61"/>
     </row>
-    <row r="35" spans="5:68">
+    <row r="35" spans="5:68" x14ac:dyDescent="0.2">
       <c r="E35" s="53"/>
       <c r="F35" s="53"/>
       <c r="G35" s="53"/>
@@ -46898,7 +46898,7 @@
       </c>
       <c r="BP35" s="61"/>
     </row>
-    <row r="38" spans="5:68">
+    <row r="38" spans="5:68" x14ac:dyDescent="0.2">
       <c r="AO38" s="48">
         <f>6677-6537</f>
         <v>140</v>
@@ -46986,12 +46986,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{899DCCE6-AC8C-4240-97A0-4DE2A77B53A2}">
   <sheetPr codeName="Hoja6"/>
   <dimension ref="A1:Q53"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B1" s="160">
         <v>45566</v>
       </c>
@@ -47011,7 +47011,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>234</v>
       </c>
@@ -47042,7 +47042,7 @@
         <v>8119.2000000000007</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>235</v>
       </c>
@@ -47073,7 +47073,7 @@
         <v>7514.4000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>236</v>
       </c>
@@ -47104,7 +47104,7 @@
         <v>8853.5999999999985</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>237</v>
       </c>
@@ -47122,7 +47122,7 @@
         <v>2823</v>
       </c>
     </row>
-    <row r="28" spans="2:12">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="314" t="s">
         <v>238</v>
       </c>
@@ -47148,7 +47148,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="2:12">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="317" t="s">
         <v>244</v>
       </c>
@@ -47177,7 +47177,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="30" spans="2:12">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="317" t="s">
         <v>245</v>
       </c>
@@ -47203,7 +47203,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="317" t="s">
         <v>246</v>
       </c>
@@ -47229,7 +47229,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="317" t="s">
         <v>247</v>
       </c>
@@ -47255,7 +47255,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B33" s="317" t="s">
         <v>248</v>
       </c>
@@ -47281,13 +47281,13 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="34" spans="2:17">
-      <c r="B34" s="616" t="s">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B34" s="589" t="s">
         <v>249</v>
       </c>
-      <c r="C34" s="616"/>
-      <c r="D34" s="616"/>
-      <c r="E34" s="616"/>
+      <c r="C34" s="589"/>
+      <c r="D34" s="589"/>
+      <c r="E34" s="589"/>
       <c r="F34" s="313">
         <f>SUM(F29:F33)</f>
         <v>13715</v>
@@ -47297,7 +47297,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="I35" s="322"/>
       <c r="N35" t="s">
         <v>250</v>
@@ -47309,15 +47309,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="2:17">
-      <c r="E36" s="616" t="s">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="E36" s="589" t="s">
         <v>251</v>
       </c>
-      <c r="F36" s="616"/>
-      <c r="G36" s="616"/>
+      <c r="F36" s="589"/>
+      <c r="G36" s="589"/>
       <c r="I36" s="322"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E37" s="314" t="s">
         <v>238</v>
       </c>
@@ -47342,7 +47342,7 @@
         <v>3096.9354838709678</v>
       </c>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E38" s="317" t="s">
         <v>254</v>
       </c>
@@ -47358,7 +47358,7 @@
         <v>342875</v>
       </c>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E39" s="317" t="s">
         <v>253</v>
       </c>
@@ -47389,7 +47389,7 @@
         <v>13715</v>
       </c>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B40" s="314"/>
       <c r="C40" s="314"/>
       <c r="D40" s="314"/>
@@ -47409,7 +47409,7 @@
         <v>420298.38709677424</v>
       </c>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E41" s="329" t="s">
         <v>257</v>
       </c>
@@ -47425,7 +47425,7 @@
         <v>60042.626728110612</v>
       </c>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E42" s="329" t="s">
         <v>258</v>
       </c>
@@ -47441,7 +47441,7 @@
         <v>78055.4147465438</v>
       </c>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E43" s="329" t="s">
         <v>259</v>
       </c>
@@ -47457,7 +47457,7 @@
         <v>30021.313364055306</v>
       </c>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E44" s="329" t="s">
         <v>260</v>
       </c>
@@ -47473,7 +47473,7 @@
         <v>12008.525345622122</v>
       </c>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E45" s="314" t="s">
         <v>261</v>
       </c>
@@ -47486,7 +47486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="E47" s="314" t="s">
         <v>262</v>
       </c>
@@ -47494,7 +47494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="5:12">
+    <row r="49" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E49" s="325" t="s">
         <v>263</v>
       </c>
@@ -47515,13 +47515,13 @@
         <v>5043580.6451612907</v>
       </c>
     </row>
-    <row r="50" spans="5:12">
+    <row r="50" spans="5:12" x14ac:dyDescent="0.2">
       <c r="L50" s="312">
         <f t="shared" ref="L50:L53" si="7">+G41*$G$49</f>
         <v>720511.52073732729</v>
       </c>
     </row>
-    <row r="51" spans="5:12">
+    <row r="51" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E51" s="325" t="s">
         <v>232</v>
       </c>
@@ -47542,13 +47542,13 @@
         <v>936664.97695852548</v>
       </c>
     </row>
-    <row r="52" spans="5:12">
+    <row r="52" spans="5:12" x14ac:dyDescent="0.2">
       <c r="L52" s="312">
         <f t="shared" si="7"/>
         <v>360255.76036866364</v>
       </c>
     </row>
-    <row r="53" spans="5:12">
+    <row r="53" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E53" s="315" t="s">
         <v>264</v>
       </c>
@@ -47578,17 +47578,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1695925A-2D63-4886-B7E3-27A68E97157E}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" style="345" customWidth="1"/>
-    <col min="2" max="2" width="64.140625" style="345" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="345" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="345" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="345" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.85546875" style="345"/>
+    <col min="2" max="2" width="64.1640625" style="345" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" style="345" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" style="345" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="345" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="345"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="343" customFormat="1">
+    <row r="1" spans="1:5" s="343" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="343" t="s">
         <v>0</v>
       </c>
@@ -47605,7 +47605,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="345">
         <v>1</v>
       </c>
@@ -47622,7 +47622,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="345">
         <f>1+A2</f>
         <v>2</v>
@@ -47640,7 +47640,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="345">
         <f t="shared" ref="A4:A7" si="0">1+A3</f>
         <v>3</v>
@@ -47658,7 +47658,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="345">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -47676,7 +47676,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="345">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -47694,7 +47694,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="345">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -47712,26 +47712,26 @@
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D8" s="346"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D9" s="346"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D10" s="346"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="344"/>
       <c r="D11" s="346"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D12" s="346"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D13" s="346"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D14" s="346"/>
     </row>
   </sheetData>
@@ -47746,61 +47746,61 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E08EA5-F1A8-45D5-95E8-BF6CEF257FE2}">
   <sheetPr codeName="Hoja5"/>
   <dimension ref="B1:CN36"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.15" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="230"/>
-    <col min="2" max="2" width="6.85546875" style="230" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" style="230" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" style="230" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="230" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="6.42578125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="7.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="6.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="6.42578125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="11.5" style="230"/>
+    <col min="2" max="2" width="6.83203125" style="230" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="230" customWidth="1"/>
+    <col min="4" max="4" width="22.5" style="230" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="6.5" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="7.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="6.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="6.5" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="6" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="5.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="12.5703125" style="230" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="17" width="8.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="22" width="9.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="5.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="12.5" style="230" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="17" width="8.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="22" width="9.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="25" max="27" width="9" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="30" max="33" width="11.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="34" max="34" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="35" max="38" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="39" max="39" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="40" max="43" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="44" max="44" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="45" max="49" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="50" max="50" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="51" max="54" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="55" max="55" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="56" max="59" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="60" max="60" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="61" max="65" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="66" max="66" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="67" max="67" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="68" max="70" width="11.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="71" max="71" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="72" max="76" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="77" max="77" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="78" max="78" width="10.140625" style="230" customWidth="1"/>
-    <col min="79" max="79" width="10.140625" style="230" bestFit="1" customWidth="1"/>
-    <col min="80" max="80" width="10.85546875" style="230" customWidth="1"/>
+    <col min="28" max="28" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="30" max="33" width="11.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="34" max="34" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="35" max="38" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="39" max="39" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="40" max="43" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="45" max="49" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="50" max="50" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="51" max="54" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="55" max="55" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="56" max="59" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="60" max="60" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="61" max="65" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="66" max="66" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="67" max="67" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="68" max="70" width="11.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="71" max="71" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="72" max="76" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="77" max="77" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="78" max="78" width="10.1640625" style="230" customWidth="1"/>
+    <col min="79" max="79" width="10.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="80" max="80" width="10.83203125" style="230" customWidth="1"/>
     <col min="81" max="81" width="12" style="230" bestFit="1" customWidth="1"/>
-    <col min="82" max="82" width="13.85546875" style="230" bestFit="1" customWidth="1"/>
-    <col min="83" max="84" width="11.5703125" style="230"/>
-    <col min="85" max="85" width="17.85546875" style="230" bestFit="1" customWidth="1"/>
-    <col min="86" max="16384" width="11.5703125" style="230"/>
+    <col min="82" max="82" width="13.83203125" style="230" bestFit="1" customWidth="1"/>
+    <col min="83" max="84" width="11.5" style="230"/>
+    <col min="85" max="85" width="17.83203125" style="230" bestFit="1" customWidth="1"/>
+    <col min="86" max="16384" width="11.5" style="230"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:92" ht="13.9" thickBot="1"/>
-    <row r="2" spans="2:92" ht="29.85" customHeight="1" thickBot="1">
+    <row r="1" spans="2:92" ht="13" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:92" ht="29.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="248" t="s">
         <v>178</v>
       </c>
@@ -48053,14 +48053,14 @@
         <v>283</v>
       </c>
     </row>
-    <row r="3" spans="2:92" ht="18.600000000000001" customHeight="1">
-      <c r="B3" s="619" t="s">
+    <row r="3" spans="2:92" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="592" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="620">
+      <c r="C3" s="593">
         <v>1</v>
       </c>
-      <c r="D3" s="622" t="s">
+      <c r="D3" s="595" t="s">
         <v>220</v>
       </c>
       <c r="E3" s="261" t="s">
@@ -48090,7 +48090,7 @@
         <f>+SUM(I3:K3)</f>
         <v>42</v>
       </c>
-      <c r="M3" s="624">
+      <c r="M3" s="597">
         <f>+L4/L3</f>
         <v>236.3095238095238</v>
       </c>
@@ -48298,7 +48298,7 @@
         <f>+BT3+BU3+BV3+BW3+BX3</f>
         <v>18</v>
       </c>
-      <c r="BZ3" s="624">
+      <c r="BZ3" s="597">
         <f>+IFERROR(BY4/BY3,0)</f>
         <v>203.5</v>
       </c>
@@ -48306,7 +48306,7 @@
         <f>+R3+W3+AB3+AH3+AM3+AR3+AX3+BC3+BH3+BN3+BS3+BY3</f>
         <v>164</v>
       </c>
-      <c r="CB3" s="617">
+      <c r="CB3" s="590">
         <f>+CA4/CA3</f>
         <v>266.19512195121951</v>
       </c>
@@ -48322,10 +48322,10 @@
         <v>9025</v>
       </c>
     </row>
-    <row r="4" spans="2:92" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B4" s="619"/>
-      <c r="C4" s="621"/>
-      <c r="D4" s="623"/>
+    <row r="4" spans="2:92" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="592"/>
+      <c r="C4" s="594"/>
+      <c r="D4" s="596"/>
       <c r="E4" s="252" t="s">
         <v>13</v>
       </c>
@@ -48354,7 +48354,7 @@
         <f t="shared" ref="L4:L23" si="2">+SUM(I4:K4)</f>
         <v>9925</v>
       </c>
-      <c r="M4" s="625"/>
+      <c r="M4" s="598"/>
       <c r="N4" s="253">
         <v>200</v>
       </c>
@@ -48567,12 +48567,12 @@
         <f t="shared" ref="BY4:BY14" si="5">+BT4+BU4+BV4+BW4+BX4</f>
         <v>3663</v>
       </c>
-      <c r="BZ4" s="625"/>
+      <c r="BZ4" s="598"/>
       <c r="CA4" s="289">
         <f t="shared" ref="CA4:CA14" si="6">+R4+W4+AB4+AH4+AM4+AR4+AX4+BC4+BH4+BN4+BS4+BY4</f>
         <v>43656</v>
       </c>
-      <c r="CB4" s="618"/>
+      <c r="CB4" s="591"/>
       <c r="CC4" s="231">
         <f>+AVERAGE(R4,W4,AB4,AH4,AM4,AR4,AX4,BC4,BH4,BN4,BS4)</f>
         <v>3635.7272727272725</v>
@@ -48596,14 +48596,14 @@
         <v>822</v>
       </c>
     </row>
-    <row r="5" spans="2:92" ht="18.600000000000001" customHeight="1">
-      <c r="B5" s="619" t="s">
+    <row r="5" spans="2:92" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="592" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="620">
+      <c r="C5" s="593">
         <v>2</v>
       </c>
-      <c r="D5" s="622" t="s">
+      <c r="D5" s="595" t="s">
         <v>221</v>
       </c>
       <c r="E5" s="261" t="s">
@@ -48631,7 +48631,7 @@
         <f>+SUM(I5:K5)</f>
         <v>18</v>
       </c>
-      <c r="M5" s="624">
+      <c r="M5" s="597">
         <f>+L6/L5</f>
         <v>181.66666666666666</v>
       </c>
@@ -48837,7 +48837,7 @@
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
-      <c r="BZ5" s="624">
+      <c r="BZ5" s="597">
         <f>+IFERROR(BY6/BY5,0)</f>
         <v>186.57142857142858</v>
       </c>
@@ -48845,7 +48845,7 @@
         <f t="shared" si="6"/>
         <v>78</v>
       </c>
-      <c r="CB5" s="617">
+      <c r="CB5" s="590">
         <f>+CA6/CA5</f>
         <v>131.74358974358975</v>
       </c>
@@ -48864,10 +48864,10 @@
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="2:92" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B6" s="619"/>
-      <c r="C6" s="621"/>
-      <c r="D6" s="623"/>
+    <row r="6" spans="2:92" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="592"/>
+      <c r="C6" s="594"/>
+      <c r="D6" s="596"/>
       <c r="E6" s="252" t="s">
         <v>13</v>
       </c>
@@ -48895,7 +48895,7 @@
         <f t="shared" si="2"/>
         <v>3270</v>
       </c>
-      <c r="M6" s="625"/>
+      <c r="M6" s="598"/>
       <c r="N6" s="268">
         <v>690</v>
       </c>
@@ -49103,12 +49103,12 @@
         <f t="shared" si="5"/>
         <v>1306</v>
       </c>
-      <c r="BZ6" s="625"/>
+      <c r="BZ6" s="598"/>
       <c r="CA6" s="289">
         <f t="shared" si="6"/>
         <v>10276</v>
       </c>
-      <c r="CB6" s="618"/>
+      <c r="CB6" s="591"/>
       <c r="CC6" s="231">
         <f>+AVERAGE(R6,W6,AB6,AH6,AM6,AR6,AX6,BC6,BH6,BN6,BS6)</f>
         <v>815.4545454545455</v>
@@ -49132,14 +49132,14 @@
         <v>981</v>
       </c>
     </row>
-    <row r="7" spans="2:92" ht="18.600000000000001" customHeight="1">
-      <c r="B7" s="619" t="s">
+    <row r="7" spans="2:92" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="592" t="s">
         <v>222</v>
       </c>
-      <c r="C7" s="620">
+      <c r="C7" s="593">
         <v>3</v>
       </c>
-      <c r="D7" s="622" t="s">
+      <c r="D7" s="595" t="s">
         <v>286</v>
       </c>
       <c r="E7" s="261" t="s">
@@ -49161,7 +49161,7 @@
         <f t="shared" si="2"/>
         <v>61</v>
       </c>
-      <c r="M7" s="624">
+      <c r="M7" s="597">
         <f>+L8/L7</f>
         <v>31.950819672131146</v>
       </c>
@@ -49369,7 +49369,7 @@
         <f t="shared" si="5"/>
         <v>11</v>
       </c>
-      <c r="BZ7" s="624">
+      <c r="BZ7" s="597">
         <f>+IFERROR(BY8/BY7,0)</f>
         <v>38.454545454545453</v>
       </c>
@@ -49377,7 +49377,7 @@
         <f t="shared" si="6"/>
         <v>222</v>
       </c>
-      <c r="CB7" s="617">
+      <c r="CB7" s="590">
         <f>+CA8/CA7</f>
         <v>40.707207207207205</v>
       </c>
@@ -49390,10 +49390,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:92" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B8" s="619"/>
-      <c r="C8" s="621"/>
-      <c r="D8" s="623"/>
+    <row r="8" spans="2:92" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="592"/>
+      <c r="C8" s="594"/>
+      <c r="D8" s="596"/>
       <c r="E8" s="252" t="s">
         <v>13</v>
       </c>
@@ -49413,7 +49413,7 @@
         <f t="shared" si="2"/>
         <v>1949</v>
       </c>
-      <c r="M8" s="625"/>
+      <c r="M8" s="598"/>
       <c r="N8" s="253">
         <v>762</v>
       </c>
@@ -49619,12 +49619,12 @@
         <f t="shared" si="5"/>
         <v>423</v>
       </c>
-      <c r="BZ8" s="625"/>
+      <c r="BZ8" s="598"/>
       <c r="CA8" s="289">
         <f t="shared" si="6"/>
         <v>9037</v>
       </c>
-      <c r="CB8" s="618"/>
+      <c r="CB8" s="591"/>
       <c r="CC8" s="231">
         <f>+AVERAGE(R8,W8,AB8,AH8,AM8,AR8,AX8,BC8,BH8,BN8,BS8)</f>
         <v>783.09090909090912</v>
@@ -49637,14 +49637,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:92" ht="18.600000000000001" customHeight="1">
-      <c r="B9" s="619" t="s">
+    <row r="9" spans="2:92" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="592" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="620">
+      <c r="C9" s="593">
         <v>4</v>
       </c>
-      <c r="D9" s="626" t="s">
+      <c r="D9" s="599" t="s">
         <v>287</v>
       </c>
       <c r="E9" s="261" t="s">
@@ -49666,7 +49666,7 @@
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="M9" s="624">
+      <c r="M9" s="597">
         <f>+L10/L9</f>
         <v>34.384615384615387</v>
       </c>
@@ -49880,7 +49880,7 @@
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="BZ9" s="624">
+      <c r="BZ9" s="597">
         <f>+IFERROR(BY10/BY9,0)</f>
         <v>47</v>
       </c>
@@ -49888,7 +49888,7 @@
         <f t="shared" si="6"/>
         <v>204</v>
       </c>
-      <c r="CB9" s="617">
+      <c r="CB9" s="590">
         <f>+CA10/CA9</f>
         <v>45.849955882352937</v>
       </c>
@@ -49901,10 +49901,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:92" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B10" s="619"/>
-      <c r="C10" s="621"/>
-      <c r="D10" s="623"/>
+    <row r="10" spans="2:92" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="592"/>
+      <c r="C10" s="594"/>
+      <c r="D10" s="596"/>
       <c r="E10" s="252" t="s">
         <v>13</v>
       </c>
@@ -49925,7 +49925,7 @@
         <f t="shared" si="2"/>
         <v>1788</v>
       </c>
-      <c r="M10" s="625"/>
+      <c r="M10" s="598"/>
       <c r="N10" s="253">
         <v>0</v>
       </c>
@@ -50140,12 +50140,12 @@
         <f t="shared" si="5"/>
         <v>611</v>
       </c>
-      <c r="BZ10" s="625"/>
+      <c r="BZ10" s="598"/>
       <c r="CA10" s="289">
         <f t="shared" si="6"/>
         <v>9353.3909999999996</v>
       </c>
-      <c r="CB10" s="618"/>
+      <c r="CB10" s="591"/>
       <c r="CC10" s="231">
         <f>+AVERAGE(R10,W10,AB10,AH10,AM10,AR10,AX10,BC10,BH10,BN10,BS10,BY10)</f>
         <v>779.44925000000001</v>
@@ -50158,14 +50158,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:92" ht="18.600000000000001" customHeight="1">
-      <c r="B11" s="631" t="s">
+    <row r="11" spans="2:92" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="604" t="s">
         <v>224</v>
       </c>
-      <c r="C11" s="620">
+      <c r="C11" s="593">
         <v>5</v>
       </c>
-      <c r="D11" s="633" t="s">
+      <c r="D11" s="606" t="s">
         <v>288</v>
       </c>
       <c r="E11" s="272" t="s">
@@ -50187,7 +50187,7 @@
         <f t="shared" si="2"/>
         <v>58</v>
       </c>
-      <c r="M11" s="624">
+      <c r="M11" s="597">
         <f>+L12/L11</f>
         <v>32.379310344827587</v>
       </c>
@@ -50398,7 +50398,7 @@
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-      <c r="BZ11" s="624">
+      <c r="BZ11" s="597">
         <f>+IFERROR(BY12/BY11,0)</f>
         <v>42.19047619047619</v>
       </c>
@@ -50406,7 +50406,7 @@
         <f t="shared" si="6"/>
         <v>219</v>
       </c>
-      <c r="CB11" s="617">
+      <c r="CB11" s="590">
         <f>+CA12/CA11</f>
         <v>44.726027397260275</v>
       </c>
@@ -50426,10 +50426,10 @@
       <c r="CM11" s="233"/>
       <c r="CN11" s="233"/>
     </row>
-    <row r="12" spans="2:92" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B12" s="632"/>
-      <c r="C12" s="621"/>
-      <c r="D12" s="634"/>
+    <row r="12" spans="2:92" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="605"/>
+      <c r="C12" s="594"/>
+      <c r="D12" s="607"/>
       <c r="E12" s="251" t="s">
         <v>13</v>
       </c>
@@ -50449,7 +50449,7 @@
         <f t="shared" si="2"/>
         <v>1878</v>
       </c>
-      <c r="M12" s="625"/>
+      <c r="M12" s="598"/>
       <c r="N12" s="268">
         <v>427</v>
       </c>
@@ -50656,12 +50656,12 @@
         <f t="shared" si="5"/>
         <v>886</v>
       </c>
-      <c r="BZ12" s="625"/>
+      <c r="BZ12" s="598"/>
       <c r="CA12" s="289">
         <f t="shared" si="6"/>
         <v>9795</v>
       </c>
-      <c r="CB12" s="618"/>
+      <c r="CB12" s="591"/>
       <c r="CC12" s="231">
         <f>+AVERAGE(R12,W12,AB12,AH12,AM12,AR12,AX12,BC12,BH12,BN12,BS12)</f>
         <v>809.90909090909088</v>
@@ -50674,14 +50674,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:92" ht="18.600000000000001" customHeight="1">
-      <c r="B13" s="631" t="s">
+    <row r="13" spans="2:92" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="604" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="620">
+      <c r="C13" s="593">
         <v>6</v>
       </c>
-      <c r="D13" s="633" t="s">
+      <c r="D13" s="606" t="s">
         <v>289</v>
       </c>
       <c r="E13" s="261" t="s">
@@ -50703,7 +50703,7 @@
         <f>+SUM(I13:K13)</f>
         <v>55</v>
       </c>
-      <c r="M13" s="624">
+      <c r="M13" s="597">
         <f>+L14/L13</f>
         <v>38.109090909090909</v>
       </c>
@@ -50915,7 +50915,7 @@
         <f t="shared" si="5"/>
         <v>17</v>
       </c>
-      <c r="BZ13" s="624">
+      <c r="BZ13" s="597">
         <f>+IFERROR(BY14/BY13,0)</f>
         <v>47.882352941176471</v>
       </c>
@@ -50923,7 +50923,7 @@
         <f t="shared" si="6"/>
         <v>216</v>
       </c>
-      <c r="CB13" s="617">
+      <c r="CB13" s="590">
         <f>+CA14/CA13</f>
         <v>41.782407407407405</v>
       </c>
@@ -50936,10 +50936,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:92" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B14" s="632"/>
-      <c r="C14" s="621"/>
-      <c r="D14" s="634"/>
+    <row r="14" spans="2:92" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="605"/>
+      <c r="C14" s="594"/>
+      <c r="D14" s="607"/>
       <c r="E14" s="252" t="s">
         <v>13</v>
       </c>
@@ -50959,7 +50959,7 @@
         <f>+SUM(I14:K14)</f>
         <v>2096</v>
       </c>
-      <c r="M14" s="625"/>
+      <c r="M14" s="598"/>
       <c r="N14" s="253">
         <v>197</v>
       </c>
@@ -51168,12 +51168,12 @@
         <f t="shared" si="5"/>
         <v>814</v>
       </c>
-      <c r="BZ14" s="625"/>
+      <c r="BZ14" s="598"/>
       <c r="CA14" s="289">
         <f t="shared" si="6"/>
         <v>9025</v>
       </c>
-      <c r="CB14" s="618"/>
+      <c r="CB14" s="591"/>
       <c r="CC14" s="231">
         <f>+AVERAGE(R14,W14,AB14,AH14,AM14,AR14,AX14,BC14,BH14,BN14,BS14)</f>
         <v>746.4545454545455</v>
@@ -51186,7 +51186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:92" s="234" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1">
+    <row r="15" spans="2:92" s="234" customFormat="1" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="250" t="s">
         <v>224</v>
       </c>
@@ -51322,7 +51322,7 @@
       <c r="CE15" s="235"/>
       <c r="CF15" s="235"/>
     </row>
-    <row r="16" spans="2:92" ht="18.600000000000001" customHeight="1" thickBot="1">
+    <row r="16" spans="2:92" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="249" t="s">
         <v>222</v>
       </c>
@@ -51580,7 +51580,7 @@
       </c>
       <c r="CD16" s="237"/>
     </row>
-    <row r="17" spans="2:91" ht="18.600000000000001" customHeight="1" thickBot="1">
+    <row r="17" spans="2:91" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="249" t="s">
         <v>222</v>
       </c>
@@ -51818,14 +51818,14 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="18" spans="2:91" ht="18.600000000000001" customHeight="1">
-      <c r="B18" s="631" t="s">
+    <row r="18" spans="2:91" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="604" t="s">
         <v>222</v>
       </c>
-      <c r="C18" s="620">
+      <c r="C18" s="593">
         <v>10</v>
       </c>
-      <c r="D18" s="633" t="s">
+      <c r="D18" s="606" t="s">
         <v>290</v>
       </c>
       <c r="E18" s="272" t="s">
@@ -51966,7 +51966,7 @@
         <f t="shared" si="17"/>
         <v>9</v>
       </c>
-      <c r="BZ18" s="624">
+      <c r="BZ18" s="597">
         <f>+IFERROR(BY19/BY18,0)</f>
         <v>27.222222222222221</v>
       </c>
@@ -51974,7 +51974,7 @@
         <f t="shared" ref="CA18:CA27" si="20">+BY18</f>
         <v>9</v>
       </c>
-      <c r="CB18" s="617">
+      <c r="CB18" s="590">
         <f>+IFERROR(CA19/CA18,0)</f>
         <v>27.222222222222221</v>
       </c>
@@ -51982,10 +51982,10 @@
       <c r="CD18" s="231"/>
       <c r="CE18" s="231"/>
     </row>
-    <row r="19" spans="2:91" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B19" s="632"/>
-      <c r="C19" s="621"/>
-      <c r="D19" s="634"/>
+    <row r="19" spans="2:91" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="605"/>
+      <c r="C19" s="594"/>
+      <c r="D19" s="607"/>
       <c r="E19" s="251" t="s">
         <v>13</v>
       </c>
@@ -52124,24 +52124,24 @@
         <f t="shared" si="21"/>
         <v>245</v>
       </c>
-      <c r="BZ19" s="625"/>
+      <c r="BZ19" s="598"/>
       <c r="CA19" s="289">
         <f t="shared" si="20"/>
         <v>245</v>
       </c>
-      <c r="CB19" s="618"/>
+      <c r="CB19" s="591"/>
       <c r="CC19" s="231"/>
       <c r="CD19" s="231"/>
       <c r="CE19" s="231"/>
     </row>
-    <row r="20" spans="2:91" ht="18.600000000000001" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B20" s="648" t="s">
+    <row r="20" spans="2:91" ht="18.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="621" t="s">
         <v>222</v>
       </c>
-      <c r="C20" s="650" t="s">
+      <c r="C20" s="623" t="s">
         <v>291</v>
       </c>
-      <c r="D20" s="652" t="s">
+      <c r="D20" s="625" t="s">
         <v>292</v>
       </c>
       <c r="E20" s="293" t="s">
@@ -52154,7 +52154,7 @@
       <c r="J20" s="294"/>
       <c r="K20" s="294"/>
       <c r="L20" s="294"/>
-      <c r="M20" s="627">
+      <c r="M20" s="600">
         <v>0</v>
       </c>
       <c r="N20" s="294">
@@ -52361,7 +52361,7 @@
         <f>+BX20</f>
         <v>3</v>
       </c>
-      <c r="BZ20" s="629">
+      <c r="BZ20" s="602">
         <f>+IFERROR(BY21/BY20,0)</f>
         <v>28.666666666666668</v>
       </c>
@@ -52369,16 +52369,16 @@
         <f t="shared" si="20"/>
         <v>3</v>
       </c>
-      <c r="CB20" s="635">
+      <c r="CB20" s="608">
         <f>+CA21/CA20</f>
         <v>28.666666666666668</v>
       </c>
       <c r="CC20" s="231"/>
     </row>
-    <row r="21" spans="2:91" ht="18.600000000000001" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B21" s="649"/>
-      <c r="C21" s="651"/>
-      <c r="D21" s="653"/>
+    <row r="21" spans="2:91" ht="18.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="622"/>
+      <c r="C21" s="624"/>
+      <c r="D21" s="626"/>
       <c r="E21" s="242" t="s">
         <v>13</v>
       </c>
@@ -52389,7 +52389,7 @@
       <c r="J21" s="243"/>
       <c r="K21" s="243"/>
       <c r="L21" s="243"/>
-      <c r="M21" s="628"/>
+      <c r="M21" s="601"/>
       <c r="N21" s="243">
         <v>192</v>
       </c>
@@ -52594,23 +52594,23 @@
         <f t="shared" ref="BY21:BY23" si="26">+BX21</f>
         <v>86</v>
       </c>
-      <c r="BZ21" s="630"/>
+      <c r="BZ21" s="603"/>
       <c r="CA21" s="244">
         <f t="shared" si="20"/>
         <v>86</v>
       </c>
-      <c r="CB21" s="636"/>
+      <c r="CB21" s="609"/>
       <c r="CC21" s="231"/>
       <c r="CM21" s="238"/>
     </row>
-    <row r="22" spans="2:91" ht="18.600000000000001" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B22" s="637" t="s">
+    <row r="22" spans="2:91" ht="18.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="610" t="s">
         <v>222</v>
       </c>
-      <c r="C22" s="638" t="s">
+      <c r="C22" s="611" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="640" t="s">
+      <c r="D22" s="613" t="s">
         <v>231</v>
       </c>
       <c r="E22" s="245" t="s">
@@ -52630,7 +52630,7 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="M22" s="642">
+      <c r="M22" s="615">
         <f>+L23/L22</f>
         <v>23.5</v>
       </c>
@@ -52840,7 +52840,7 @@
         <f t="shared" si="26"/>
         <v>6</v>
       </c>
-      <c r="BZ22" s="644">
+      <c r="BZ22" s="617">
         <f>+IFERROR(BY23/BY22,0)</f>
         <v>26.5</v>
       </c>
@@ -52848,16 +52848,16 @@
         <f t="shared" si="20"/>
         <v>6</v>
       </c>
-      <c r="CB22" s="646">
+      <c r="CB22" s="619">
         <f>+CA23/CA22</f>
         <v>26.5</v>
       </c>
       <c r="CC22" s="231"/>
     </row>
-    <row r="23" spans="2:91" ht="18.600000000000001" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="B23" s="637"/>
-      <c r="C23" s="639"/>
-      <c r="D23" s="641"/>
+    <row r="23" spans="2:91" ht="18.5" hidden="1" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="610"/>
+      <c r="C23" s="612"/>
+      <c r="D23" s="614"/>
       <c r="E23" s="296" t="s">
         <v>13</v>
       </c>
@@ -52875,7 +52875,7 @@
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
-      <c r="M23" s="643"/>
+      <c r="M23" s="616"/>
       <c r="N23" s="297">
         <v>70</v>
       </c>
@@ -53086,23 +53086,23 @@
         <f t="shared" si="26"/>
         <v>159</v>
       </c>
-      <c r="BZ23" s="645"/>
+      <c r="BZ23" s="618"/>
       <c r="CA23" s="298">
         <f t="shared" si="20"/>
         <v>159</v>
       </c>
-      <c r="CB23" s="647"/>
+      <c r="CB23" s="620"/>
       <c r="CC23" s="231"/>
       <c r="CE23" s="239"/>
     </row>
-    <row r="24" spans="2:91" ht="18.600000000000001" customHeight="1" collapsed="1">
-      <c r="B24" s="631" t="s">
+    <row r="24" spans="2:91" ht="18.5" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="604" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="660">
+      <c r="C24" s="633">
         <v>11</v>
       </c>
-      <c r="D24" s="661" t="s">
+      <c r="D24" s="634" t="s">
         <v>294</v>
       </c>
       <c r="E24" s="271" t="s">
@@ -53115,7 +53115,7 @@
       <c r="J24" s="256"/>
       <c r="K24" s="256"/>
       <c r="L24" s="256"/>
-      <c r="M24" s="662"/>
+      <c r="M24" s="635"/>
       <c r="N24" s="232"/>
       <c r="O24" s="232"/>
       <c r="P24" s="232"/>
@@ -53211,7 +53211,7 @@
         <f>+BX24</f>
         <v>26</v>
       </c>
-      <c r="BZ24" s="662">
+      <c r="BZ24" s="635">
         <f>+IFERROR(BY25/BY24,0)</f>
         <v>56.230769230769234</v>
       </c>
@@ -53219,15 +53219,15 @@
         <f t="shared" si="20"/>
         <v>26</v>
       </c>
-      <c r="CB24" s="654">
+      <c r="CB24" s="627">
         <f>+IFERROR(CA25/CA24,0)</f>
         <v>56.230769230769234</v>
       </c>
     </row>
-    <row r="25" spans="2:91" ht="18.600000000000001" customHeight="1" thickBot="1">
-      <c r="B25" s="632"/>
-      <c r="C25" s="621"/>
-      <c r="D25" s="634"/>
+    <row r="25" spans="2:91" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="605"/>
+      <c r="C25" s="594"/>
+      <c r="D25" s="607"/>
       <c r="E25" s="251" t="s">
         <v>13</v>
       </c>
@@ -53238,7 +53238,7 @@
       <c r="J25" s="253"/>
       <c r="K25" s="253"/>
       <c r="L25" s="253"/>
-      <c r="M25" s="625"/>
+      <c r="M25" s="598"/>
       <c r="N25" s="309"/>
       <c r="O25" s="309"/>
       <c r="P25" s="309"/>
@@ -53334,21 +53334,21 @@
         <f t="shared" ref="BY25:BY27" si="27">+BX25</f>
         <v>1462</v>
       </c>
-      <c r="BZ25" s="625"/>
+      <c r="BZ25" s="598"/>
       <c r="CA25" s="289">
         <f t="shared" si="20"/>
         <v>1462</v>
       </c>
-      <c r="CB25" s="618"/>
+      <c r="CB25" s="591"/>
     </row>
-    <row r="26" spans="2:91" ht="18.600000000000001" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B26" s="637" t="s">
+    <row r="26" spans="2:91" ht="18.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="610" t="s">
         <v>224</v>
       </c>
-      <c r="C26" s="656" t="s">
+      <c r="C26" s="629" t="s">
         <v>295</v>
       </c>
-      <c r="D26" s="657" t="s">
+      <c r="D26" s="630" t="s">
         <v>32</v>
       </c>
       <c r="E26" s="299" t="s">
@@ -53366,7 +53366,7 @@
         <f t="shared" ref="L26:L27" si="28">+SUM(I26:K26)</f>
         <v>8</v>
       </c>
-      <c r="M26" s="659">
+      <c r="M26" s="632">
         <f>+L27/L26</f>
         <v>35.75</v>
       </c>
@@ -53574,7 +53574,7 @@
         <f t="shared" si="27"/>
         <v>11</v>
       </c>
-      <c r="BZ26" s="644">
+      <c r="BZ26" s="617">
         <f>+IFERROR(BY27/BY26,0)</f>
         <v>74.727272727272734</v>
       </c>
@@ -53582,17 +53582,17 @@
         <f t="shared" si="20"/>
         <v>11</v>
       </c>
-      <c r="CB26" s="646">
+      <c r="CB26" s="619">
         <f>+IFERROR(CA27/CA26,0)</f>
         <v>74.727272727272734</v>
       </c>
       <c r="CC26" s="231"/>
       <c r="CD26" s="231"/>
     </row>
-    <row r="27" spans="2:91" ht="18.600000000000001" hidden="1" customHeight="1" outlineLevel="1" thickBot="1">
-      <c r="B27" s="655"/>
-      <c r="C27" s="639"/>
-      <c r="D27" s="658"/>
+    <row r="27" spans="2:91" ht="18.5" hidden="1" customHeight="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="628"/>
+      <c r="C27" s="612"/>
+      <c r="D27" s="631"/>
       <c r="E27" s="296" t="s">
         <v>35</v>
       </c>
@@ -53608,7 +53608,7 @@
         <f t="shared" si="28"/>
         <v>286</v>
       </c>
-      <c r="M27" s="645"/>
+      <c r="M27" s="618"/>
       <c r="N27" s="297">
         <v>110</v>
       </c>
@@ -53814,20 +53814,20 @@
         <f t="shared" si="27"/>
         <v>822</v>
       </c>
-      <c r="BZ27" s="645"/>
+      <c r="BZ27" s="618"/>
       <c r="CA27" s="297">
         <f t="shared" si="20"/>
         <v>822</v>
       </c>
-      <c r="CB27" s="647"/>
+      <c r="CB27" s="620"/>
       <c r="CC27" s="231"/>
       <c r="CD27" s="240"/>
     </row>
-    <row r="28" spans="2:91" collapsed="1"/>
-    <row r="30" spans="2:91">
+    <row r="28" spans="2:91" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:91" x14ac:dyDescent="0.2">
       <c r="CA30" s="231"/>
     </row>
-    <row r="31" spans="2:91">
+    <row r="31" spans="2:91" x14ac:dyDescent="0.2">
       <c r="AC31" s="230">
         <v>2</v>
       </c>
@@ -53842,7 +53842,7 @@
       </c>
       <c r="CA31" s="237"/>
     </row>
-    <row r="32" spans="2:91">
+    <row r="32" spans="2:91" x14ac:dyDescent="0.2">
       <c r="R32" s="231"/>
       <c r="S32" s="231"/>
       <c r="T32" s="231"/>
@@ -53897,7 +53897,7 @@
       <c r="CA32" s="231"/>
       <c r="CB32" s="231"/>
     </row>
-    <row r="33" spans="18:89">
+    <row r="33" spans="18:89" x14ac:dyDescent="0.15">
       <c r="R33" s="231"/>
       <c r="S33" s="231"/>
       <c r="T33" s="231"/>
@@ -53967,7 +53967,7 @@
       <c r="CB33" s="349"/>
       <c r="CC33" s="349"/>
     </row>
-    <row r="34" spans="18:89">
+    <row r="34" spans="18:89" x14ac:dyDescent="0.15">
       <c r="BU34" s="340" t="s">
         <v>298</v>
       </c>
@@ -53983,7 +53983,7 @@
       <c r="CC34" s="349"/>
       <c r="CK34" s="231"/>
     </row>
-    <row r="35" spans="18:89">
+    <row r="35" spans="18:89" x14ac:dyDescent="0.2">
       <c r="CF35" s="231"/>
       <c r="CG35" s="231"/>
       <c r="CH35" s="231"/>
@@ -53991,7 +53991,7 @@
       <c r="CJ35" s="231"/>
       <c r="CK35" s="231"/>
     </row>
-    <row r="36" spans="18:89">
+    <row r="36" spans="18:89" x14ac:dyDescent="0.2">
       <c r="AO36" s="230">
         <f>6677-6537</f>
         <v>140</v>
@@ -54079,59 +54079,59 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="B1:CH35"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="13.15" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="12" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="230" customWidth="1"/>
-    <col min="2" max="2" width="6.85546875" style="230" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.140625" style="230" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" style="230" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="230" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="9.140625" style="230" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="11" width="8.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="16" width="9.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="2.6640625" style="230" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" style="230" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="230" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1640625" style="230" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="9.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="8.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="16" width="9.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
     <col min="19" max="21" width="9" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="22" max="22" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="27" width="11.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="28" max="28" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="29" max="32" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="33" max="33" width="10.85546875" style="230" customWidth="1" collapsed="1"/>
-    <col min="34" max="37" width="10.85546875" style="230" customWidth="1" outlineLevel="1"/>
-    <col min="38" max="38" width="10.85546875" style="230" customWidth="1"/>
-    <col min="39" max="43" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="44" max="44" width="10.85546875" style="230" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="45" max="48" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="49" max="49" width="10.85546875" style="230" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="50" max="53" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="54" max="54" width="10.85546875" style="230" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="55" max="59" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="60" max="60" width="10.85546875" style="230" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="61" max="61" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="62" max="64" width="11.140625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="65" max="65" width="10.85546875" style="230" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="66" max="70" width="10.85546875" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="71" max="71" width="8.140625" style="230" hidden="1" customWidth="1" collapsed="1"/>
-    <col min="72" max="72" width="10.140625" style="230" customWidth="1"/>
-    <col min="73" max="73" width="10.140625" style="230" bestFit="1" customWidth="1"/>
-    <col min="74" max="74" width="10.85546875" style="230" customWidth="1"/>
+    <col min="22" max="22" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="27" width="11.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="28" max="28" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="29" max="32" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="33" width="10.83203125" style="230" customWidth="1" collapsed="1"/>
+    <col min="34" max="37" width="10.83203125" style="230" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="10.83203125" style="230" customWidth="1"/>
+    <col min="39" max="43" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="10.83203125" style="230" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="45" max="48" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="49" max="49" width="10.83203125" style="230" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="50" max="53" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="54" max="54" width="10.83203125" style="230" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="55" max="59" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="60" max="60" width="10.83203125" style="230" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="61" max="61" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="62" max="64" width="11.1640625" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="65" max="65" width="10.83203125" style="230" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="66" max="70" width="10.83203125" style="230" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="71" max="71" width="8.1640625" style="230" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="72" max="72" width="10.1640625" style="230" customWidth="1"/>
+    <col min="73" max="73" width="10.1640625" style="230" bestFit="1" customWidth="1"/>
+    <col min="74" max="74" width="10.83203125" style="230" customWidth="1"/>
     <col min="75" max="75" width="12" style="230" bestFit="1" customWidth="1"/>
-    <col min="76" max="76" width="13.85546875" style="230" bestFit="1" customWidth="1"/>
-    <col min="77" max="78" width="11.5703125" style="230"/>
-    <col min="79" max="79" width="17.85546875" style="230" bestFit="1" customWidth="1"/>
-    <col min="80" max="81" width="11.5703125" style="230"/>
+    <col min="76" max="76" width="13.83203125" style="230" bestFit="1" customWidth="1"/>
+    <col min="77" max="78" width="11.5" style="230"/>
+    <col min="79" max="79" width="17.83203125" style="230" bestFit="1" customWidth="1"/>
+    <col min="80" max="81" width="11.5" style="230"/>
     <col min="82" max="82" width="12" style="230" bestFit="1" customWidth="1"/>
-    <col min="83" max="16384" width="11.5703125" style="230"/>
+    <col min="83" max="16384" width="11.5" style="230"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:86">
+    <row r="1" spans="2:86" x14ac:dyDescent="0.2">
       <c r="AC1" s="231"/>
     </row>
-    <row r="2" spans="2:86" ht="29.85" customHeight="1" thickBot="1">
+    <row r="2" spans="2:86" ht="29.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="523" t="s">
         <v>178</v>
       </c>
@@ -54365,14 +54365,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B3" s="559" t="s">
+    <row r="3" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="659" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="560">
+      <c r="C3" s="660">
         <v>1</v>
       </c>
-      <c r="D3" s="561" t="s">
+      <c r="D3" s="661" t="s">
         <v>220</v>
       </c>
       <c r="E3" s="374" t="s">
@@ -54381,7 +54381,7 @@
       <c r="F3" s="379">
         <v>164</v>
       </c>
-      <c r="G3" s="562">
+      <c r="G3" s="662">
         <f>+F4/F3</f>
         <v>266.19512195121951</v>
       </c>
@@ -54511,7 +54511,7 @@
         <f>+BN3+BO3+BP3+BQ3+BR3</f>
         <v>0</v>
       </c>
-      <c r="BT3" s="563">
+      <c r="BT3" s="663">
         <f>+IFERROR(AL4/AL3,0)</f>
         <v>959.75866666666661</v>
       </c>
@@ -54519,7 +54519,7 @@
         <f t="shared" ref="BU3:BU15" si="3">+L3+Q3+V3+AB3+AG3+AL3</f>
         <v>86</v>
       </c>
-      <c r="BV3" s="564">
+      <c r="BV3" s="664">
         <f>+IFERROR(BU4/BU3,0)</f>
         <v>221.94140697674419</v>
       </c>
@@ -54536,17 +54536,17 @@
         <v>0.58245299910474491</v>
       </c>
     </row>
-    <row r="4" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B4" s="548"/>
-      <c r="C4" s="550"/>
-      <c r="D4" s="552"/>
+    <row r="4" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="648"/>
+      <c r="C4" s="650"/>
+      <c r="D4" s="652"/>
       <c r="E4" s="375" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="380">
         <v>43656</v>
       </c>
-      <c r="G4" s="554"/>
+      <c r="G4" s="654"/>
       <c r="H4" s="363"/>
       <c r="I4" s="363"/>
       <c r="J4" s="363"/>
@@ -54673,12 +54673,12 @@
         <f t="shared" ref="BS4:BS14" si="6">+BN4+BO4+BP4+BQ4+BR4</f>
         <v>0</v>
       </c>
-      <c r="BT4" s="556"/>
+      <c r="BT4" s="656"/>
       <c r="BU4" s="402">
         <f t="shared" si="3"/>
         <v>19086.960999999999</v>
       </c>
-      <c r="BV4" s="546"/>
+      <c r="BV4" s="646"/>
       <c r="BW4" s="521">
         <v>1683</v>
       </c>
@@ -54703,14 +54703,14 @@
         <v>0.27162041181736796</v>
       </c>
     </row>
-    <row r="5" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B5" s="557" t="s">
+    <row r="5" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="657" t="s">
         <v>219</v>
       </c>
-      <c r="C5" s="549">
+      <c r="C5" s="649">
         <v>2</v>
       </c>
-      <c r="D5" s="558" t="s">
+      <c r="D5" s="658" t="s">
         <v>221</v>
       </c>
       <c r="E5" s="376" t="s">
@@ -54719,7 +54719,7 @@
       <c r="F5" s="381">
         <v>78</v>
       </c>
-      <c r="G5" s="553">
+      <c r="G5" s="653">
         <f>+F6/F5</f>
         <v>131.74358974358975</v>
       </c>
@@ -54849,7 +54849,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT5" s="555">
+      <c r="BT5" s="655">
         <f>+IFERROR(AL6/AL5,0)</f>
         <v>0</v>
       </c>
@@ -54857,7 +54857,7 @@
         <f t="shared" si="3"/>
         <v>34</v>
       </c>
-      <c r="BV5" s="545">
+      <c r="BV5" s="645">
         <f>+IFERROR(BU6/BU5,0)</f>
         <v>119.14470588235294</v>
       </c>
@@ -54878,17 +54878,17 @@
         <v>0.14592658907788719</v>
       </c>
     </row>
-    <row r="6" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B6" s="548"/>
-      <c r="C6" s="550"/>
-      <c r="D6" s="552"/>
+    <row r="6" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="648"/>
+      <c r="C6" s="650"/>
+      <c r="D6" s="652"/>
       <c r="E6" s="375" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="380">
         <v>10276</v>
       </c>
-      <c r="G6" s="554"/>
+      <c r="G6" s="654"/>
       <c r="H6" s="363"/>
       <c r="I6" s="363"/>
       <c r="J6" s="363"/>
@@ -55015,12 +55015,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT6" s="556"/>
+      <c r="BT6" s="656"/>
       <c r="BU6" s="402">
         <f t="shared" si="3"/>
         <v>4050.92</v>
       </c>
-      <c r="BV6" s="546"/>
+      <c r="BV6" s="646"/>
       <c r="BW6" s="231"/>
       <c r="BX6" s="231"/>
       <c r="BY6" s="231"/>
@@ -55036,14 +55036,14 @@
         <v>261</v>
       </c>
     </row>
-    <row r="7" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B7" s="557" t="s">
+    <row r="7" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B7" s="657" t="s">
         <v>222</v>
       </c>
-      <c r="C7" s="549">
+      <c r="C7" s="649">
         <v>3</v>
       </c>
-      <c r="D7" s="558" t="s">
+      <c r="D7" s="658" t="s">
         <v>286</v>
       </c>
       <c r="E7" s="376" t="s">
@@ -55052,7 +55052,7 @@
       <c r="F7" s="381">
         <v>222</v>
       </c>
-      <c r="G7" s="553">
+      <c r="G7" s="653">
         <f>+F8/F7</f>
         <v>40.707207207207205</v>
       </c>
@@ -55183,7 +55183,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT7" s="555">
+      <c r="BT7" s="655">
         <f>+IFERROR(AL8/AL7,0)</f>
         <v>47.384615384615387</v>
       </c>
@@ -55191,7 +55191,7 @@
         <f t="shared" si="3"/>
         <v>109</v>
       </c>
-      <c r="BV7" s="545">
+      <c r="BV7" s="645">
         <f>+IFERROR(BU8/BU7,0)</f>
         <v>38.592742213529554</v>
       </c>
@@ -55204,17 +55204,17 @@
       </c>
       <c r="BY7" s="231"/>
     </row>
-    <row r="8" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B8" s="548"/>
-      <c r="C8" s="550"/>
-      <c r="D8" s="552"/>
+    <row r="8" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="648"/>
+      <c r="C8" s="650"/>
+      <c r="D8" s="652"/>
       <c r="E8" s="375" t="s">
         <v>13</v>
       </c>
       <c r="F8" s="380">
         <v>9037</v>
       </c>
-      <c r="G8" s="554"/>
+      <c r="G8" s="654"/>
       <c r="H8" s="363"/>
       <c r="I8" s="363"/>
       <c r="J8" s="363"/>
@@ -55344,12 +55344,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT8" s="556"/>
+      <c r="BT8" s="656"/>
       <c r="BU8" s="402">
         <f t="shared" si="3"/>
         <v>4206.6089012747216</v>
       </c>
-      <c r="BV8" s="546"/>
+      <c r="BV8" s="646"/>
       <c r="BW8" s="521">
         <v>702</v>
       </c>
@@ -55359,14 +55359,14 @@
       </c>
       <c r="BY8" s="231"/>
     </row>
-    <row r="9" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B9" s="557" t="s">
+    <row r="9" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="657" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="549">
+      <c r="C9" s="649">
         <v>4</v>
       </c>
-      <c r="D9" s="551" t="s">
+      <c r="D9" s="651" t="s">
         <v>303</v>
       </c>
       <c r="E9" s="376" t="s">
@@ -55375,7 +55375,7 @@
       <c r="F9" s="381">
         <v>204</v>
       </c>
-      <c r="G9" s="553">
+      <c r="G9" s="653">
         <f>+F10/F9</f>
         <v>45.849955882352937</v>
       </c>
@@ -55507,7 +55507,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT9" s="555">
+      <c r="BT9" s="655">
         <f>+IFERROR(AL10/AL9,0)</f>
         <v>0</v>
       </c>
@@ -55515,7 +55515,7 @@
         <f t="shared" si="3"/>
         <v>86</v>
       </c>
-      <c r="BV9" s="545">
+      <c r="BV9" s="645">
         <f>+IFERROR(BU10/BU9,0)</f>
         <v>41.840124533776304</v>
       </c>
@@ -55543,17 +55543,17 @@
         <v>304</v>
       </c>
     </row>
-    <row r="10" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B10" s="548"/>
-      <c r="C10" s="550"/>
-      <c r="D10" s="552"/>
+    <row r="10" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="648"/>
+      <c r="C10" s="650"/>
+      <c r="D10" s="652"/>
       <c r="E10" s="375" t="s">
         <v>13</v>
       </c>
       <c r="F10" s="380">
         <v>9353.3909999999996</v>
       </c>
-      <c r="G10" s="554"/>
+      <c r="G10" s="654"/>
       <c r="H10" s="363"/>
       <c r="I10" s="363"/>
       <c r="J10" s="363"/>
@@ -55683,12 +55683,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT10" s="556"/>
+      <c r="BT10" s="656"/>
       <c r="BU10" s="402">
         <f t="shared" si="3"/>
         <v>3598.2507099047621</v>
       </c>
-      <c r="BV10" s="546"/>
+      <c r="BV10" s="646"/>
       <c r="BW10" s="521">
         <v>561</v>
       </c>
@@ -55717,14 +55717,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B11" s="547" t="s">
+    <row r="11" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="647" t="s">
         <v>224</v>
       </c>
-      <c r="C11" s="549">
+      <c r="C11" s="649">
         <v>5</v>
       </c>
-      <c r="D11" s="551" t="s">
+      <c r="D11" s="651" t="s">
         <v>306</v>
       </c>
       <c r="E11" s="376" t="s">
@@ -55733,7 +55733,7 @@
       <c r="F11" s="381">
         <v>219</v>
       </c>
-      <c r="G11" s="553">
+      <c r="G11" s="653">
         <f>+F12/F11</f>
         <v>44.726027397260275</v>
       </c>
@@ -55864,7 +55864,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT11" s="555">
+      <c r="BT11" s="655">
         <f>+IFERROR(AL12/AL11,0)</f>
         <v>76</v>
       </c>
@@ -55872,7 +55872,7 @@
         <f t="shared" si="3"/>
         <v>77</v>
       </c>
-      <c r="BV11" s="545">
+      <c r="BV11" s="645">
         <f>+IFERROR(BU12/BU11,0)</f>
         <v>41.694139212603126</v>
       </c>
@@ -55907,17 +55907,17 @@
       <c r="CG11" s="233"/>
       <c r="CH11" s="233"/>
     </row>
-    <row r="12" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B12" s="548"/>
-      <c r="C12" s="550"/>
-      <c r="D12" s="552"/>
+    <row r="12" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="648"/>
+      <c r="C12" s="650"/>
+      <c r="D12" s="652"/>
       <c r="E12" s="375" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="380">
         <v>9795</v>
       </c>
-      <c r="G12" s="554"/>
+      <c r="G12" s="654"/>
       <c r="H12" s="363"/>
       <c r="I12" s="363"/>
       <c r="J12" s="363"/>
@@ -56046,12 +56046,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT12" s="556"/>
+      <c r="BT12" s="656"/>
       <c r="BU12" s="402">
         <f t="shared" si="3"/>
         <v>3210.4487193704408</v>
       </c>
-      <c r="BV12" s="546"/>
+      <c r="BV12" s="646"/>
       <c r="BW12" s="521">
         <v>579</v>
       </c>
@@ -56080,14 +56080,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B13" s="547" t="s">
+    <row r="13" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="647" t="s">
         <v>224</v>
       </c>
-      <c r="C13" s="549">
+      <c r="C13" s="649">
         <v>6</v>
       </c>
-      <c r="D13" s="551" t="s">
+      <c r="D13" s="651" t="s">
         <v>309</v>
       </c>
       <c r="E13" s="376" t="s">
@@ -56096,7 +56096,7 @@
       <c r="F13" s="381">
         <v>216</v>
       </c>
-      <c r="G13" s="553">
+      <c r="G13" s="653">
         <f>+F14/F13</f>
         <v>41.782407407407405</v>
       </c>
@@ -56224,7 +56224,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT13" s="555">
+      <c r="BT13" s="655">
         <f>+IFERROR(AL14/AL13,0)</f>
         <v>16.333333333333332</v>
       </c>
@@ -56232,7 +56232,7 @@
         <f t="shared" si="3"/>
         <v>82</v>
       </c>
-      <c r="BV13" s="545">
+      <c r="BV13" s="645">
         <f>+IFERROR(BU14/BU13,0)</f>
         <v>39.670731707317074</v>
       </c>
@@ -56264,17 +56264,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:86" ht="18.600000000000001" customHeight="1">
-      <c r="B14" s="548"/>
-      <c r="C14" s="550"/>
-      <c r="D14" s="552"/>
+    <row r="14" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="648"/>
+      <c r="C14" s="650"/>
+      <c r="D14" s="652"/>
       <c r="E14" s="375" t="s">
         <v>13</v>
       </c>
       <c r="F14" s="380">
         <v>9025</v>
       </c>
-      <c r="G14" s="554"/>
+      <c r="G14" s="654"/>
       <c r="H14" s="363"/>
       <c r="I14" s="363"/>
       <c r="J14" s="363"/>
@@ -56399,12 +56399,12 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="BT14" s="556"/>
+      <c r="BT14" s="656"/>
       <c r="BU14" s="402">
         <f t="shared" si="3"/>
         <v>3253</v>
       </c>
-      <c r="BV14" s="546"/>
+      <c r="BV14" s="646"/>
       <c r="BW14" s="521">
         <v>426</v>
       </c>
@@ -56439,7 +56439,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="2:86" s="234" customFormat="1" ht="18.600000000000001" customHeight="1">
+    <row r="15" spans="2:86" s="234" customFormat="1" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="372" t="s">
         <v>224</v>
       </c>
@@ -56608,7 +56608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="2:86" ht="18.600000000000001" customHeight="1">
+    <row r="16" spans="2:86" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="373" t="s">
         <v>222</v>
       </c>
@@ -56783,7 +56783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:85" ht="18.600000000000001" customHeight="1">
+    <row r="17" spans="2:85" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="373" t="s">
         <v>222</v>
       </c>
@@ -56945,14 +56945,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:85" ht="18.600000000000001" customHeight="1">
-      <c r="B18" s="537" t="s">
+    <row r="18" spans="2:85" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="637" t="s">
         <v>222</v>
       </c>
-      <c r="C18" s="539">
+      <c r="C18" s="639">
         <v>10</v>
       </c>
-      <c r="D18" s="540" t="s">
+      <c r="D18" s="640" t="s">
         <v>290</v>
       </c>
       <c r="E18" s="378" t="s">
@@ -56961,7 +56961,7 @@
       <c r="F18" s="384">
         <v>9</v>
       </c>
-      <c r="G18" s="542">
+      <c r="G18" s="642">
         <f>+F19/F18</f>
         <v>27.222222222222221</v>
       </c>
@@ -57095,7 +57095,7 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BT18" s="543">
+      <c r="BT18" s="643">
         <f>+IFERROR(AL19/AL18,0)</f>
         <v>33.958333333333336</v>
       </c>
@@ -57103,7 +57103,7 @@
         <f t="shared" ref="BU18:BU24" si="19">+AL18</f>
         <v>24</v>
       </c>
-      <c r="BV18" s="536">
+      <c r="BV18" s="636">
         <f>+IFERROR(BU19/BU18,0)</f>
         <v>33.958333333333336</v>
       </c>
@@ -57130,17 +57130,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:85" ht="18.600000000000001" customHeight="1">
-      <c r="B19" s="538"/>
-      <c r="C19" s="539"/>
-      <c r="D19" s="541"/>
+    <row r="19" spans="2:85" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="638"/>
+      <c r="C19" s="639"/>
+      <c r="D19" s="641"/>
       <c r="E19" s="378" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="384">
         <v>245</v>
       </c>
-      <c r="G19" s="542"/>
+      <c r="G19" s="642"/>
       <c r="H19" s="358"/>
       <c r="I19" s="358"/>
       <c r="J19" s="358"/>
@@ -57271,12 +57271,12 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="BT19" s="543"/>
+      <c r="BT19" s="643"/>
       <c r="BU19" s="404">
         <f t="shared" si="19"/>
         <v>815</v>
       </c>
-      <c r="BV19" s="536"/>
+      <c r="BV19" s="636"/>
       <c r="BW19" s="231"/>
       <c r="BX19" s="231"/>
       <c r="BY19" s="231"/>
@@ -57300,14 +57300,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B20" s="537" t="s">
+    <row r="20" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="637" t="s">
         <v>222</v>
       </c>
-      <c r="C20" s="544" t="s">
+      <c r="C20" s="644" t="s">
         <v>291</v>
       </c>
-      <c r="D20" s="540" t="s">
+      <c r="D20" s="640" t="s">
         <v>317</v>
       </c>
       <c r="E20" s="378" t="s">
@@ -57316,7 +57316,7 @@
       <c r="F20" s="384">
         <v>3</v>
       </c>
-      <c r="G20" s="542"/>
+      <c r="G20" s="642"/>
       <c r="H20" s="358"/>
       <c r="I20" s="358"/>
       <c r="J20" s="358"/>
@@ -57437,7 +57437,7 @@
         <f>+BR20</f>
         <v>0</v>
       </c>
-      <c r="BT20" s="543">
+      <c r="BT20" s="643">
         <f>+IFERROR(AL21/AL20,0)</f>
         <v>29.80952380952381</v>
       </c>
@@ -57445,7 +57445,7 @@
         <f t="shared" si="19"/>
         <v>21</v>
       </c>
-      <c r="BV20" s="536">
+      <c r="BV20" s="636">
         <f>+IFERROR(BU21/BU20,0)</f>
         <v>29.80952380952381</v>
       </c>
@@ -57470,17 +57470,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B21" s="538"/>
-      <c r="C21" s="544"/>
-      <c r="D21" s="541"/>
+    <row r="21" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="638"/>
+      <c r="C21" s="644"/>
+      <c r="D21" s="641"/>
       <c r="E21" s="378" t="s">
         <v>13</v>
       </c>
       <c r="F21" s="384">
         <v>86</v>
       </c>
-      <c r="G21" s="542"/>
+      <c r="G21" s="642"/>
       <c r="H21" s="358"/>
       <c r="I21" s="358"/>
       <c r="J21" s="358"/>
@@ -57601,12 +57601,12 @@
         <f t="shared" ref="BS21:BS23" si="30">+BR21</f>
         <v>0</v>
       </c>
-      <c r="BT21" s="543"/>
+      <c r="BT21" s="643"/>
       <c r="BU21" s="522">
         <f t="shared" si="19"/>
         <v>626</v>
       </c>
-      <c r="BV21" s="536"/>
+      <c r="BV21" s="636"/>
       <c r="BW21" s="231"/>
       <c r="CA21" s="406" t="s">
         <v>319</v>
@@ -57629,14 +57629,14 @@
       </c>
       <c r="CG21" s="238"/>
     </row>
-    <row r="22" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B22" s="537" t="s">
+    <row r="22" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="637" t="s">
         <v>222</v>
       </c>
-      <c r="C22" s="544" t="s">
+      <c r="C22" s="644" t="s">
         <v>293</v>
       </c>
-      <c r="D22" s="540" t="s">
+      <c r="D22" s="640" t="s">
         <v>320</v>
       </c>
       <c r="E22" s="378" t="s">
@@ -57645,7 +57645,7 @@
       <c r="F22" s="384">
         <v>6</v>
       </c>
-      <c r="G22" s="542"/>
+      <c r="G22" s="642"/>
       <c r="H22" s="358"/>
       <c r="I22" s="358"/>
       <c r="J22" s="358"/>
@@ -57766,7 +57766,7 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="BT22" s="543">
+      <c r="BT22" s="643">
         <f>+IFERROR(AL23/AL22,0)</f>
         <v>63</v>
       </c>
@@ -57774,23 +57774,23 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="BV22" s="536">
+      <c r="BV22" s="636">
         <f>+IFERROR(BU23/BU22,0)</f>
         <v>63</v>
       </c>
       <c r="BW22" s="231"/>
     </row>
-    <row r="23" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B23" s="537"/>
-      <c r="C23" s="544"/>
-      <c r="D23" s="540"/>
+    <row r="23" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="637"/>
+      <c r="C23" s="644"/>
+      <c r="D23" s="640"/>
       <c r="E23" s="378" t="s">
         <v>13</v>
       </c>
       <c r="F23" s="384">
         <v>159</v>
       </c>
-      <c r="G23" s="542"/>
+      <c r="G23" s="642"/>
       <c r="H23" s="358"/>
       <c r="I23" s="358"/>
       <c r="J23" s="358"/>
@@ -57914,23 +57914,23 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="BT23" s="543"/>
+      <c r="BT23" s="643"/>
       <c r="BU23" s="522">
         <f t="shared" si="19"/>
         <v>189</v>
       </c>
-      <c r="BV23" s="536"/>
+      <c r="BV23" s="636"/>
       <c r="BW23" s="231"/>
       <c r="BY23" s="239"/>
     </row>
-    <row r="24" spans="2:85" ht="18.600000000000001" customHeight="1" collapsed="1">
-      <c r="B24" s="537" t="s">
+    <row r="24" spans="2:85" ht="18.5" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="637" t="s">
         <v>222</v>
       </c>
-      <c r="C24" s="539">
+      <c r="C24" s="639">
         <v>11</v>
       </c>
-      <c r="D24" s="540" t="s">
+      <c r="D24" s="640" t="s">
         <v>321</v>
       </c>
       <c r="E24" s="378" t="s">
@@ -57939,7 +57939,7 @@
       <c r="F24" s="384">
         <v>26</v>
       </c>
-      <c r="G24" s="542">
+      <c r="G24" s="642">
         <f>+F25/F24</f>
         <v>56.230769230769234</v>
       </c>
@@ -58054,7 +58054,7 @@
         <f>+BR24</f>
         <v>0</v>
       </c>
-      <c r="BT24" s="543">
+      <c r="BT24" s="643">
         <f>+IFERROR(AL25/AL24,0)</f>
         <v>65.956521739130437</v>
       </c>
@@ -58062,22 +58062,22 @@
         <f t="shared" si="19"/>
         <v>23</v>
       </c>
-      <c r="BV24" s="536">
+      <c r="BV24" s="636">
         <f>+IFERROR(BU25/BU24,0)</f>
         <v>65.956521739130437</v>
       </c>
     </row>
-    <row r="25" spans="2:85" ht="18.600000000000001" customHeight="1">
-      <c r="B25" s="538"/>
-      <c r="C25" s="539"/>
-      <c r="D25" s="541"/>
+    <row r="25" spans="2:85" ht="18.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="638"/>
+      <c r="C25" s="639"/>
+      <c r="D25" s="641"/>
       <c r="E25" s="378" t="s">
         <v>13</v>
       </c>
       <c r="F25" s="384">
         <v>1462</v>
       </c>
-      <c r="G25" s="542"/>
+      <c r="G25" s="642"/>
       <c r="H25" s="358"/>
       <c r="I25" s="358"/>
       <c r="J25" s="358"/>
@@ -58189,21 +58189,21 @@
         <f t="shared" ref="BS25:BS27" si="32">+BR25</f>
         <v>0</v>
       </c>
-      <c r="BT25" s="543"/>
+      <c r="BT25" s="643"/>
       <c r="BU25" s="404">
         <f t="shared" ref="BU25:BU27" si="33">+AL25</f>
         <v>1517</v>
       </c>
-      <c r="BV25" s="536"/>
+      <c r="BV25" s="636"/>
     </row>
-    <row r="26" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B26" s="537" t="s">
+    <row r="26" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="637" t="s">
         <v>224</v>
       </c>
-      <c r="C26" s="544" t="s">
+      <c r="C26" s="644" t="s">
         <v>295</v>
       </c>
-      <c r="D26" s="540" t="s">
+      <c r="D26" s="640" t="s">
         <v>32</v>
       </c>
       <c r="E26" s="378" t="s">
@@ -58212,7 +58212,7 @@
       <c r="F26" s="384">
         <v>11</v>
       </c>
-      <c r="G26" s="542"/>
+      <c r="G26" s="642"/>
       <c r="H26" s="358"/>
       <c r="I26" s="358"/>
       <c r="J26" s="358"/>
@@ -58333,7 +58333,7 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="BT26" s="543">
+      <c r="BT26" s="643">
         <f>+IFERROR(AL27/AL26,0)</f>
         <v>36</v>
       </c>
@@ -58341,24 +58341,24 @@
         <f t="shared" si="33"/>
         <v>2</v>
       </c>
-      <c r="BV26" s="536">
+      <c r="BV26" s="636">
         <f>+IFERROR(BU27/BU26,0)</f>
         <v>36</v>
       </c>
       <c r="BW26" s="231"/>
       <c r="BX26" s="231"/>
     </row>
-    <row r="27" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1">
-      <c r="B27" s="538"/>
-      <c r="C27" s="544"/>
-      <c r="D27" s="541"/>
+    <row r="27" spans="2:85" ht="18.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="638"/>
+      <c r="C27" s="644"/>
+      <c r="D27" s="641"/>
       <c r="E27" s="378" t="s">
         <v>35</v>
       </c>
       <c r="F27" s="384">
         <v>822</v>
       </c>
-      <c r="G27" s="542"/>
+      <c r="G27" s="642"/>
       <c r="H27" s="358"/>
       <c r="I27" s="358"/>
       <c r="J27" s="358"/>
@@ -58479,24 +58479,24 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="BT27" s="543"/>
+      <c r="BT27" s="643"/>
       <c r="BU27" s="522">
         <f t="shared" si="33"/>
         <v>72</v>
       </c>
-      <c r="BV27" s="536"/>
+      <c r="BV27" s="636"/>
       <c r="BW27" s="231"/>
       <c r="BX27" s="240"/>
     </row>
-    <row r="28" spans="2:85" collapsed="1"/>
-    <row r="30" spans="2:85">
+    <row r="28" spans="2:85" collapsed="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="2:85" x14ac:dyDescent="0.2">
       <c r="BU30" s="231"/>
     </row>
-    <row r="31" spans="2:85">
+    <row r="31" spans="2:85" x14ac:dyDescent="0.2">
       <c r="AB31" s="231"/>
       <c r="BU31" s="237"/>
     </row>
-    <row r="32" spans="2:85">
+    <row r="32" spans="2:85" x14ac:dyDescent="0.2">
       <c r="L32" s="231"/>
       <c r="M32" s="231"/>
       <c r="N32" s="231"/>
@@ -58543,7 +58543,7 @@
       <c r="BU32" s="231"/>
       <c r="BV32" s="231"/>
     </row>
-    <row r="33" spans="12:83">
+    <row r="33" spans="12:83" x14ac:dyDescent="0.15">
       <c r="L33" s="231"/>
       <c r="M33" s="231"/>
       <c r="N33" s="231"/>
@@ -58613,7 +58613,7 @@
       <c r="BV33" s="349"/>
       <c r="BW33" s="349"/>
     </row>
-    <row r="34" spans="12:83">
+    <row r="34" spans="12:83" x14ac:dyDescent="0.15">
       <c r="BO34" s="340" t="s">
         <v>298</v>
       </c>
@@ -58629,7 +58629,7 @@
       <c r="BW34" s="349"/>
       <c r="CE34" s="231"/>
     </row>
-    <row r="35" spans="12:83">
+    <row r="35" spans="12:83" x14ac:dyDescent="0.2">
       <c r="CC35" s="231"/>
       <c r="CD35" s="231"/>
       <c r="CE35" s="231"/>
@@ -58715,16 +58715,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7391C42-D23F-419E-AB2A-423C9344465D}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="4" width="27.42578125" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" customWidth="1"/>
+    <col min="3" max="4" width="27.5" customWidth="1"/>
+    <col min="5" max="5" width="21.83203125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="314" t="s">
         <v>0</v>
       </c>
@@ -58744,7 +58744,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -58755,7 +58755,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -58766,7 +58766,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -58777,7 +58777,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -58788,7 +58788,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -58799,7 +58799,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -58810,7 +58810,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -58821,7 +58821,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="F9" s="314" t="s">
         <v>249</v>
       </c>
@@ -58833,15 +58833,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="379e1408-2888-4c35-8838-6acad26c5d63" xsi:nil="true"/>
@@ -58852,7 +58843,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000E5B92ACAE07D34EBD9C6E2622D0FB90" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f49de2c6b713e81b883d83440abc7b4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="0aaa94c6-a08a-4f31-80d4-9ed0227976f0" xmlns:ns3="379e1408-2888-4c35-8838-6acad26c5d63" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c077b7c82340bc93c6b35a1c6c7b7bd0" ns2:_="" ns3:_="">
     <xsd:import namespace="0aaa94c6-a08a-4f31-80d4-9ed0227976f0"/>
@@ -59067,14 +59058,49 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A808150-E722-40D5-B8E8-D4C3587EF81E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA55BE4-4489-45BC-A4D4-47ECF3AE446A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="379e1408-2888-4c35-8838-6acad26c5d63"/>
+    <ds:schemaRef ds:uri="0aaa94c6-a08a-4f31-80d4-9ed0227976f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFA55BE4-4489-45BC-A4D4-47ECF3AE446A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CC976FF-657C-434E-9000-618B1772614B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0aaa94c6-a08a-4f31-80d4-9ed0227976f0"/>
+    <ds:schemaRef ds:uri="379e1408-2888-4c35-8838-6acad26c5d63"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CC976FF-657C-434E-9000-618B1772614B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A808150-E722-40D5-B8E8-D4C3587EF81E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>